--- a/JP (Exclude Game)/Data/chara_talk.xlsx
+++ b/JP (Exclude Game)/Data/chara_talk.xlsx
@@ -11,7 +11,7 @@
     <sheet name="1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$126</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$127</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="303">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -446,7 +446,7 @@
   <si>
     <t xml:space="preserve">とんでもない変態{だ}。
 このクズ！
-どうしようもないわね。
+どうしようもないわ{よ}。
 罵られて喜ぶの？
 気持ち悪い{よ}。
 このブタが！
@@ -455,8 +455,8 @@
 死のう？
 ゴミ♪
 このかたつむり！
-ミンチにされたいの？
-どうしようもないカタツムリね。</t>
+ミンチにされたいの{か}？
+どうしようもないカタツムリ{ね}。</t>
   </si>
   <si>
     <t xml:space="preserve">insult_m</t>
@@ -467,7 +467,9 @@
 すぐに殺してやるよ。
 消えろザコめ。
 このかたつむり野郎。
-すぐにミンチにしてやるよ。</t>
+すぐにミンチにしてやるよ。
+この牝豚が！
+犬め！</t>
   </si>
   <si>
     <t xml:space="preserve">insult_f</t>
@@ -562,6 +564,15 @@
     <t xml:space="preserve">(…#1！#1！)
 (#1…)
 (#1を{くれ}…)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pervert4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">とんだ変態{だ}。
+おやおや。
+ふーん…？
+そう、私に？</t>
   </si>
   <si>
     <t xml:space="preserve">pervert3</t>
@@ -1762,9 +1773,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>2082240</xdr:colOff>
+      <xdr:colOff>2081520</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>126360</xdr:rowOff>
+      <xdr:rowOff>125640</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1774,7 +1785,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="50982840" cy="126360"/>
+          <a:ext cx="50982120" cy="125640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1807,9 +1818,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>519840</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>318600</xdr:rowOff>
+      <xdr:colOff>519120</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>317880</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1819,7 +1830,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="55190880" cy="37593000"/>
+          <a:ext cx="55190160" cy="38406960"/>
         </a:xfrm>
         <a:solidFill>
           <a:srgbClr val="ffffff"/>
@@ -1954,7 +1965,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CJ127"/>
+  <dimension ref="A1:CJ128"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.04"/>
@@ -3137,7 +3148,7 @@
       <c r="AU29" s="3"/>
       <c r="AV29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>91</v>
       </c>
@@ -3503,14 +3514,15 @@
       <c r="AU39" s="3"/>
       <c r="AV39" s="3"/>
     </row>
-    <row r="40" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="F40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
@@ -3540,13 +3552,14 @@
       <c r="AU40" s="3"/>
       <c r="AV40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>114</v>
       </c>
+      <c r="F41" s="4"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
@@ -3648,11 +3661,11 @@
       <c r="AU43" s="3"/>
       <c r="AV43" s="3"/>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="4" t="s">
         <v>120</v>
       </c>
       <c r="U44" s="3"/>
@@ -3684,11 +3697,11 @@
       <c r="AU44" s="3"/>
       <c r="AV44" s="3"/>
     </row>
-    <row r="45" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="1" t="s">
         <v>122</v>
       </c>
       <c r="U45" s="3"/>
@@ -3720,7 +3733,7 @@
       <c r="AU45" s="3"/>
       <c r="AV45" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>123</v>
       </c>
@@ -3756,7 +3769,7 @@
       <c r="AU46" s="3"/>
       <c r="AV46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>125</v>
       </c>
@@ -3792,7 +3805,7 @@
       <c r="AU47" s="3"/>
       <c r="AV47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>127</v>
       </c>
@@ -3829,30 +3842,12 @@
       <c r="AV48" s="3"/>
     </row>
     <row r="49" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="1" t="s">
         <v>129</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="5"/>
-      <c r="K49" s="5"/>
-      <c r="L49" s="5"/>
-      <c r="M49" s="5"/>
-      <c r="N49" s="5"/>
-      <c r="O49" s="5"/>
-      <c r="P49" s="5"/>
-      <c r="Q49" s="5"/>
-      <c r="R49" s="5"/>
-      <c r="S49" s="5"/>
-      <c r="T49" s="5"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
@@ -3882,11 +3877,11 @@
       <c r="AU49" s="3"/>
       <c r="AV49" s="3"/>
     </row>
-    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="4" t="s">
         <v>132</v>
       </c>
       <c r="C50" s="5"/>
@@ -3936,11 +3931,11 @@
       <c r="AU50" s="3"/>
       <c r="AV50" s="3"/>
     </row>
-    <row r="51" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="5" t="s">
         <v>134</v>
       </c>
       <c r="C51" s="5"/>
@@ -3990,13 +3985,31 @@
       <c r="AU51" s="3"/>
       <c r="AV51" s="3"/>
     </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+    <row r="52" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="4" t="s">
         <v>136</v>
       </c>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="5"/>
+      <c r="R52" s="5"/>
+      <c r="S52" s="5"/>
+      <c r="T52" s="5"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
@@ -4134,11 +4147,11 @@
       <c r="AU55" s="3"/>
       <c r="AV55" s="3"/>
     </row>
-    <row r="56" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="1" t="s">
         <v>144</v>
       </c>
       <c r="U56" s="3"/>
@@ -4170,7 +4183,7 @@
       <c r="AU56" s="3"/>
       <c r="AV56" s="3"/>
     </row>
-    <row r="57" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
         <v>145</v>
       </c>
@@ -4206,11 +4219,11 @@
       <c r="AU57" s="3"/>
       <c r="AV57" s="3"/>
     </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="4" t="s">
         <v>148</v>
       </c>
       <c r="U58" s="3"/>
@@ -4242,11 +4255,11 @@
       <c r="AU58" s="3"/>
       <c r="AV58" s="3"/>
     </row>
-    <row r="59" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="1" t="s">
         <v>150</v>
       </c>
       <c r="U59" s="3"/>
@@ -4278,11 +4291,11 @@
       <c r="AU59" s="3"/>
       <c r="AV59" s="3"/>
     </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="4" t="s">
         <v>152</v>
       </c>
       <c r="U60" s="3"/>
@@ -4386,11 +4399,11 @@
       <c r="AU62" s="3"/>
       <c r="AV62" s="3"/>
     </row>
-    <row r="63" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="1" t="s">
         <v>158</v>
       </c>
       <c r="U63" s="3"/>
@@ -4422,9 +4435,12 @@
       <c r="AU63" s="3"/>
       <c r="AV63" s="3"/>
     </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
         <v>159</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>160</v>
       </c>
       <c r="U64" s="3"/>
       <c r="V64" s="3"/>
@@ -4455,11 +4471,8 @@
       <c r="AU64" s="3"/>
       <c r="AV64" s="3"/>
     </row>
-    <row r="65" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B65" s="4" t="s">
         <v>161</v>
       </c>
       <c r="U65" s="3"/>
@@ -4491,11 +4504,11 @@
       <c r="AU65" s="3"/>
       <c r="AV65" s="3"/>
     </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="4" t="s">
         <v>163</v>
       </c>
       <c r="U66" s="3"/>
@@ -4527,12 +4540,12 @@
       <c r="AU66" s="3"/>
       <c r="AV66" s="3"/>
     </row>
-    <row r="67" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B67" s="4" t="s">
-        <v>144</v>
+      <c r="B67" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
@@ -4563,12 +4576,12 @@
       <c r="AU67" s="3"/>
       <c r="AV67" s="3"/>
     </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B68" s="1" t="s">
         <v>166</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>146</v>
       </c>
       <c r="U68" s="3"/>
       <c r="V68" s="3"/>
@@ -4599,11 +4612,11 @@
       <c r="AU68" s="3"/>
       <c r="AV68" s="3"/>
     </row>
-    <row r="69" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="1" t="s">
         <v>168</v>
       </c>
       <c r="U69" s="3"/>
@@ -4635,7 +4648,7 @@
       <c r="AU69" s="3"/>
       <c r="AV69" s="3"/>
     </row>
-    <row r="70" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
         <v>169</v>
       </c>
@@ -4671,7 +4684,7 @@
       <c r="AU70" s="3"/>
       <c r="AV70" s="3"/>
     </row>
-    <row r="71" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
         <v>171</v>
       </c>
@@ -4707,7 +4720,7 @@
       <c r="AU71" s="3"/>
       <c r="AV71" s="3"/>
     </row>
-    <row r="72" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
         <v>173</v>
       </c>
@@ -4743,7 +4756,7 @@
       <c r="AU72" s="3"/>
       <c r="AV72" s="3"/>
     </row>
-    <row r="73" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>175</v>
       </c>
@@ -4779,11 +4792,11 @@
       <c r="AU73" s="3"/>
       <c r="AV73" s="3"/>
     </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="4" t="s">
         <v>178</v>
       </c>
       <c r="U74" s="3"/>
@@ -4815,11 +4828,11 @@
       <c r="AU74" s="3"/>
       <c r="AV74" s="3"/>
     </row>
-    <row r="75" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="1" t="s">
         <v>180</v>
       </c>
       <c r="U75" s="3"/>
@@ -4851,7 +4864,7 @@
       <c r="AU75" s="3"/>
       <c r="AV75" s="3"/>
     </row>
-    <row r="76" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
         <v>181</v>
       </c>
@@ -4887,11 +4900,11 @@
       <c r="AU76" s="3"/>
       <c r="AV76" s="3"/>
     </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="4" t="s">
         <v>184</v>
       </c>
       <c r="U77" s="3"/>
@@ -4995,7 +5008,7 @@
       <c r="AU79" s="3"/>
       <c r="AV79" s="3"/>
     </row>
-    <row r="80" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
         <v>189</v>
       </c>
@@ -5031,7 +5044,7 @@
       <c r="AU80" s="3"/>
       <c r="AV80" s="3"/>
     </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
         <v>191</v>
       </c>
@@ -5067,11 +5080,11 @@
       <c r="AU81" s="3"/>
       <c r="AV81" s="3"/>
     </row>
-    <row r="82" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B82" s="1" t="s">
         <v>194</v>
       </c>
       <c r="U82" s="3"/>
@@ -5103,11 +5116,11 @@
       <c r="AU82" s="3"/>
       <c r="AV82" s="3"/>
     </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="4" t="s">
         <v>196</v>
       </c>
       <c r="U83" s="3"/>
@@ -5139,11 +5152,11 @@
       <c r="AU83" s="3"/>
       <c r="AV83" s="3"/>
     </row>
-    <row r="84" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="1" t="s">
         <v>198</v>
       </c>
       <c r="U84" s="3"/>
@@ -5175,13 +5188,41 @@
       <c r="AU84" s="3"/>
       <c r="AV84" s="3"/>
     </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="4" t="s">
         <v>200</v>
       </c>
+      <c r="U85" s="3"/>
+      <c r="V85" s="3"/>
+      <c r="W85" s="3"/>
+      <c r="X85" s="3"/>
+      <c r="Y85" s="3"/>
+      <c r="Z85" s="3"/>
+      <c r="AA85" s="3"/>
+      <c r="AB85" s="3"/>
+      <c r="AC85" s="3"/>
+      <c r="AD85" s="3"/>
+      <c r="AE85" s="3"/>
+      <c r="AF85" s="3"/>
+      <c r="AG85" s="3"/>
+      <c r="AH85" s="3"/>
+      <c r="AI85" s="3"/>
+      <c r="AJ85" s="3"/>
+      <c r="AK85" s="3"/>
+      <c r="AL85" s="3"/>
+      <c r="AM85" s="3"/>
+      <c r="AN85" s="3"/>
+      <c r="AO85" s="3"/>
+      <c r="AP85" s="3"/>
+      <c r="AQ85" s="3"/>
+      <c r="AR85" s="3"/>
+      <c r="AS85" s="3"/>
+      <c r="AT85" s="3"/>
+      <c r="AU85" s="3"/>
+      <c r="AV85" s="3"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
@@ -5195,16 +5236,16 @@
       <c r="A87" s="1" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="88" customFormat="false" ht="335.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B88" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="335.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
         <v>206</v>
       </c>
@@ -5212,7 +5253,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
         <v>208</v>
       </c>
@@ -5220,39 +5261,39 @@
         <v>209</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="5" t="s">
+    <row r="91" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
         <v>210</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C91" s="5"/>
-      <c r="D91" s="5"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
-      <c r="G91" s="5"/>
-      <c r="H91" s="5"/>
-      <c r="I91" s="5"/>
-      <c r="J91" s="5"/>
-      <c r="K91" s="5"/>
-      <c r="L91" s="5"/>
-      <c r="M91" s="5"/>
-      <c r="N91" s="5"/>
-      <c r="O91" s="5"/>
-      <c r="P91" s="5"/>
-      <c r="Q91" s="5"/>
-      <c r="R91" s="5"/>
-      <c r="S91" s="5"/>
-      <c r="T91" s="5"/>
-    </row>
-    <row r="92" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
+    </row>
+    <row r="92" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="5" t="s">
         <v>212</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>213</v>
       </c>
+      <c r="C92" s="5"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="5"/>
+      <c r="K92" s="5"/>
+      <c r="L92" s="5"/>
+      <c r="M92" s="5"/>
+      <c r="N92" s="5"/>
+      <c r="O92" s="5"/>
+      <c r="P92" s="5"/>
+      <c r="Q92" s="5"/>
+      <c r="R92" s="5"/>
+      <c r="S92" s="5"/>
+      <c r="T92" s="5"/>
     </row>
     <row r="93" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
@@ -5262,7 +5303,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
         <v>216</v>
       </c>
@@ -5270,7 +5311,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
         <v>218</v>
       </c>
@@ -5278,7 +5319,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
         <v>220</v>
       </c>
@@ -5286,7 +5327,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
         <v>222</v>
       </c>
@@ -5294,93 +5335,93 @@
         <v>223</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="5" t="s">
+    <row r="98" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
         <v>224</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="C98" s="5"/>
-      <c r="D98" s="5"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
-      <c r="G98" s="5"/>
-      <c r="H98" s="5"/>
-      <c r="I98" s="5"/>
-      <c r="J98" s="5"/>
-      <c r="K98" s="5"/>
-      <c r="L98" s="5"/>
-      <c r="M98" s="5"/>
-      <c r="N98" s="5"/>
-      <c r="O98" s="5"/>
-      <c r="P98" s="5"/>
-      <c r="Q98" s="5"/>
-      <c r="R98" s="5"/>
-      <c r="S98" s="5"/>
-      <c r="T98" s="5"/>
-    </row>
-    <row r="99" customFormat="false" ht="252.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="6" t="s">
+    </row>
+    <row r="99" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="5" t="s">
         <v>226</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4"/>
-      <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
-      <c r="K99" s="4"/>
-      <c r="L99" s="4"/>
-      <c r="M99" s="4"/>
-      <c r="N99" s="4"/>
-      <c r="O99" s="4"/>
-      <c r="P99" s="4"/>
-      <c r="Q99" s="4"/>
-      <c r="R99" s="4"/>
-      <c r="S99" s="4"/>
-      <c r="T99" s="4"/>
-    </row>
-    <row r="100" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="5" t="s">
+      <c r="C99" s="5"/>
+      <c r="D99" s="5"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="5"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="5"/>
+      <c r="I99" s="5"/>
+      <c r="J99" s="5"/>
+      <c r="K99" s="5"/>
+      <c r="L99" s="5"/>
+      <c r="M99" s="5"/>
+      <c r="N99" s="5"/>
+      <c r="O99" s="5"/>
+      <c r="P99" s="5"/>
+      <c r="Q99" s="5"/>
+      <c r="R99" s="5"/>
+      <c r="S99" s="5"/>
+      <c r="T99" s="5"/>
+    </row>
+    <row r="100" customFormat="false" ht="252.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="6" t="s">
         <v>228</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="C100" s="5"/>
-      <c r="D100" s="5"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="5"/>
-      <c r="G100" s="5"/>
-      <c r="H100" s="5"/>
-      <c r="I100" s="5"/>
-      <c r="J100" s="5"/>
-      <c r="K100" s="5"/>
-      <c r="L100" s="5"/>
-      <c r="M100" s="5"/>
-      <c r="N100" s="5"/>
-      <c r="O100" s="5"/>
-      <c r="P100" s="5"/>
-      <c r="Q100" s="5"/>
-      <c r="R100" s="5"/>
-      <c r="S100" s="5"/>
-      <c r="T100" s="5"/>
-    </row>
-    <row r="101" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="4"/>
+      <c r="K100" s="4"/>
+      <c r="L100" s="4"/>
+      <c r="M100" s="4"/>
+      <c r="N100" s="4"/>
+      <c r="O100" s="4"/>
+      <c r="P100" s="4"/>
+      <c r="Q100" s="4"/>
+      <c r="R100" s="4"/>
+      <c r="S100" s="4"/>
+      <c r="T100" s="4"/>
+    </row>
+    <row r="101" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="5" t="s">
         <v>230</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="102" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C101" s="5"/>
+      <c r="D101" s="5"/>
+      <c r="E101" s="5"/>
+      <c r="F101" s="5"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="5"/>
+      <c r="I101" s="5"/>
+      <c r="J101" s="5"/>
+      <c r="K101" s="5"/>
+      <c r="L101" s="5"/>
+      <c r="M101" s="5"/>
+      <c r="N101" s="5"/>
+      <c r="O101" s="5"/>
+      <c r="P101" s="5"/>
+      <c r="Q101" s="5"/>
+      <c r="R101" s="5"/>
+      <c r="S101" s="5"/>
+      <c r="T101" s="5"/>
+    </row>
+    <row r="102" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
         <v>232</v>
       </c>
@@ -5388,7 +5429,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
         <v>234</v>
       </c>
@@ -5396,31 +5437,13 @@
         <v>235</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="5" t="s">
+    <row r="104" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
         <v>236</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="C104" s="5"/>
-      <c r="D104" s="5"/>
-      <c r="E104" s="5"/>
-      <c r="F104" s="5"/>
-      <c r="G104" s="5"/>
-      <c r="H104" s="5"/>
-      <c r="I104" s="5"/>
-      <c r="J104" s="5"/>
-      <c r="K104" s="5"/>
-      <c r="L104" s="5"/>
-      <c r="M104" s="5"/>
-      <c r="N104" s="5"/>
-      <c r="O104" s="5"/>
-      <c r="P104" s="5"/>
-      <c r="Q104" s="5"/>
-      <c r="R104" s="5"/>
-      <c r="S104" s="5"/>
-      <c r="T104" s="5"/>
     </row>
     <row r="105" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="5" t="s">
@@ -5448,77 +5471,95 @@
       <c r="S105" s="5"/>
       <c r="T105" s="5"/>
     </row>
-    <row r="106" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="1" t="s">
+    <row r="106" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="5" t="s">
         <v>240</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C106" s="5"/>
+      <c r="D106" s="5"/>
+      <c r="E106" s="5"/>
+      <c r="F106" s="5"/>
+      <c r="G106" s="5"/>
+      <c r="H106" s="5"/>
+      <c r="I106" s="5"/>
+      <c r="J106" s="5"/>
+      <c r="K106" s="5"/>
+      <c r="L106" s="5"/>
+      <c r="M106" s="5"/>
+      <c r="N106" s="5"/>
+      <c r="O106" s="5"/>
+      <c r="P106" s="5"/>
+      <c r="Q106" s="5"/>
+      <c r="R106" s="5"/>
+      <c r="S106" s="5"/>
+      <c r="T106" s="5"/>
+    </row>
+    <row r="107" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D106" s="4" t="s">
+      <c r="B107" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="E106" s="4" t="s">
+      <c r="C107" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="F106" s="4" t="s">
+      <c r="D107" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="G106" s="4" t="s">
+      <c r="E107" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="H106" s="4" t="s">
+      <c r="F107" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="I106" s="4" t="s">
+      <c r="G107" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="J106" s="4" t="s">
+      <c r="H107" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="K106" s="4" t="s">
+      <c r="I107" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="L106" s="4" t="s">
+      <c r="J107" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="M106" s="4" t="s">
+      <c r="K107" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="N106" s="4" t="s">
+      <c r="L107" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="O106" s="4" t="s">
+      <c r="M107" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="P106" s="4" t="s">
+      <c r="N107" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="Q106" s="4" t="s">
+      <c r="O107" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="R106" s="4" t="s">
+      <c r="P107" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="S106" s="4" t="s">
+      <c r="Q107" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="T106" s="4" t="s">
+      <c r="R107" s="4" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="107" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="s">
+      <c r="S107" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="T107" s="4" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
         <v>262</v>
       </c>
@@ -5526,41 +5567,41 @@
         <v>263</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="5" t="s">
+    <row r="109" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1" t="s">
         <v>264</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="C109" s="5"/>
-      <c r="D109" s="5"/>
-      <c r="E109" s="5"/>
-      <c r="F109" s="5"/>
-      <c r="G109" s="5"/>
-      <c r="H109" s="5"/>
-      <c r="I109" s="5"/>
-      <c r="J109" s="5"/>
-      <c r="K109" s="5"/>
-      <c r="L109" s="5"/>
-      <c r="M109" s="5"/>
-      <c r="N109" s="5"/>
-      <c r="O109" s="5"/>
-      <c r="P109" s="5"/>
-      <c r="Q109" s="5"/>
-      <c r="R109" s="5"/>
-      <c r="S109" s="5"/>
-      <c r="T109" s="5"/>
-    </row>
-    <row r="110" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="1" t="s">
+    </row>
+    <row r="110" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="B110" s="7" t="s">
+      <c r="B110" s="4" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="111" customFormat="false" ht="54.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C110" s="5"/>
+      <c r="D110" s="5"/>
+      <c r="E110" s="5"/>
+      <c r="F110" s="5"/>
+      <c r="G110" s="5"/>
+      <c r="H110" s="5"/>
+      <c r="I110" s="5"/>
+      <c r="J110" s="5"/>
+      <c r="K110" s="5"/>
+      <c r="L110" s="5"/>
+      <c r="M110" s="5"/>
+      <c r="N110" s="5"/>
+      <c r="O110" s="5"/>
+      <c r="P110" s="5"/>
+      <c r="Q110" s="5"/>
+      <c r="R110" s="5"/>
+      <c r="S110" s="5"/>
+      <c r="T110" s="5"/>
+    </row>
+    <row r="111" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
         <v>268</v>
       </c>
@@ -5568,85 +5609,85 @@
         <v>269</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="54.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B112" s="7" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B113" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="I113" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="J113" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="K113" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="L113" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="M113" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="N113" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="O113" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="P113" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q113" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="R113" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="S113" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="T113" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B114" s="1" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="115" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C114" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="M114" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="N114" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="O114" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="P114" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q114" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="R114" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="S114" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="T114" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
         <v>276</v>
       </c>
@@ -5654,11 +5695,11 @@
         <v>277</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B116" s="4" t="s">
         <v>279</v>
       </c>
     </row>
@@ -5670,68 +5711,68 @@
         <v>281</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="B118" s="1" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
         <v>284</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="AX119" s="3"/>
-      <c r="AY119" s="3"/>
-      <c r="AZ119" s="3"/>
-      <c r="BA119" s="3"/>
-      <c r="BB119" s="3"/>
-      <c r="BC119" s="3"/>
-      <c r="BD119" s="3"/>
-      <c r="BE119" s="3"/>
-      <c r="BF119" s="3"/>
-      <c r="BG119" s="3"/>
-      <c r="BH119" s="3"/>
-      <c r="BI119" s="3"/>
-      <c r="BJ119" s="3"/>
-      <c r="BK119" s="3"/>
-      <c r="BL119" s="3"/>
-      <c r="BM119" s="3"/>
-      <c r="BN119" s="3"/>
-      <c r="BO119" s="3"/>
-      <c r="BP119" s="3"/>
-      <c r="BQ119" s="3"/>
-      <c r="BR119" s="3"/>
-      <c r="BS119" s="3"/>
-      <c r="BT119" s="3"/>
-      <c r="BU119" s="3"/>
-      <c r="BV119" s="3"/>
-      <c r="BW119" s="3"/>
-      <c r="BX119" s="3"/>
-      <c r="BY119" s="3"/>
-      <c r="BZ119" s="3"/>
-      <c r="CA119" s="3"/>
-      <c r="CB119" s="3"/>
-      <c r="CC119" s="3"/>
-      <c r="CD119" s="3"/>
-      <c r="CE119" s="3"/>
-      <c r="CF119" s="3"/>
-      <c r="CG119" s="3"/>
-      <c r="CH119" s="3"/>
-      <c r="CI119" s="3"/>
-      <c r="CJ119" s="3"/>
-    </row>
-    <row r="120" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="120" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
         <v>286</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>287</v>
       </c>
+      <c r="AX120" s="3"/>
+      <c r="AY120" s="3"/>
+      <c r="AZ120" s="3"/>
+      <c r="BA120" s="3"/>
+      <c r="BB120" s="3"/>
+      <c r="BC120" s="3"/>
+      <c r="BD120" s="3"/>
+      <c r="BE120" s="3"/>
+      <c r="BF120" s="3"/>
+      <c r="BG120" s="3"/>
+      <c r="BH120" s="3"/>
+      <c r="BI120" s="3"/>
+      <c r="BJ120" s="3"/>
+      <c r="BK120" s="3"/>
+      <c r="BL120" s="3"/>
+      <c r="BM120" s="3"/>
+      <c r="BN120" s="3"/>
+      <c r="BO120" s="3"/>
+      <c r="BP120" s="3"/>
+      <c r="BQ120" s="3"/>
+      <c r="BR120" s="3"/>
+      <c r="BS120" s="3"/>
+      <c r="BT120" s="3"/>
+      <c r="BU120" s="3"/>
+      <c r="BV120" s="3"/>
+      <c r="BW120" s="3"/>
+      <c r="BX120" s="3"/>
+      <c r="BY120" s="3"/>
+      <c r="BZ120" s="3"/>
+      <c r="CA120" s="3"/>
+      <c r="CB120" s="3"/>
+      <c r="CC120" s="3"/>
+      <c r="CD120" s="3"/>
+      <c r="CE120" s="3"/>
+      <c r="CF120" s="3"/>
+      <c r="CG120" s="3"/>
+      <c r="CH120" s="3"/>
+      <c r="CI120" s="3"/>
+      <c r="CJ120" s="3"/>
     </row>
     <row r="121" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
@@ -5740,47 +5781,8 @@
       <c r="B121" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="AX121" s="3"/>
-      <c r="AY121" s="3"/>
-      <c r="AZ121" s="3"/>
-      <c r="BA121" s="3"/>
-      <c r="BB121" s="3"/>
-      <c r="BC121" s="3"/>
-      <c r="BD121" s="3"/>
-      <c r="BE121" s="3"/>
-      <c r="BF121" s="3"/>
-      <c r="BG121" s="3"/>
-      <c r="BH121" s="3"/>
-      <c r="BI121" s="3"/>
-      <c r="BJ121" s="3"/>
-      <c r="BK121" s="3"/>
-      <c r="BL121" s="3"/>
-      <c r="BM121" s="3"/>
-      <c r="BN121" s="3"/>
-      <c r="BO121" s="3"/>
-      <c r="BP121" s="3"/>
-      <c r="BQ121" s="3"/>
-      <c r="BR121" s="3"/>
-      <c r="BS121" s="3"/>
-      <c r="BT121" s="3"/>
-      <c r="BU121" s="3"/>
-      <c r="BV121" s="3"/>
-      <c r="BW121" s="3"/>
-      <c r="BX121" s="3"/>
-      <c r="BY121" s="3"/>
-      <c r="BZ121" s="3"/>
-      <c r="CA121" s="3"/>
-      <c r="CB121" s="3"/>
-      <c r="CC121" s="3"/>
-      <c r="CD121" s="3"/>
-      <c r="CE121" s="3"/>
-      <c r="CF121" s="3"/>
-      <c r="CG121" s="3"/>
-      <c r="CH121" s="3"/>
-      <c r="CI121" s="3"/>
-      <c r="CJ121" s="3"/>
-    </row>
-    <row r="122" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="122" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
         <v>290</v>
       </c>
@@ -5827,78 +5829,117 @@
       <c r="CI122" s="3"/>
       <c r="CJ122" s="3"/>
     </row>
-    <row r="123" s="3" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
         <v>292</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
-      <c r="E123" s="1"/>
-      <c r="F123" s="1"/>
-      <c r="G123" s="1"/>
-      <c r="H123" s="1"/>
-      <c r="I123" s="1"/>
-      <c r="J123" s="1"/>
-      <c r="K123" s="1"/>
-      <c r="L123" s="1"/>
-      <c r="M123" s="1"/>
-      <c r="N123" s="1"/>
-      <c r="O123" s="1"/>
-      <c r="P123" s="1"/>
-      <c r="Q123" s="1"/>
-      <c r="R123" s="1"/>
-      <c r="S123" s="1"/>
-      <c r="T123" s="1"/>
-      <c r="U123" s="1"/>
-      <c r="V123" s="1"/>
-      <c r="W123" s="1"/>
-      <c r="X123" s="1"/>
-      <c r="Y123" s="1"/>
-      <c r="Z123" s="1"/>
-      <c r="AA123" s="1"/>
-      <c r="AB123" s="1"/>
-      <c r="AC123" s="1"/>
-      <c r="AD123" s="1"/>
-      <c r="AE123" s="1"/>
-      <c r="AF123" s="1"/>
-      <c r="AG123" s="1"/>
-      <c r="AH123" s="1"/>
-      <c r="AI123" s="1"/>
-      <c r="AJ123" s="1"/>
-      <c r="AK123" s="1"/>
-      <c r="AL123" s="1"/>
-      <c r="AM123" s="1"/>
-      <c r="AN123" s="1"/>
-      <c r="AO123" s="1"/>
-      <c r="AP123" s="1"/>
-      <c r="AQ123" s="1"/>
-      <c r="AR123" s="1"/>
-      <c r="AS123" s="1"/>
-      <c r="AT123" s="1"/>
-      <c r="AU123" s="1"/>
-      <c r="AV123" s="1"/>
-      <c r="AW123" s="1"/>
-    </row>
-    <row r="124" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>293</v>
+      </c>
+      <c r="AX123" s="3"/>
+      <c r="AY123" s="3"/>
+      <c r="AZ123" s="3"/>
+      <c r="BA123" s="3"/>
+      <c r="BB123" s="3"/>
+      <c r="BC123" s="3"/>
+      <c r="BD123" s="3"/>
+      <c r="BE123" s="3"/>
+      <c r="BF123" s="3"/>
+      <c r="BG123" s="3"/>
+      <c r="BH123" s="3"/>
+      <c r="BI123" s="3"/>
+      <c r="BJ123" s="3"/>
+      <c r="BK123" s="3"/>
+      <c r="BL123" s="3"/>
+      <c r="BM123" s="3"/>
+      <c r="BN123" s="3"/>
+      <c r="BO123" s="3"/>
+      <c r="BP123" s="3"/>
+      <c r="BQ123" s="3"/>
+      <c r="BR123" s="3"/>
+      <c r="BS123" s="3"/>
+      <c r="BT123" s="3"/>
+      <c r="BU123" s="3"/>
+      <c r="BV123" s="3"/>
+      <c r="BW123" s="3"/>
+      <c r="BX123" s="3"/>
+      <c r="BY123" s="3"/>
+      <c r="BZ123" s="3"/>
+      <c r="CA123" s="3"/>
+      <c r="CB123" s="3"/>
+      <c r="CC123" s="3"/>
+      <c r="CD123" s="3"/>
+      <c r="CE123" s="3"/>
+      <c r="CF123" s="3"/>
+      <c r="CG123" s="3"/>
+      <c r="CH123" s="3"/>
+      <c r="CI123" s="3"/>
+      <c r="CJ123" s="3"/>
+    </row>
+    <row r="124" s="3" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>146</v>
+      </c>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
+      <c r="E124" s="1"/>
+      <c r="F124" s="1"/>
+      <c r="G124" s="1"/>
+      <c r="H124" s="1"/>
+      <c r="I124" s="1"/>
+      <c r="J124" s="1"/>
+      <c r="K124" s="1"/>
+      <c r="L124" s="1"/>
+      <c r="M124" s="1"/>
+      <c r="N124" s="1"/>
+      <c r="O124" s="1"/>
+      <c r="P124" s="1"/>
+      <c r="Q124" s="1"/>
+      <c r="R124" s="1"/>
+      <c r="S124" s="1"/>
+      <c r="T124" s="1"/>
+      <c r="U124" s="1"/>
+      <c r="V124" s="1"/>
+      <c r="W124" s="1"/>
+      <c r="X124" s="1"/>
+      <c r="Y124" s="1"/>
+      <c r="Z124" s="1"/>
+      <c r="AA124" s="1"/>
+      <c r="AB124" s="1"/>
+      <c r="AC124" s="1"/>
+      <c r="AD124" s="1"/>
+      <c r="AE124" s="1"/>
+      <c r="AF124" s="1"/>
+      <c r="AG124" s="1"/>
+      <c r="AH124" s="1"/>
+      <c r="AI124" s="1"/>
+      <c r="AJ124" s="1"/>
+      <c r="AK124" s="1"/>
+      <c r="AL124" s="1"/>
+      <c r="AM124" s="1"/>
+      <c r="AN124" s="1"/>
+      <c r="AO124" s="1"/>
+      <c r="AP124" s="1"/>
+      <c r="AQ124" s="1"/>
+      <c r="AR124" s="1"/>
+      <c r="AS124" s="1"/>
+      <c r="AT124" s="1"/>
+      <c r="AU124" s="1"/>
+      <c r="AV124" s="1"/>
+      <c r="AW124" s="1"/>
+    </row>
+    <row r="125" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B125" s="8" t="s">
+      <c r="B125" s="4" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
         <v>297</v>
       </c>
@@ -5906,16 +5947,24 @@
         <v>298</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B127" s="4" t="s">
+      <c r="B127" s="8" t="s">
         <v>300</v>
       </c>
     </row>
+    <row r="128" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:T126"/>
+  <autoFilter ref="A2:T127"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/JP (Exclude Game)/Data/chara_talk.xlsx
+++ b/JP (Exclude Game)/Data/chara_talk.xlsx
@@ -11,7 +11,7 @@
     <sheet name="1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$127</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$132</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="313">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -140,6 +140,91 @@
   </si>
   <si>
     <t xml:space="preserve">夢人</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kiss</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="ヒラギノ角ゴ ProN W3"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">チュッ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">*</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">curse_wed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">この泥棒猫！
+キー！
+ぶち壊してやる{よ}！
+許さない{よ}！
+認めない{よ}！
+地獄に落ち{なさい}！
+ウ゛ァ゛ぁ゛ぁ゛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grats_wed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">おめでとう！
+幸せに{な}！
+ヒューヒュー！
+素敵{だ}！
+お似合い{だ}！
+ラブラブ{だな}！
+いいぞ！
+愛に乾杯{だ}。
+かんぱ～い。
+キスしろ{よ}！
+やった{な}！
+良い日{だ}。
+最高の二人{だ}。
+愛が溢れてる{よ}。
+感動した{のだ}。
+乾杯！
+今日は飲む{よ}。
+ブラボー！
+尊い{よ}…
+幸せになって{くれ}。 
+最高のカップル爆誕！ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">die</t>
+  </si>
+  <si>
+    <t xml:space="preserve">死ね！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no_problem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ノープロブレム</t>
   </si>
   <si>
     <t xml:space="preserve">unlock_stairs_nasu</t>
@@ -1713,15 +1798,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1773,9 +1858,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>2081520</xdr:colOff>
+      <xdr:colOff>2080440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>125640</xdr:rowOff>
+      <xdr:rowOff>124560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1785,7 +1870,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="50982120" cy="125640"/>
+          <a:ext cx="50981040" cy="124560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1818,9 +1903,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>519120</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>317880</xdr:rowOff>
+      <xdr:colOff>518040</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>316800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1830,7 +1915,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="55190160" cy="38406960"/>
+          <a:ext cx="55189080" cy="42680880"/>
         </a:xfrm>
         <a:solidFill>
           <a:srgbClr val="ffffff"/>
@@ -1965,7 +2050,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CJ128"/>
+  <dimension ref="A1:CJ133"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.04"/>
@@ -2199,11 +2284,11 @@
       <c r="AU3" s="3"/>
       <c r="AV3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="4" t="s">
         <v>40</v>
       </c>
       <c r="U4" s="3"/>
@@ -2235,11 +2320,11 @@
       <c r="AU4" s="3"/>
       <c r="AV4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>42</v>
       </c>
       <c r="U5" s="3"/>
@@ -2271,11 +2356,11 @@
       <c r="AU5" s="3"/>
       <c r="AV5" s="3"/>
     </row>
-    <row r="6" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>44</v>
       </c>
       <c r="U6" s="3"/>
@@ -2307,11 +2392,11 @@
       <c r="AU6" s="3"/>
       <c r="AV6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="1" t="s">
         <v>46</v>
       </c>
       <c r="U7" s="3"/>
@@ -2343,11 +2428,11 @@
       <c r="AU7" s="3"/>
       <c r="AV7" s="3"/>
     </row>
-    <row r="8" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="1" t="s">
         <v>48</v>
       </c>
       <c r="U8" s="3"/>
@@ -2379,11 +2464,11 @@
       <c r="AU8" s="3"/>
       <c r="AV8" s="3"/>
     </row>
-    <row r="9" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="1" t="s">
         <v>50</v>
       </c>
       <c r="U9" s="3"/>
@@ -2415,11 +2500,11 @@
       <c r="AU9" s="3"/>
       <c r="AV9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>52</v>
       </c>
       <c r="U10" s="3"/>
@@ -2451,11 +2536,11 @@
       <c r="AU10" s="3"/>
       <c r="AV10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>54</v>
       </c>
       <c r="U11" s="3"/>
@@ -2487,11 +2572,11 @@
       <c r="AU11" s="3"/>
       <c r="AV11" s="3"/>
     </row>
-    <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>56</v>
       </c>
       <c r="U12" s="3"/>
@@ -2523,11 +2608,11 @@
       <c r="AU12" s="3"/>
       <c r="AV12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>58</v>
       </c>
       <c r="U13" s="3"/>
@@ -2563,7 +2648,7 @@
       <c r="A14" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>60</v>
       </c>
       <c r="U14" s="3"/>
@@ -2595,11 +2680,11 @@
       <c r="AU14" s="3"/>
       <c r="AV14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+    <row r="15" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>62</v>
       </c>
       <c r="U15" s="3"/>
@@ -2631,14 +2716,13 @@
       <c r="AU15" s="3"/>
       <c r="AV15" s="3"/>
     </row>
-    <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+    <row r="16" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="4"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
@@ -2668,11 +2752,11 @@
       <c r="AU16" s="3"/>
       <c r="AV16" s="3"/>
     </row>
-    <row r="17" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+    <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>66</v>
       </c>
       <c r="U17" s="3"/>
@@ -2704,14 +2788,13 @@
       <c r="AU17" s="3"/>
       <c r="AV17" s="3"/>
     </row>
-    <row r="18" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="4"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -2745,11 +2828,9 @@
       <c r="A19" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -2779,15 +2860,13 @@
       <c r="AU19" s="3"/>
       <c r="AV19" s="3"/>
     </row>
-    <row r="20" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -2817,15 +2896,14 @@
       <c r="AU20" s="3"/>
       <c r="AV20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+    <row r="21" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
+      <c r="C21" s="5"/>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -2855,14 +2933,13 @@
       <c r="AU21" s="3"/>
       <c r="AV21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+    <row r="22" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="4"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -2892,14 +2969,14 @@
       <c r="AU22" s="3"/>
       <c r="AV22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C23" s="4"/>
+      <c r="C23" s="5"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
@@ -2929,13 +3006,15 @@
       <c r="AU23" s="3"/>
       <c r="AV23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>80</v>
       </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -2965,13 +3044,15 @@
       <c r="AU24" s="3"/>
       <c r="AV24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>82</v>
       </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
@@ -3001,15 +3082,15 @@
       <c r="AU25" s="3"/>
       <c r="AV25" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -3043,9 +3124,10 @@
       <c r="A27" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="5" t="s">
         <v>86</v>
       </c>
+      <c r="C27" s="5"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -3075,13 +3157,14 @@
       <c r="AU27" s="3"/>
       <c r="AV27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="5" t="s">
         <v>88</v>
       </c>
+      <c r="C28" s="5"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -3111,14 +3194,13 @@
       <c r="AU28" s="3"/>
       <c r="AV28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+    <row r="29" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C29" s="4"/>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
@@ -3148,14 +3230,13 @@
       <c r="AU29" s="3"/>
       <c r="AV29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="4"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -3185,14 +3266,15 @@
       <c r="AU30" s="3"/>
       <c r="AV30" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="D31" s="4"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
@@ -3222,14 +3304,13 @@
       <c r="AU31" s="3"/>
       <c r="AV31" s="3"/>
     </row>
-    <row r="32" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C32" s="4"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
@@ -3259,14 +3340,13 @@
       <c r="AU32" s="3"/>
       <c r="AV32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E33" s="4"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -3296,13 +3376,14 @@
       <c r="AU33" s="3"/>
       <c r="AV33" s="3"/>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+    <row r="34" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="5" t="s">
         <v>100</v>
       </c>
+      <c r="C34" s="5"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
@@ -3336,9 +3417,10 @@
       <c r="A35" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="5" t="s">
         <v>102</v>
       </c>
+      <c r="C35" s="5"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -3368,13 +3450,14 @@
       <c r="AU35" s="3"/>
       <c r="AV35" s="3"/>
     </row>
-    <row r="36" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="5" t="s">
         <v>104</v>
       </c>
+      <c r="D36" s="5"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
@@ -3404,13 +3487,14 @@
       <c r="AU36" s="3"/>
       <c r="AV36" s="3"/>
     </row>
-    <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="5" t="s">
         <v>106</v>
       </c>
+      <c r="C37" s="5"/>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
@@ -3440,13 +3524,14 @@
       <c r="AU37" s="3"/>
       <c r="AV37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="5" t="s">
         <v>108</v>
       </c>
+      <c r="E38" s="5"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
@@ -3476,15 +3561,13 @@
       <c r="AU38" s="3"/>
       <c r="AV38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
@@ -3514,15 +3597,13 @@
       <c r="AU39" s="3"/>
       <c r="AV39" s="3"/>
     </row>
-    <row r="40" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
@@ -3552,14 +3633,13 @@
       <c r="AU40" s="3"/>
       <c r="AV40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F41" s="4"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
@@ -3593,7 +3673,7 @@
       <c r="A42" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="5" t="s">
         <v>116</v>
       </c>
       <c r="U42" s="3"/>
@@ -3625,11 +3705,11 @@
       <c r="AU42" s="3"/>
       <c r="AV42" s="3"/>
     </row>
-    <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="5" t="s">
         <v>118</v>
       </c>
       <c r="U43" s="3"/>
@@ -3661,13 +3741,15 @@
       <c r="AU43" s="3"/>
       <c r="AV43" s="3"/>
     </row>
-    <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="5" t="s">
         <v>120</v>
       </c>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
@@ -3697,13 +3779,15 @@
       <c r="AU44" s="3"/>
       <c r="AV44" s="3"/>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="5" t="s">
         <v>122</v>
       </c>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
@@ -3733,13 +3817,14 @@
       <c r="AU45" s="3"/>
       <c r="AV45" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="5" t="s">
         <v>124</v>
       </c>
+      <c r="F46" s="5"/>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
@@ -3769,11 +3854,11 @@
       <c r="AU46" s="3"/>
       <c r="AV46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="5" t="s">
         <v>126</v>
       </c>
       <c r="U47" s="3"/>
@@ -3805,11 +3890,11 @@
       <c r="AU47" s="3"/>
       <c r="AV47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="5" t="s">
         <v>128</v>
       </c>
       <c r="U48" s="3"/>
@@ -3841,11 +3926,11 @@
       <c r="AU48" s="3"/>
       <c r="AV48" s="3"/>
     </row>
-    <row r="49" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="5" t="s">
         <v>130</v>
       </c>
       <c r="U49" s="3"/>
@@ -3877,31 +3962,13 @@
       <c r="AU49" s="3"/>
       <c r="AV49" s="3"/>
     </row>
-    <row r="50" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="s">
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="5"/>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="5"/>
-      <c r="R50" s="5"/>
-      <c r="S50" s="5"/>
-      <c r="T50" s="5"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
@@ -3931,31 +3998,13 @@
       <c r="AU50" s="3"/>
       <c r="AV50" s="3"/>
     </row>
-    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5" t="s">
+    <row r="51" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
         <v>133</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5"/>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="5"/>
-      <c r="R51" s="5"/>
-      <c r="S51" s="5"/>
-      <c r="T51" s="5"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
@@ -3985,31 +4034,13 @@
       <c r="AU51" s="3"/>
       <c r="AV51" s="3"/>
     </row>
-    <row r="52" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5" t="s">
+    <row r="52" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="5"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="5"/>
-      <c r="M52" s="5"/>
-      <c r="N52" s="5"/>
-      <c r="O52" s="5"/>
-      <c r="P52" s="5"/>
-      <c r="Q52" s="5"/>
-      <c r="R52" s="5"/>
-      <c r="S52" s="5"/>
-      <c r="T52" s="5"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
@@ -4039,11 +4070,11 @@
       <c r="AU52" s="3"/>
       <c r="AV52" s="3"/>
     </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="5" t="s">
         <v>138</v>
       </c>
       <c r="U53" s="3"/>
@@ -4075,11 +4106,11 @@
       <c r="AU53" s="3"/>
       <c r="AV53" s="3"/>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="5" t="s">
         <v>140</v>
       </c>
       <c r="U54" s="3"/>
@@ -4111,13 +4142,31 @@
       <c r="AU54" s="3"/>
       <c r="AV54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
+    <row r="55" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="5" t="s">
         <v>142</v>
       </c>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+      <c r="N55" s="6"/>
+      <c r="O55" s="6"/>
+      <c r="P55" s="6"/>
+      <c r="Q55" s="6"/>
+      <c r="R55" s="6"/>
+      <c r="S55" s="6"/>
+      <c r="T55" s="6"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
@@ -4147,13 +4196,31 @@
       <c r="AU55" s="3"/>
       <c r="AV55" s="3"/>
     </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
+    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="6" t="s">
         <v>144</v>
       </c>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="6"/>
+      <c r="N56" s="6"/>
+      <c r="O56" s="6"/>
+      <c r="P56" s="6"/>
+      <c r="Q56" s="6"/>
+      <c r="R56" s="6"/>
+      <c r="S56" s="6"/>
+      <c r="T56" s="6"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
@@ -4183,13 +4250,31 @@
       <c r="AU56" s="3"/>
       <c r="AV56" s="3"/>
     </row>
-    <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
+    <row r="57" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="5" t="s">
         <v>146</v>
       </c>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="6"/>
+      <c r="N57" s="6"/>
+      <c r="O57" s="6"/>
+      <c r="P57" s="6"/>
+      <c r="Q57" s="6"/>
+      <c r="R57" s="6"/>
+      <c r="S57" s="6"/>
+      <c r="T57" s="6"/>
       <c r="U57" s="3"/>
       <c r="V57" s="3"/>
       <c r="W57" s="3"/>
@@ -4219,11 +4304,11 @@
       <c r="AU57" s="3"/>
       <c r="AV57" s="3"/>
     </row>
-    <row r="58" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="1" t="s">
         <v>148</v>
       </c>
       <c r="U58" s="3"/>
@@ -4291,11 +4376,11 @@
       <c r="AU59" s="3"/>
       <c r="AV59" s="3"/>
     </row>
-    <row r="60" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="1" t="s">
         <v>152</v>
       </c>
       <c r="U60" s="3"/>
@@ -4363,11 +4448,11 @@
       <c r="AU61" s="3"/>
       <c r="AV61" s="3"/>
     </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="5" t="s">
         <v>156</v>
       </c>
       <c r="U62" s="3"/>
@@ -4399,11 +4484,11 @@
       <c r="AU62" s="3"/>
       <c r="AV62" s="3"/>
     </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="5" t="s">
         <v>158</v>
       </c>
       <c r="U63" s="3"/>
@@ -4435,11 +4520,11 @@
       <c r="AU63" s="3"/>
       <c r="AV63" s="3"/>
     </row>
-    <row r="64" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="1" t="s">
         <v>160</v>
       </c>
       <c r="U64" s="3"/>
@@ -4471,9 +4556,12 @@
       <c r="AU64" s="3"/>
       <c r="AV64" s="3"/>
     </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
         <v>161</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>162</v>
       </c>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
@@ -4504,12 +4592,12 @@
       <c r="AU65" s="3"/>
       <c r="AV65" s="3"/>
     </row>
-    <row r="66" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B66" s="4" t="s">
         <v>163</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="U66" s="3"/>
       <c r="V66" s="3"/>
@@ -4542,10 +4630,10 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
@@ -4576,12 +4664,12 @@
       <c r="AU67" s="3"/>
       <c r="AV67" s="3"/>
     </row>
-    <row r="68" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>146</v>
+        <v>167</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>168</v>
       </c>
       <c r="U68" s="3"/>
       <c r="V68" s="3"/>
@@ -4612,12 +4700,12 @@
       <c r="AU68" s="3"/>
       <c r="AV68" s="3"/>
     </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>170</v>
       </c>
       <c r="U69" s="3"/>
       <c r="V69" s="3"/>
@@ -4648,12 +4736,9 @@
       <c r="AU69" s="3"/>
       <c r="AV69" s="3"/>
     </row>
-    <row r="70" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="U70" s="3"/>
       <c r="V70" s="3"/>
@@ -4684,12 +4769,12 @@
       <c r="AU70" s="3"/>
       <c r="AV70" s="3"/>
     </row>
-    <row r="71" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B71" s="4" t="s">
         <v>172</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>173</v>
       </c>
       <c r="U71" s="3"/>
       <c r="V71" s="3"/>
@@ -4720,12 +4805,12 @@
       <c r="AU71" s="3"/>
       <c r="AV71" s="3"/>
     </row>
-    <row r="72" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B72" s="4" t="s">
         <v>174</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="U72" s="3"/>
       <c r="V72" s="3"/>
@@ -4758,10 +4843,10 @@
     </row>
     <row r="73" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B73" s="4" t="s">
         <v>176</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>156</v>
       </c>
       <c r="U73" s="3"/>
       <c r="V73" s="3"/>
@@ -4792,11 +4877,11 @@
       <c r="AU73" s="3"/>
       <c r="AV73" s="3"/>
     </row>
-    <row r="74" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="1" t="s">
         <v>178</v>
       </c>
       <c r="U74" s="3"/>
@@ -4828,11 +4913,11 @@
       <c r="AU74" s="3"/>
       <c r="AV74" s="3"/>
     </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="5" t="s">
         <v>180</v>
       </c>
       <c r="U75" s="3"/>
@@ -4864,11 +4949,11 @@
       <c r="AU75" s="3"/>
       <c r="AV75" s="3"/>
     </row>
-    <row r="76" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="5" t="s">
         <v>182</v>
       </c>
       <c r="U76" s="3"/>
@@ -4900,11 +4985,11 @@
       <c r="AU76" s="3"/>
       <c r="AV76" s="3"/>
     </row>
-    <row r="77" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="5" t="s">
         <v>184</v>
       </c>
       <c r="U77" s="3"/>
@@ -4936,11 +5021,11 @@
       <c r="AU77" s="3"/>
       <c r="AV77" s="3"/>
     </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="5" t="s">
         <v>186</v>
       </c>
       <c r="U78" s="3"/>
@@ -4972,11 +5057,11 @@
       <c r="AU78" s="3"/>
       <c r="AV78" s="3"/>
     </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="5" t="s">
         <v>188</v>
       </c>
       <c r="U79" s="3"/>
@@ -5044,11 +5129,11 @@
       <c r="AU80" s="3"/>
       <c r="AV80" s="3"/>
     </row>
-    <row r="81" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="5" t="s">
         <v>192</v>
       </c>
       <c r="U81" s="3"/>
@@ -5080,11 +5165,11 @@
       <c r="AU81" s="3"/>
       <c r="AV81" s="3"/>
     </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="5" t="s">
         <v>194</v>
       </c>
       <c r="U82" s="3"/>
@@ -5116,11 +5201,11 @@
       <c r="AU82" s="3"/>
       <c r="AV82" s="3"/>
     </row>
-    <row r="83" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="1" t="s">
         <v>196</v>
       </c>
       <c r="U83" s="3"/>
@@ -5188,11 +5273,11 @@
       <c r="AU84" s="3"/>
       <c r="AV84" s="3"/>
     </row>
-    <row r="85" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="1" t="s">
         <v>200</v>
       </c>
       <c r="U85" s="3"/>
@@ -5224,13 +5309,41 @@
       <c r="AU85" s="3"/>
       <c r="AV85" s="3"/>
     </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
         <v>201</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>202</v>
       </c>
+      <c r="U86" s="3"/>
+      <c r="V86" s="3"/>
+      <c r="W86" s="3"/>
+      <c r="X86" s="3"/>
+      <c r="Y86" s="3"/>
+      <c r="Z86" s="3"/>
+      <c r="AA86" s="3"/>
+      <c r="AB86" s="3"/>
+      <c r="AC86" s="3"/>
+      <c r="AD86" s="3"/>
+      <c r="AE86" s="3"/>
+      <c r="AF86" s="3"/>
+      <c r="AG86" s="3"/>
+      <c r="AH86" s="3"/>
+      <c r="AI86" s="3"/>
+      <c r="AJ86" s="3"/>
+      <c r="AK86" s="3"/>
+      <c r="AL86" s="3"/>
+      <c r="AM86" s="3"/>
+      <c r="AN86" s="3"/>
+      <c r="AO86" s="3"/>
+      <c r="AP86" s="3"/>
+      <c r="AQ86" s="3"/>
+      <c r="AR86" s="3"/>
+      <c r="AS86" s="3"/>
+      <c r="AT86" s="3"/>
+      <c r="AU86" s="3"/>
+      <c r="AV86" s="3"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
@@ -5239,217 +5352,293 @@
       <c r="B87" s="1" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U87" s="3"/>
+      <c r="V87" s="3"/>
+      <c r="W87" s="3"/>
+      <c r="X87" s="3"/>
+      <c r="Y87" s="3"/>
+      <c r="Z87" s="3"/>
+      <c r="AA87" s="3"/>
+      <c r="AB87" s="3"/>
+      <c r="AC87" s="3"/>
+      <c r="AD87" s="3"/>
+      <c r="AE87" s="3"/>
+      <c r="AF87" s="3"/>
+      <c r="AG87" s="3"/>
+      <c r="AH87" s="3"/>
+      <c r="AI87" s="3"/>
+      <c r="AJ87" s="3"/>
+      <c r="AK87" s="3"/>
+      <c r="AL87" s="3"/>
+      <c r="AM87" s="3"/>
+      <c r="AN87" s="3"/>
+      <c r="AO87" s="3"/>
+      <c r="AP87" s="3"/>
+      <c r="AQ87" s="3"/>
+      <c r="AR87" s="3"/>
+      <c r="AS87" s="3"/>
+      <c r="AT87" s="3"/>
+      <c r="AU87" s="3"/>
+      <c r="AV87" s="3"/>
+    </row>
+    <row r="88" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="89" customFormat="false" ht="335.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B88" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="U88" s="3"/>
+      <c r="V88" s="3"/>
+      <c r="W88" s="3"/>
+      <c r="X88" s="3"/>
+      <c r="Y88" s="3"/>
+      <c r="Z88" s="3"/>
+      <c r="AA88" s="3"/>
+      <c r="AB88" s="3"/>
+      <c r="AC88" s="3"/>
+      <c r="AD88" s="3"/>
+      <c r="AE88" s="3"/>
+      <c r="AF88" s="3"/>
+      <c r="AG88" s="3"/>
+      <c r="AH88" s="3"/>
+      <c r="AI88" s="3"/>
+      <c r="AJ88" s="3"/>
+      <c r="AK88" s="3"/>
+      <c r="AL88" s="3"/>
+      <c r="AM88" s="3"/>
+      <c r="AN88" s="3"/>
+      <c r="AO88" s="3"/>
+      <c r="AP88" s="3"/>
+      <c r="AQ88" s="3"/>
+      <c r="AR88" s="3"/>
+      <c r="AS88" s="3"/>
+      <c r="AT88" s="3"/>
+      <c r="AU88" s="3"/>
+      <c r="AV88" s="3"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B89" s="4" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="90" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="U89" s="3"/>
+      <c r="V89" s="3"/>
+      <c r="W89" s="3"/>
+      <c r="X89" s="3"/>
+      <c r="Y89" s="3"/>
+      <c r="Z89" s="3"/>
+      <c r="AA89" s="3"/>
+      <c r="AB89" s="3"/>
+      <c r="AC89" s="3"/>
+      <c r="AD89" s="3"/>
+      <c r="AE89" s="3"/>
+      <c r="AF89" s="3"/>
+      <c r="AG89" s="3"/>
+      <c r="AH89" s="3"/>
+      <c r="AI89" s="3"/>
+      <c r="AJ89" s="3"/>
+      <c r="AK89" s="3"/>
+      <c r="AL89" s="3"/>
+      <c r="AM89" s="3"/>
+      <c r="AN89" s="3"/>
+      <c r="AO89" s="3"/>
+      <c r="AP89" s="3"/>
+      <c r="AQ89" s="3"/>
+      <c r="AR89" s="3"/>
+      <c r="AS89" s="3"/>
+      <c r="AT89" s="3"/>
+      <c r="AU89" s="3"/>
+      <c r="AV89" s="3"/>
+    </row>
+    <row r="90" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B90" s="4" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="91" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B90" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
+      <c r="AR90" s="3"/>
+      <c r="AS90" s="3"/>
+      <c r="AT90" s="3"/>
+      <c r="AU90" s="3"/>
+      <c r="AV90" s="3"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B91" s="4" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="92" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="5" t="s">
+      <c r="B91" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B92" s="4" t="s">
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C92" s="5"/>
-      <c r="D92" s="5"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="5"/>
-      <c r="G92" s="5"/>
-      <c r="H92" s="5"/>
-      <c r="I92" s="5"/>
-      <c r="J92" s="5"/>
-      <c r="K92" s="5"/>
-      <c r="L92" s="5"/>
-      <c r="M92" s="5"/>
-      <c r="N92" s="5"/>
-      <c r="O92" s="5"/>
-      <c r="P92" s="5"/>
-      <c r="Q92" s="5"/>
-      <c r="R92" s="5"/>
-      <c r="S92" s="5"/>
-      <c r="T92" s="5"/>
-    </row>
-    <row r="93" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B92" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B93" s="4" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="335.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="5" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" s="5" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="5" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
+    <row r="97" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" s="5" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="98" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C97" s="6"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="6"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="6"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="6"/>
+      <c r="J97" s="6"/>
+      <c r="K97" s="6"/>
+      <c r="L97" s="6"/>
+      <c r="M97" s="6"/>
+      <c r="N97" s="6"/>
+      <c r="O97" s="6"/>
+      <c r="P97" s="6"/>
+      <c r="Q97" s="6"/>
+      <c r="R97" s="6"/>
+      <c r="S97" s="6"/>
+      <c r="T97" s="6"/>
+    </row>
+    <row r="98" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="5" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="5" t="s">
+    <row r="99" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="C99" s="5"/>
-      <c r="D99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
-      <c r="G99" s="5"/>
-      <c r="H99" s="5"/>
-      <c r="I99" s="5"/>
-      <c r="J99" s="5"/>
-      <c r="K99" s="5"/>
-      <c r="L99" s="5"/>
-      <c r="M99" s="5"/>
-      <c r="N99" s="5"/>
-      <c r="O99" s="5"/>
-      <c r="P99" s="5"/>
-      <c r="Q99" s="5"/>
-      <c r="R99" s="5"/>
-      <c r="S99" s="5"/>
-      <c r="T99" s="5"/>
-    </row>
-    <row r="100" customFormat="false" ht="252.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="6" t="s">
+    </row>
+    <row r="100" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="4"/>
-      <c r="I100" s="4"/>
-      <c r="J100" s="4"/>
-      <c r="K100" s="4"/>
-      <c r="L100" s="4"/>
-      <c r="M100" s="4"/>
-      <c r="N100" s="4"/>
-      <c r="O100" s="4"/>
-      <c r="P100" s="4"/>
-      <c r="Q100" s="4"/>
-      <c r="R100" s="4"/>
-      <c r="S100" s="4"/>
-      <c r="T100" s="4"/>
     </row>
     <row r="101" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="5" t="s">
+      <c r="A101" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B101" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="C101" s="5"/>
-      <c r="D101" s="5"/>
-      <c r="E101" s="5"/>
-      <c r="F101" s="5"/>
-      <c r="G101" s="5"/>
-      <c r="H101" s="5"/>
-      <c r="I101" s="5"/>
-      <c r="J101" s="5"/>
-      <c r="K101" s="5"/>
-      <c r="L101" s="5"/>
-      <c r="M101" s="5"/>
-      <c r="N101" s="5"/>
-      <c r="O101" s="5"/>
-      <c r="P101" s="5"/>
-      <c r="Q101" s="5"/>
-      <c r="R101" s="5"/>
-      <c r="S101" s="5"/>
-      <c r="T101" s="5"/>
     </row>
     <row r="102" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="5" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B103" s="5" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1" t="s">
+    <row r="104" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B104" s="5" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="105" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="5" t="s">
+      <c r="C104" s="6"/>
+      <c r="D104" s="6"/>
+      <c r="E104" s="6"/>
+      <c r="F104" s="6"/>
+      <c r="G104" s="6"/>
+      <c r="H104" s="6"/>
+      <c r="I104" s="6"/>
+      <c r="J104" s="6"/>
+      <c r="K104" s="6"/>
+      <c r="L104" s="6"/>
+      <c r="M104" s="6"/>
+      <c r="N104" s="6"/>
+      <c r="O104" s="6"/>
+      <c r="P104" s="6"/>
+      <c r="Q104" s="6"/>
+      <c r="R104" s="6"/>
+      <c r="S104" s="6"/>
+      <c r="T104" s="6"/>
+    </row>
+    <row r="105" customFormat="false" ht="252.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B105" s="5" t="s">
         <v>239</v>
       </c>
       <c r="C105" s="5"/>
@@ -5471,500 +5660,576 @@
       <c r="S105" s="5"/>
       <c r="T105" s="5"/>
     </row>
-    <row r="106" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="5" t="s">
+    <row r="106" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B106" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="C106" s="5"/>
-      <c r="D106" s="5"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
-      <c r="G106" s="5"/>
-      <c r="H106" s="5"/>
-      <c r="I106" s="5"/>
-      <c r="J106" s="5"/>
-      <c r="K106" s="5"/>
-      <c r="L106" s="5"/>
-      <c r="M106" s="5"/>
-      <c r="N106" s="5"/>
-      <c r="O106" s="5"/>
-      <c r="P106" s="5"/>
-      <c r="Q106" s="5"/>
-      <c r="R106" s="5"/>
-      <c r="S106" s="5"/>
-      <c r="T106" s="5"/>
-    </row>
-    <row r="107" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C106" s="6"/>
+      <c r="D106" s="6"/>
+      <c r="E106" s="6"/>
+      <c r="F106" s="6"/>
+      <c r="G106" s="6"/>
+      <c r="H106" s="6"/>
+      <c r="I106" s="6"/>
+      <c r="J106" s="6"/>
+      <c r="K106" s="6"/>
+      <c r="L106" s="6"/>
+      <c r="M106" s="6"/>
+      <c r="N106" s="6"/>
+      <c r="O106" s="6"/>
+      <c r="P106" s="6"/>
+      <c r="Q106" s="6"/>
+      <c r="R106" s="6"/>
+      <c r="S106" s="6"/>
+      <c r="T106" s="6"/>
+    </row>
+    <row r="107" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B107" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="C107" s="4" t="s">
+    </row>
+    <row r="108" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D107" s="4" t="s">
+      <c r="B108" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="E107" s="4" t="s">
+    </row>
+    <row r="109" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="F107" s="4" t="s">
+      <c r="B109" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="G107" s="4" t="s">
+    </row>
+    <row r="110" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="H107" s="4" t="s">
+      <c r="B110" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="I107" s="4" t="s">
+      <c r="C110" s="6"/>
+      <c r="D110" s="6"/>
+      <c r="E110" s="6"/>
+      <c r="F110" s="6"/>
+      <c r="G110" s="6"/>
+      <c r="H110" s="6"/>
+      <c r="I110" s="6"/>
+      <c r="J110" s="6"/>
+      <c r="K110" s="6"/>
+      <c r="L110" s="6"/>
+      <c r="M110" s="6"/>
+      <c r="N110" s="6"/>
+      <c r="O110" s="6"/>
+      <c r="P110" s="6"/>
+      <c r="Q110" s="6"/>
+      <c r="R110" s="6"/>
+      <c r="S110" s="6"/>
+      <c r="T110" s="6"/>
+    </row>
+    <row r="111" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="J107" s="4" t="s">
+      <c r="B111" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="K107" s="4" t="s">
+      <c r="C111" s="6"/>
+      <c r="D111" s="6"/>
+      <c r="E111" s="6"/>
+      <c r="F111" s="6"/>
+      <c r="G111" s="6"/>
+      <c r="H111" s="6"/>
+      <c r="I111" s="6"/>
+      <c r="J111" s="6"/>
+      <c r="K111" s="6"/>
+      <c r="L111" s="6"/>
+      <c r="M111" s="6"/>
+      <c r="N111" s="6"/>
+      <c r="O111" s="6"/>
+      <c r="P111" s="6"/>
+      <c r="Q111" s="6"/>
+      <c r="R111" s="6"/>
+      <c r="S111" s="6"/>
+      <c r="T111" s="6"/>
+    </row>
+    <row r="112" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="L107" s="4" t="s">
+      <c r="B112" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="M107" s="4" t="s">
+      <c r="C112" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="N107" s="4" t="s">
+      <c r="D112" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="O107" s="4" t="s">
+      <c r="E112" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="P107" s="4" t="s">
+      <c r="F112" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="Q107" s="4" t="s">
+      <c r="G112" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="R107" s="4" t="s">
+      <c r="H112" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="S107" s="4" t="s">
+      <c r="I112" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="T107" s="4" t="s">
+      <c r="J112" s="5" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="108" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="s">
+      <c r="K112" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="L112" s="5" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="109" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1" t="s">
+      <c r="M112" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="N112" s="5" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="110" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="5" t="s">
+      <c r="O112" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="P112" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="C110" s="5"/>
-      <c r="D110" s="5"/>
-      <c r="E110" s="5"/>
-      <c r="F110" s="5"/>
-      <c r="G110" s="5"/>
-      <c r="H110" s="5"/>
-      <c r="I110" s="5"/>
-      <c r="J110" s="5"/>
-      <c r="K110" s="5"/>
-      <c r="L110" s="5"/>
-      <c r="M110" s="5"/>
-      <c r="N110" s="5"/>
-      <c r="O110" s="5"/>
-      <c r="P110" s="5"/>
-      <c r="Q110" s="5"/>
-      <c r="R110" s="5"/>
-      <c r="S110" s="5"/>
-      <c r="T110" s="5"/>
-    </row>
-    <row r="111" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="1" t="s">
+      <c r="Q112" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="B111" s="7" t="s">
+      <c r="R112" s="5" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="112" customFormat="false" ht="54.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1" t="s">
+      <c r="S112" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="B112" s="7" t="s">
+      <c r="T112" s="5" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="B113" s="5" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B114" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="I114" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="J114" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="K114" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="L114" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="M114" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="N114" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="O114" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="P114" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q114" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="R114" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="S114" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="T114" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1" t="s">
+    </row>
+    <row r="115" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="B115" s="5" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="116" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C115" s="6"/>
+      <c r="D115" s="6"/>
+      <c r="E115" s="6"/>
+      <c r="F115" s="6"/>
+      <c r="G115" s="6"/>
+      <c r="H115" s="6"/>
+      <c r="I115" s="6"/>
+      <c r="J115" s="6"/>
+      <c r="K115" s="6"/>
+      <c r="L115" s="6"/>
+      <c r="M115" s="6"/>
+      <c r="N115" s="6"/>
+      <c r="O115" s="6"/>
+      <c r="P115" s="6"/>
+      <c r="Q115" s="6"/>
+      <c r="R115" s="6"/>
+      <c r="S115" s="6"/>
+      <c r="T115" s="6"/>
+    </row>
+    <row r="116" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="7" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="54.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="B117" s="7" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B118" s="5" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="B119" s="1" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="120" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C119" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="M119" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="N119" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="O119" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="P119" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q119" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="R119" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="S119" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="T119" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B120" s="4" t="s">
+      <c r="B120" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="AX120" s="3"/>
-      <c r="AY120" s="3"/>
-      <c r="AZ120" s="3"/>
-      <c r="BA120" s="3"/>
-      <c r="BB120" s="3"/>
-      <c r="BC120" s="3"/>
-      <c r="BD120" s="3"/>
-      <c r="BE120" s="3"/>
-      <c r="BF120" s="3"/>
-      <c r="BG120" s="3"/>
-      <c r="BH120" s="3"/>
-      <c r="BI120" s="3"/>
-      <c r="BJ120" s="3"/>
-      <c r="BK120" s="3"/>
-      <c r="BL120" s="3"/>
-      <c r="BM120" s="3"/>
-      <c r="BN120" s="3"/>
-      <c r="BO120" s="3"/>
-      <c r="BP120" s="3"/>
-      <c r="BQ120" s="3"/>
-      <c r="BR120" s="3"/>
-      <c r="BS120" s="3"/>
-      <c r="BT120" s="3"/>
-      <c r="BU120" s="3"/>
-      <c r="BV120" s="3"/>
-      <c r="BW120" s="3"/>
-      <c r="BX120" s="3"/>
-      <c r="BY120" s="3"/>
-      <c r="BZ120" s="3"/>
-      <c r="CA120" s="3"/>
-      <c r="CB120" s="3"/>
-      <c r="CC120" s="3"/>
-      <c r="CD120" s="3"/>
-      <c r="CE120" s="3"/>
-      <c r="CF120" s="3"/>
-      <c r="CG120" s="3"/>
-      <c r="CH120" s="3"/>
-      <c r="CI120" s="3"/>
-      <c r="CJ120" s="3"/>
-    </row>
-    <row r="121" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="121" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="B121" s="5" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B122" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="AX122" s="3"/>
-      <c r="AY122" s="3"/>
-      <c r="AZ122" s="3"/>
-      <c r="BA122" s="3"/>
-      <c r="BB122" s="3"/>
-      <c r="BC122" s="3"/>
-      <c r="BD122" s="3"/>
-      <c r="BE122" s="3"/>
-      <c r="BF122" s="3"/>
-      <c r="BG122" s="3"/>
-      <c r="BH122" s="3"/>
-      <c r="BI122" s="3"/>
-      <c r="BJ122" s="3"/>
-      <c r="BK122" s="3"/>
-      <c r="BL122" s="3"/>
-      <c r="BM122" s="3"/>
-      <c r="BN122" s="3"/>
-      <c r="BO122" s="3"/>
-      <c r="BP122" s="3"/>
-      <c r="BQ122" s="3"/>
-      <c r="BR122" s="3"/>
-      <c r="BS122" s="3"/>
-      <c r="BT122" s="3"/>
-      <c r="BU122" s="3"/>
-      <c r="BV122" s="3"/>
-      <c r="BW122" s="3"/>
-      <c r="BX122" s="3"/>
-      <c r="BY122" s="3"/>
-      <c r="BZ122" s="3"/>
-      <c r="CA122" s="3"/>
-      <c r="CB122" s="3"/>
-      <c r="CC122" s="3"/>
-      <c r="CD122" s="3"/>
-      <c r="CE122" s="3"/>
-      <c r="CF122" s="3"/>
-      <c r="CG122" s="3"/>
-      <c r="CH122" s="3"/>
-      <c r="CI122" s="3"/>
-      <c r="CJ122" s="3"/>
-    </row>
-    <row r="123" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B123" s="4" t="s">
+      <c r="B123" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="AX123" s="3"/>
-      <c r="AY123" s="3"/>
-      <c r="AZ123" s="3"/>
-      <c r="BA123" s="3"/>
-      <c r="BB123" s="3"/>
-      <c r="BC123" s="3"/>
-      <c r="BD123" s="3"/>
-      <c r="BE123" s="3"/>
-      <c r="BF123" s="3"/>
-      <c r="BG123" s="3"/>
-      <c r="BH123" s="3"/>
-      <c r="BI123" s="3"/>
-      <c r="BJ123" s="3"/>
-      <c r="BK123" s="3"/>
-      <c r="BL123" s="3"/>
-      <c r="BM123" s="3"/>
-      <c r="BN123" s="3"/>
-      <c r="BO123" s="3"/>
-      <c r="BP123" s="3"/>
-      <c r="BQ123" s="3"/>
-      <c r="BR123" s="3"/>
-      <c r="BS123" s="3"/>
-      <c r="BT123" s="3"/>
-      <c r="BU123" s="3"/>
-      <c r="BV123" s="3"/>
-      <c r="BW123" s="3"/>
-      <c r="BX123" s="3"/>
-      <c r="BY123" s="3"/>
-      <c r="BZ123" s="3"/>
-      <c r="CA123" s="3"/>
-      <c r="CB123" s="3"/>
-      <c r="CC123" s="3"/>
-      <c r="CD123" s="3"/>
-      <c r="CE123" s="3"/>
-      <c r="CF123" s="3"/>
-      <c r="CG123" s="3"/>
-      <c r="CH123" s="3"/>
-      <c r="CI123" s="3"/>
-      <c r="CJ123" s="3"/>
-    </row>
-    <row r="124" s="3" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="124" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B124" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
-      <c r="E124" s="1"/>
-      <c r="F124" s="1"/>
-      <c r="G124" s="1"/>
-      <c r="H124" s="1"/>
-      <c r="I124" s="1"/>
-      <c r="J124" s="1"/>
-      <c r="K124" s="1"/>
-      <c r="L124" s="1"/>
-      <c r="M124" s="1"/>
-      <c r="N124" s="1"/>
-      <c r="O124" s="1"/>
-      <c r="P124" s="1"/>
-      <c r="Q124" s="1"/>
-      <c r="R124" s="1"/>
-      <c r="S124" s="1"/>
-      <c r="T124" s="1"/>
-      <c r="U124" s="1"/>
-      <c r="V124" s="1"/>
-      <c r="W124" s="1"/>
-      <c r="X124" s="1"/>
-      <c r="Y124" s="1"/>
-      <c r="Z124" s="1"/>
-      <c r="AA124" s="1"/>
-      <c r="AB124" s="1"/>
-      <c r="AC124" s="1"/>
-      <c r="AD124" s="1"/>
-      <c r="AE124" s="1"/>
-      <c r="AF124" s="1"/>
-      <c r="AG124" s="1"/>
-      <c r="AH124" s="1"/>
-      <c r="AI124" s="1"/>
-      <c r="AJ124" s="1"/>
-      <c r="AK124" s="1"/>
-      <c r="AL124" s="1"/>
-      <c r="AM124" s="1"/>
-      <c r="AN124" s="1"/>
-      <c r="AO124" s="1"/>
-      <c r="AP124" s="1"/>
-      <c r="AQ124" s="1"/>
-      <c r="AR124" s="1"/>
-      <c r="AS124" s="1"/>
-      <c r="AT124" s="1"/>
-      <c r="AU124" s="1"/>
-      <c r="AV124" s="1"/>
-      <c r="AW124" s="1"/>
-    </row>
-    <row r="125" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B124" s="5" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="B125" s="4" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="126" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B125" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="AX125" s="3"/>
+      <c r="AY125" s="3"/>
+      <c r="AZ125" s="3"/>
+      <c r="BA125" s="3"/>
+      <c r="BB125" s="3"/>
+      <c r="BC125" s="3"/>
+      <c r="BD125" s="3"/>
+      <c r="BE125" s="3"/>
+      <c r="BF125" s="3"/>
+      <c r="BG125" s="3"/>
+      <c r="BH125" s="3"/>
+      <c r="BI125" s="3"/>
+      <c r="BJ125" s="3"/>
+      <c r="BK125" s="3"/>
+      <c r="BL125" s="3"/>
+      <c r="BM125" s="3"/>
+      <c r="BN125" s="3"/>
+      <c r="BO125" s="3"/>
+      <c r="BP125" s="3"/>
+      <c r="BQ125" s="3"/>
+      <c r="BR125" s="3"/>
+      <c r="BS125" s="3"/>
+      <c r="BT125" s="3"/>
+      <c r="BU125" s="3"/>
+      <c r="BV125" s="3"/>
+      <c r="BW125" s="3"/>
+      <c r="BX125" s="3"/>
+      <c r="BY125" s="3"/>
+      <c r="BZ125" s="3"/>
+      <c r="CA125" s="3"/>
+      <c r="CB125" s="3"/>
+      <c r="CC125" s="3"/>
+      <c r="CD125" s="3"/>
+      <c r="CE125" s="3"/>
+      <c r="CF125" s="3"/>
+      <c r="CG125" s="3"/>
+      <c r="CH125" s="3"/>
+      <c r="CI125" s="3"/>
+      <c r="CJ125" s="3"/>
+    </row>
+    <row r="126" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B126" s="8" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="127" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B126" s="5" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B127" s="8" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="128" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B127" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="AX127" s="3"/>
+      <c r="AY127" s="3"/>
+      <c r="AZ127" s="3"/>
+      <c r="BA127" s="3"/>
+      <c r="BB127" s="3"/>
+      <c r="BC127" s="3"/>
+      <c r="BD127" s="3"/>
+      <c r="BE127" s="3"/>
+      <c r="BF127" s="3"/>
+      <c r="BG127" s="3"/>
+      <c r="BH127" s="3"/>
+      <c r="BI127" s="3"/>
+      <c r="BJ127" s="3"/>
+      <c r="BK127" s="3"/>
+      <c r="BL127" s="3"/>
+      <c r="BM127" s="3"/>
+      <c r="BN127" s="3"/>
+      <c r="BO127" s="3"/>
+      <c r="BP127" s="3"/>
+      <c r="BQ127" s="3"/>
+      <c r="BR127" s="3"/>
+      <c r="BS127" s="3"/>
+      <c r="BT127" s="3"/>
+      <c r="BU127" s="3"/>
+      <c r="BV127" s="3"/>
+      <c r="BW127" s="3"/>
+      <c r="BX127" s="3"/>
+      <c r="BY127" s="3"/>
+      <c r="BZ127" s="3"/>
+      <c r="CA127" s="3"/>
+      <c r="CB127" s="3"/>
+      <c r="CC127" s="3"/>
+      <c r="CD127" s="3"/>
+      <c r="CE127" s="3"/>
+      <c r="CF127" s="3"/>
+      <c r="CG127" s="3"/>
+      <c r="CH127" s="3"/>
+      <c r="CI127" s="3"/>
+      <c r="CJ127" s="3"/>
+    </row>
+    <row r="128" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B128" s="4" t="s">
         <v>302</v>
       </c>
+      <c r="B128" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="AX128" s="3"/>
+      <c r="AY128" s="3"/>
+      <c r="AZ128" s="3"/>
+      <c r="BA128" s="3"/>
+      <c r="BB128" s="3"/>
+      <c r="BC128" s="3"/>
+      <c r="BD128" s="3"/>
+      <c r="BE128" s="3"/>
+      <c r="BF128" s="3"/>
+      <c r="BG128" s="3"/>
+      <c r="BH128" s="3"/>
+      <c r="BI128" s="3"/>
+      <c r="BJ128" s="3"/>
+      <c r="BK128" s="3"/>
+      <c r="BL128" s="3"/>
+      <c r="BM128" s="3"/>
+      <c r="BN128" s="3"/>
+      <c r="BO128" s="3"/>
+      <c r="BP128" s="3"/>
+      <c r="BQ128" s="3"/>
+      <c r="BR128" s="3"/>
+      <c r="BS128" s="3"/>
+      <c r="BT128" s="3"/>
+      <c r="BU128" s="3"/>
+      <c r="BV128" s="3"/>
+      <c r="BW128" s="3"/>
+      <c r="BX128" s="3"/>
+      <c r="BY128" s="3"/>
+      <c r="BZ128" s="3"/>
+      <c r="CA128" s="3"/>
+      <c r="CB128" s="3"/>
+      <c r="CC128" s="3"/>
+      <c r="CD128" s="3"/>
+      <c r="CE128" s="3"/>
+      <c r="CF128" s="3"/>
+      <c r="CG128" s="3"/>
+      <c r="CH128" s="3"/>
+      <c r="CI128" s="3"/>
+      <c r="CJ128" s="3"/>
+    </row>
+    <row r="129" s="3" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+      <c r="J129" s="1"/>
+      <c r="K129" s="1"/>
+      <c r="L129" s="1"/>
+      <c r="M129" s="1"/>
+      <c r="N129" s="1"/>
+      <c r="O129" s="1"/>
+      <c r="P129" s="1"/>
+      <c r="Q129" s="1"/>
+      <c r="R129" s="1"/>
+      <c r="S129" s="1"/>
+      <c r="T129" s="1"/>
+      <c r="U129" s="1"/>
+      <c r="V129" s="1"/>
+      <c r="W129" s="1"/>
+      <c r="X129" s="1"/>
+      <c r="Y129" s="1"/>
+      <c r="Z129" s="1"/>
+      <c r="AA129" s="1"/>
+      <c r="AB129" s="1"/>
+      <c r="AC129" s="1"/>
+      <c r="AD129" s="1"/>
+      <c r="AE129" s="1"/>
+      <c r="AF129" s="1"/>
+      <c r="AG129" s="1"/>
+      <c r="AH129" s="1"/>
+      <c r="AI129" s="1"/>
+      <c r="AJ129" s="1"/>
+      <c r="AK129" s="1"/>
+      <c r="AL129" s="1"/>
+      <c r="AM129" s="1"/>
+      <c r="AN129" s="1"/>
+      <c r="AO129" s="1"/>
+      <c r="AP129" s="1"/>
+      <c r="AQ129" s="1"/>
+      <c r="AR129" s="1"/>
+      <c r="AS129" s="1"/>
+      <c r="AT129" s="1"/>
+      <c r="AU129" s="1"/>
+      <c r="AV129" s="1"/>
+      <c r="AW129" s="1"/>
+    </row>
+    <row r="130" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>312</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:T127"/>
+  <autoFilter ref="A2:T132"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/JP (Exclude Game)/Data/chara_talk.xlsx
+++ b/JP (Exclude Game)/Data/chara_talk.xlsx
@@ -11,7 +11,7 @@
     <sheet name="1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$132</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$134</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="317">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -140,6 +140,37 @@
   </si>
   <si>
     <t xml:space="preserve">夢人</t>
+  </si>
+  <si>
+    <t xml:space="preserve">play_baby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ママー！
+ママぁ！
+バブ！
+バブバブ！
+オギャー！
+ママどこ？
+ママなの？
+…ママ？
+…ママぁ！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">play_mama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">よしよし。
+ママ{だよ}～！
+いい子いい子。
+はいはい。
+ママ{だよ}。
+うん、うん。
+大丈夫、大丈夫。
+ぎゅーっ！
+ぎゅっ。
+ママはここにいる{よ}。
+ほら、甘えていい{よ}。
+受け止めてあげる{のだ}。</t>
   </si>
   <si>
     <t xml:space="preserve">kiss</t>
@@ -1798,12 +1829,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1858,9 +1889,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>2080440</xdr:colOff>
+      <xdr:colOff>2080080</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>124560</xdr:rowOff>
+      <xdr:rowOff>124200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1870,7 +1901,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="50981040" cy="124560"/>
+          <a:ext cx="50980680" cy="124200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1903,9 +1934,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>518040</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>316800</xdr:rowOff>
+      <xdr:colOff>517680</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>316440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1915,7 +1946,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="55189080" cy="42680880"/>
+          <a:ext cx="55188720" cy="45504360"/>
         </a:xfrm>
         <a:solidFill>
           <a:srgbClr val="ffffff"/>
@@ -2050,7 +2081,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CJ133"/>
+  <dimension ref="A1:CJ135"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.04"/>
@@ -2284,7 +2315,7 @@
       <c r="AU3" s="3"/>
       <c r="AV3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>39</v>
       </c>
@@ -2320,11 +2351,11 @@
       <c r="AU4" s="3"/>
       <c r="AV4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>42</v>
       </c>
       <c r="U5" s="3"/>
@@ -2356,7 +2387,7 @@
       <c r="AU5" s="3"/>
       <c r="AV5" s="3"/>
     </row>
-    <row r="6" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>43</v>
       </c>
@@ -2392,11 +2423,11 @@
       <c r="AU6" s="3"/>
       <c r="AV6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="4" t="s">
         <v>46</v>
       </c>
       <c r="U7" s="3"/>
@@ -2428,11 +2459,11 @@
       <c r="AU7" s="3"/>
       <c r="AV7" s="3"/>
     </row>
-    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="4" t="s">
         <v>48</v>
       </c>
       <c r="U8" s="3"/>
@@ -2500,11 +2531,11 @@
       <c r="AU9" s="3"/>
       <c r="AV9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="1" t="s">
         <v>52</v>
       </c>
       <c r="U10" s="3"/>
@@ -2536,11 +2567,11 @@
       <c r="AU10" s="3"/>
       <c r="AV10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="1" t="s">
         <v>54</v>
       </c>
       <c r="U11" s="3"/>
@@ -2572,11 +2603,11 @@
       <c r="AU11" s="3"/>
       <c r="AV11" s="3"/>
     </row>
-    <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>56</v>
       </c>
       <c r="U12" s="3"/>
@@ -2608,11 +2639,11 @@
       <c r="AU12" s="3"/>
       <c r="AV12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>58</v>
       </c>
       <c r="U13" s="3"/>
@@ -2644,11 +2675,11 @@
       <c r="AU13" s="3"/>
       <c r="AV13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>60</v>
       </c>
       <c r="U14" s="3"/>
@@ -2680,11 +2711,11 @@
       <c r="AU14" s="3"/>
       <c r="AV14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>62</v>
       </c>
       <c r="U15" s="3"/>
@@ -2716,11 +2747,11 @@
       <c r="AU15" s="3"/>
       <c r="AV15" s="3"/>
     </row>
-    <row r="16" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>64</v>
       </c>
       <c r="U16" s="3"/>
@@ -2752,11 +2783,11 @@
       <c r="AU16" s="3"/>
       <c r="AV16" s="3"/>
     </row>
-    <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>66</v>
       </c>
       <c r="U17" s="3"/>
@@ -2788,11 +2819,11 @@
       <c r="AU17" s="3"/>
       <c r="AV17" s="3"/>
     </row>
-    <row r="18" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>68</v>
       </c>
       <c r="U18" s="3"/>
@@ -2824,11 +2855,11 @@
       <c r="AU18" s="3"/>
       <c r="AV18" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>70</v>
       </c>
       <c r="U19" s="3"/>
@@ -2860,11 +2891,11 @@
       <c r="AU19" s="3"/>
       <c r="AV19" s="3"/>
     </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
+    <row r="20" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>72</v>
       </c>
       <c r="U20" s="3"/>
@@ -2896,14 +2927,13 @@
       <c r="AU20" s="3"/>
       <c r="AV20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
+    <row r="21" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="5"/>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -2933,11 +2963,11 @@
       <c r="AU21" s="3"/>
       <c r="AV21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>76</v>
       </c>
       <c r="U22" s="3"/>
@@ -2969,14 +2999,14 @@
       <c r="AU22" s="3"/>
       <c r="AV22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+    <row r="23" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C23" s="5"/>
+      <c r="C23" s="4"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
@@ -3007,14 +3037,12 @@
       <c r="AV23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -3044,15 +3072,14 @@
       <c r="AU24" s="3"/>
       <c r="AV24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="4"/>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
@@ -3082,15 +3109,15 @@
       <c r="AU25" s="3"/>
       <c r="AV25" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -3120,14 +3147,15 @@
       <c r="AU26" s="3"/>
       <c r="AV26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C27" s="5"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -3157,14 +3185,15 @@
       <c r="AU27" s="3"/>
       <c r="AV27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="5"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -3194,13 +3223,14 @@
       <c r="AU28" s="3"/>
       <c r="AV28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>90</v>
       </c>
+      <c r="C29" s="4"/>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
@@ -3230,13 +3260,14 @@
       <c r="AU29" s="3"/>
       <c r="AV29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="4" t="s">
         <v>92</v>
       </c>
+      <c r="C30" s="4"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -3266,15 +3297,13 @@
       <c r="AU30" s="3"/>
       <c r="AV30" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
@@ -3304,11 +3333,11 @@
       <c r="AU31" s="3"/>
       <c r="AV31" s="3"/>
     </row>
-    <row r="32" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="4" t="s">
         <v>96</v>
       </c>
       <c r="U32" s="3"/>
@@ -3340,13 +3369,15 @@
       <c r="AU32" s="3"/>
       <c r="AV32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="4" t="s">
         <v>98</v>
       </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -3376,14 +3407,13 @@
       <c r="AU33" s="3"/>
       <c r="AV33" s="3"/>
     </row>
-    <row r="34" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
+    <row r="34" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C34" s="5"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
@@ -3413,14 +3443,13 @@
       <c r="AU34" s="3"/>
       <c r="AV34" s="3"/>
     </row>
-    <row r="35" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C35" s="5"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -3450,14 +3479,14 @@
       <c r="AU35" s="3"/>
       <c r="AV35" s="3"/>
     </row>
-    <row r="36" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+    <row r="36" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D36" s="5"/>
+      <c r="C36" s="4"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
@@ -3487,14 +3516,14 @@
       <c r="AU36" s="3"/>
       <c r="AV36" s="3"/>
     </row>
-    <row r="37" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C37" s="5"/>
+      <c r="C37" s="4"/>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
@@ -3524,14 +3553,14 @@
       <c r="AU37" s="3"/>
       <c r="AV37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E38" s="5"/>
+      <c r="D38" s="4"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
@@ -3561,13 +3590,14 @@
       <c r="AU38" s="3"/>
       <c r="AV38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="4" t="s">
         <v>110</v>
       </c>
+      <c r="C39" s="4"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
@@ -3597,13 +3627,14 @@
       <c r="AU39" s="3"/>
       <c r="AV39" s="3"/>
     </row>
-    <row r="40" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="4" t="s">
         <v>112</v>
       </c>
+      <c r="E40" s="4"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
@@ -3633,11 +3664,11 @@
       <c r="AU40" s="3"/>
       <c r="AV40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="4" t="s">
         <v>114</v>
       </c>
       <c r="U41" s="3"/>
@@ -3669,11 +3700,11 @@
       <c r="AU41" s="3"/>
       <c r="AV41" s="3"/>
     </row>
-    <row r="42" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="4" t="s">
         <v>116</v>
       </c>
       <c r="U42" s="3"/>
@@ -3705,11 +3736,11 @@
       <c r="AU42" s="3"/>
       <c r="AV42" s="3"/>
     </row>
-    <row r="43" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="4" t="s">
         <v>118</v>
       </c>
       <c r="U43" s="3"/>
@@ -3741,15 +3772,13 @@
       <c r="AU43" s="3"/>
       <c r="AV43" s="3"/>
     </row>
-    <row r="44" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
@@ -3779,15 +3808,13 @@
       <c r="AU44" s="3"/>
       <c r="AV44" s="3"/>
     </row>
-    <row r="45" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
@@ -3817,14 +3844,15 @@
       <c r="AU45" s="3"/>
       <c r="AV45" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="F46" s="5"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
@@ -3854,13 +3882,15 @@
       <c r="AU46" s="3"/>
       <c r="AV46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="4" t="s">
         <v>126</v>
       </c>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
@@ -3890,13 +3920,14 @@
       <c r="AU47" s="3"/>
       <c r="AV47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="4" t="s">
         <v>128</v>
       </c>
+      <c r="F48" s="4"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
@@ -3930,7 +3961,7 @@
       <c r="A49" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="4" t="s">
         <v>130</v>
       </c>
       <c r="U49" s="3"/>
@@ -3962,11 +3993,11 @@
       <c r="AU49" s="3"/>
       <c r="AV49" s="3"/>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="4" t="s">
         <v>132</v>
       </c>
       <c r="U50" s="3"/>
@@ -3998,11 +4029,11 @@
       <c r="AU50" s="3"/>
       <c r="AV50" s="3"/>
     </row>
-    <row r="51" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="4" t="s">
         <v>134</v>
       </c>
       <c r="U51" s="3"/>
@@ -4034,11 +4065,11 @@
       <c r="AU51" s="3"/>
       <c r="AV51" s="3"/>
     </row>
-    <row r="52" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="1" t="s">
         <v>136</v>
       </c>
       <c r="U52" s="3"/>
@@ -4070,11 +4101,11 @@
       <c r="AU52" s="3"/>
       <c r="AV52" s="3"/>
     </row>
-    <row r="53" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="4" t="s">
         <v>138</v>
       </c>
       <c r="U53" s="3"/>
@@ -4106,11 +4137,11 @@
       <c r="AU53" s="3"/>
       <c r="AV53" s="3"/>
     </row>
-    <row r="54" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="4" t="s">
         <v>140</v>
       </c>
       <c r="U54" s="3"/>
@@ -4142,31 +4173,13 @@
       <c r="AU54" s="3"/>
       <c r="AV54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="s">
+    <row r="55" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="6"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6"/>
-      <c r="P55" s="6"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="6"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
@@ -4196,31 +4209,13 @@
       <c r="AU55" s="3"/>
       <c r="AV55" s="3"/>
     </row>
-    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6" t="s">
+    <row r="56" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6"/>
-      <c r="L56" s="6"/>
-      <c r="M56" s="6"/>
-      <c r="N56" s="6"/>
-      <c r="O56" s="6"/>
-      <c r="P56" s="6"/>
-      <c r="Q56" s="6"/>
-      <c r="R56" s="6"/>
-      <c r="S56" s="6"/>
-      <c r="T56" s="6"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
@@ -4250,11 +4245,11 @@
       <c r="AU56" s="3"/>
       <c r="AV56" s="3"/>
     </row>
-    <row r="57" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="4" t="s">
         <v>146</v>
       </c>
       <c r="C57" s="6"/>
@@ -4304,13 +4299,31 @@
       <c r="AU57" s="3"/>
       <c r="AV57" s="3"/>
     </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
+    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="6" t="s">
         <v>148</v>
       </c>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
+      <c r="M58" s="6"/>
+      <c r="N58" s="6"/>
+      <c r="O58" s="6"/>
+      <c r="P58" s="6"/>
+      <c r="Q58" s="6"/>
+      <c r="R58" s="6"/>
+      <c r="S58" s="6"/>
+      <c r="T58" s="6"/>
       <c r="U58" s="3"/>
       <c r="V58" s="3"/>
       <c r="W58" s="3"/>
@@ -4340,13 +4353,31 @@
       <c r="AU58" s="3"/>
       <c r="AV58" s="3"/>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+    <row r="59" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="4" t="s">
         <v>150</v>
       </c>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
+      <c r="N59" s="6"/>
+      <c r="O59" s="6"/>
+      <c r="P59" s="6"/>
+      <c r="Q59" s="6"/>
+      <c r="R59" s="6"/>
+      <c r="S59" s="6"/>
+      <c r="T59" s="6"/>
       <c r="U59" s="3"/>
       <c r="V59" s="3"/>
       <c r="W59" s="3"/>
@@ -4448,11 +4479,11 @@
       <c r="AU61" s="3"/>
       <c r="AV61" s="3"/>
     </row>
-    <row r="62" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="1" t="s">
         <v>156</v>
       </c>
       <c r="U62" s="3"/>
@@ -4484,11 +4515,11 @@
       <c r="AU62" s="3"/>
       <c r="AV62" s="3"/>
     </row>
-    <row r="63" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="1" t="s">
         <v>158</v>
       </c>
       <c r="U63" s="3"/>
@@ -4520,11 +4551,11 @@
       <c r="AU63" s="3"/>
       <c r="AV63" s="3"/>
     </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="4" t="s">
         <v>160</v>
       </c>
       <c r="U64" s="3"/>
@@ -4556,11 +4587,11 @@
       <c r="AU64" s="3"/>
       <c r="AV64" s="3"/>
     </row>
-    <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B65" s="4" t="s">
         <v>162</v>
       </c>
       <c r="U65" s="3"/>
@@ -4628,11 +4659,11 @@
       <c r="AU66" s="3"/>
       <c r="AV66" s="3"/>
     </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="4" t="s">
         <v>166</v>
       </c>
       <c r="U67" s="3"/>
@@ -4700,11 +4731,11 @@
       <c r="AU68" s="3"/>
       <c r="AV68" s="3"/>
     </row>
-    <row r="69" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B69" s="1" t="s">
         <v>170</v>
       </c>
       <c r="U69" s="3"/>
@@ -4740,6 +4771,9 @@
       <c r="A70" s="1" t="s">
         <v>171</v>
       </c>
+      <c r="B70" s="1" t="s">
+        <v>172</v>
+      </c>
       <c r="U70" s="3"/>
       <c r="V70" s="3"/>
       <c r="W70" s="3"/>
@@ -4769,12 +4803,12 @@
       <c r="AU70" s="3"/>
       <c r="AV70" s="3"/>
     </row>
-    <row r="71" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B71" s="5" t="s">
         <v>173</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>174</v>
       </c>
       <c r="U71" s="3"/>
       <c r="V71" s="3"/>
@@ -4807,9 +4841,6 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B72" s="1" t="s">
         <v>175</v>
       </c>
       <c r="U72" s="3"/>
@@ -4841,12 +4872,12 @@
       <c r="AU72" s="3"/>
       <c r="AV72" s="3"/>
     </row>
-    <row r="73" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B73" s="5" t="s">
-        <v>156</v>
+      <c r="B73" s="4" t="s">
+        <v>177</v>
       </c>
       <c r="U73" s="3"/>
       <c r="V73" s="3"/>
@@ -4879,10 +4910,10 @@
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="U74" s="3"/>
       <c r="V74" s="3"/>
@@ -4913,12 +4944,12 @@
       <c r="AU74" s="3"/>
       <c r="AV74" s="3"/>
     </row>
-    <row r="75" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B75" s="5" t="s">
         <v>180</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>160</v>
       </c>
       <c r="U75" s="3"/>
       <c r="V75" s="3"/>
@@ -4949,11 +4980,11 @@
       <c r="AU75" s="3"/>
       <c r="AV75" s="3"/>
     </row>
-    <row r="76" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="1" t="s">
         <v>182</v>
       </c>
       <c r="U76" s="3"/>
@@ -4985,11 +5016,11 @@
       <c r="AU76" s="3"/>
       <c r="AV76" s="3"/>
     </row>
-    <row r="77" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="B77" s="4" t="s">
         <v>184</v>
       </c>
       <c r="U77" s="3"/>
@@ -5021,11 +5052,11 @@
       <c r="AU77" s="3"/>
       <c r="AV77" s="3"/>
     </row>
-    <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="B78" s="4" t="s">
         <v>186</v>
       </c>
       <c r="U78" s="3"/>
@@ -5057,11 +5088,11 @@
       <c r="AU78" s="3"/>
       <c r="AV78" s="3"/>
     </row>
-    <row r="79" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B79" s="4" t="s">
         <v>188</v>
       </c>
       <c r="U79" s="3"/>
@@ -5093,11 +5124,11 @@
       <c r="AU79" s="3"/>
       <c r="AV79" s="3"/>
     </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="4" t="s">
         <v>190</v>
       </c>
       <c r="U80" s="3"/>
@@ -5129,11 +5160,11 @@
       <c r="AU80" s="3"/>
       <c r="AV80" s="3"/>
     </row>
-    <row r="81" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="B81" s="4" t="s">
         <v>192</v>
       </c>
       <c r="U81" s="3"/>
@@ -5165,11 +5196,11 @@
       <c r="AU81" s="3"/>
       <c r="AV81" s="3"/>
     </row>
-    <row r="82" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="B82" s="1" t="s">
         <v>194</v>
       </c>
       <c r="U82" s="3"/>
@@ -5201,11 +5232,11 @@
       <c r="AU82" s="3"/>
       <c r="AV82" s="3"/>
     </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="4" t="s">
         <v>196</v>
       </c>
       <c r="U83" s="3"/>
@@ -5237,11 +5268,11 @@
       <c r="AU83" s="3"/>
       <c r="AV83" s="3"/>
     </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="4" t="s">
         <v>198</v>
       </c>
       <c r="U84" s="3"/>
@@ -5309,7 +5340,7 @@
       <c r="AU85" s="3"/>
       <c r="AV85" s="3"/>
     </row>
-    <row r="86" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
         <v>201</v>
       </c>
@@ -5381,11 +5412,11 @@
       <c r="AU87" s="3"/>
       <c r="AV87" s="3"/>
     </row>
-    <row r="88" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="1" t="s">
         <v>206</v>
       </c>
       <c r="U88" s="3"/>
@@ -5453,11 +5484,11 @@
       <c r="AU89" s="3"/>
       <c r="AV89" s="3"/>
     </row>
-    <row r="90" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="B90" s="4" t="s">
         <v>210</v>
       </c>
       <c r="U90" s="3"/>
@@ -5496,175 +5527,195 @@
       <c r="B91" s="1" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U91" s="3"/>
+      <c r="V91" s="3"/>
+      <c r="W91" s="3"/>
+      <c r="X91" s="3"/>
+      <c r="Y91" s="3"/>
+      <c r="Z91" s="3"/>
+      <c r="AA91" s="3"/>
+      <c r="AB91" s="3"/>
+      <c r="AC91" s="3"/>
+      <c r="AD91" s="3"/>
+      <c r="AE91" s="3"/>
+      <c r="AF91" s="3"/>
+      <c r="AG91" s="3"/>
+      <c r="AH91" s="3"/>
+      <c r="AI91" s="3"/>
+      <c r="AJ91" s="3"/>
+      <c r="AK91" s="3"/>
+      <c r="AL91" s="3"/>
+      <c r="AM91" s="3"/>
+      <c r="AN91" s="3"/>
+      <c r="AO91" s="3"/>
+      <c r="AP91" s="3"/>
+      <c r="AQ91" s="3"/>
+      <c r="AR91" s="3"/>
+      <c r="AS91" s="3"/>
+      <c r="AT91" s="3"/>
+      <c r="AU91" s="3"/>
+      <c r="AV91" s="3"/>
+    </row>
+    <row r="92" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="4" t="s">
         <v>214</v>
       </c>
+      <c r="U92" s="3"/>
+      <c r="V92" s="3"/>
+      <c r="W92" s="3"/>
+      <c r="X92" s="3"/>
+      <c r="Y92" s="3"/>
+      <c r="Z92" s="3"/>
+      <c r="AA92" s="3"/>
+      <c r="AB92" s="3"/>
+      <c r="AC92" s="3"/>
+      <c r="AD92" s="3"/>
+      <c r="AE92" s="3"/>
+      <c r="AF92" s="3"/>
+      <c r="AG92" s="3"/>
+      <c r="AH92" s="3"/>
+      <c r="AI92" s="3"/>
+      <c r="AJ92" s="3"/>
+      <c r="AK92" s="3"/>
+      <c r="AL92" s="3"/>
+      <c r="AM92" s="3"/>
+      <c r="AN92" s="3"/>
+      <c r="AO92" s="3"/>
+      <c r="AP92" s="3"/>
+      <c r="AQ92" s="3"/>
+      <c r="AR92" s="3"/>
+      <c r="AS92" s="3"/>
+      <c r="AT92" s="3"/>
+      <c r="AU92" s="3"/>
+      <c r="AV92" s="3"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="94" customFormat="false" ht="335.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B93" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B94" s="5" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="95" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B94" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B95" s="5" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="335.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B96" s="5" t="s">
+      <c r="B96" s="4" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="6" t="s">
+    <row r="97" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="B97" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="C97" s="6"/>
-      <c r="D97" s="6"/>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
-      <c r="G97" s="6"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="6"/>
-      <c r="J97" s="6"/>
-      <c r="K97" s="6"/>
-      <c r="L97" s="6"/>
-      <c r="M97" s="6"/>
-      <c r="N97" s="6"/>
-      <c r="O97" s="6"/>
-      <c r="P97" s="6"/>
-      <c r="Q97" s="6"/>
-      <c r="R97" s="6"/>
-      <c r="S97" s="6"/>
-      <c r="T97" s="6"/>
-    </row>
-    <row r="98" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="98" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="B98" s="4" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="s">
+    <row r="99" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B99" s="4" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="100" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C99" s="6"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="6"/>
+      <c r="J99" s="6"/>
+      <c r="K99" s="6"/>
+      <c r="L99" s="6"/>
+      <c r="M99" s="6"/>
+      <c r="N99" s="6"/>
+      <c r="O99" s="6"/>
+      <c r="P99" s="6"/>
+      <c r="Q99" s="6"/>
+      <c r="R99" s="6"/>
+      <c r="S99" s="6"/>
+      <c r="T99" s="6"/>
+    </row>
+    <row r="100" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B100" s="5" t="s">
+      <c r="B100" s="4" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B101" s="5" t="s">
+      <c r="B101" s="4" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B102" s="4" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B103" s="5" t="s">
+      <c r="B103" s="4" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="6" t="s">
+    <row r="104" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B104" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6"/>
-      <c r="E104" s="6"/>
-      <c r="F104" s="6"/>
-      <c r="G104" s="6"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="6"/>
-      <c r="J104" s="6"/>
-      <c r="K104" s="6"/>
-      <c r="L104" s="6"/>
-      <c r="M104" s="6"/>
-      <c r="N104" s="6"/>
-      <c r="O104" s="6"/>
-      <c r="P104" s="6"/>
-      <c r="Q104" s="6"/>
-      <c r="R104" s="6"/>
-      <c r="S104" s="6"/>
-      <c r="T104" s="6"/>
-    </row>
-    <row r="105" customFormat="false" ht="252.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="4" t="s">
+    </row>
+    <row r="105" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B105" s="5" t="s">
+      <c r="B105" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C105" s="5"/>
-      <c r="D105" s="5"/>
-      <c r="E105" s="5"/>
-      <c r="F105" s="5"/>
-      <c r="G105" s="5"/>
-      <c r="H105" s="5"/>
-      <c r="I105" s="5"/>
-      <c r="J105" s="5"/>
-      <c r="K105" s="5"/>
-      <c r="L105" s="5"/>
-      <c r="M105" s="5"/>
-      <c r="N105" s="5"/>
-      <c r="O105" s="5"/>
-      <c r="P105" s="5"/>
-      <c r="Q105" s="5"/>
-      <c r="R105" s="5"/>
-      <c r="S105" s="5"/>
-      <c r="T105" s="5"/>
-    </row>
-    <row r="106" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="106" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="B106" s="5" t="s">
+      <c r="B106" s="4" t="s">
         <v>241</v>
       </c>
       <c r="C106" s="6"/>
@@ -5686,372 +5737,369 @@
       <c r="S106" s="6"/>
       <c r="T106" s="6"/>
     </row>
-    <row r="107" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="s">
+    <row r="107" customFormat="false" ht="252.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="B107" s="5" t="s">
+      <c r="B107" s="4" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="108" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="s">
+      <c r="C107" s="4"/>
+      <c r="D107" s="4"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="4"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
+      <c r="K107" s="4"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+      <c r="N107" s="4"/>
+      <c r="O107" s="4"/>
+      <c r="P107" s="4"/>
+      <c r="Q107" s="4"/>
+      <c r="R107" s="4"/>
+      <c r="S107" s="4"/>
+      <c r="T107" s="4"/>
+    </row>
+    <row r="108" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="B108" s="5" t="s">
+      <c r="B108" s="4" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="109" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C108" s="6"/>
+      <c r="D108" s="6"/>
+      <c r="E108" s="6"/>
+      <c r="F108" s="6"/>
+      <c r="G108" s="6"/>
+      <c r="H108" s="6"/>
+      <c r="I108" s="6"/>
+      <c r="J108" s="6"/>
+      <c r="K108" s="6"/>
+      <c r="L108" s="6"/>
+      <c r="M108" s="6"/>
+      <c r="N108" s="6"/>
+      <c r="O108" s="6"/>
+      <c r="P108" s="6"/>
+      <c r="Q108" s="6"/>
+      <c r="R108" s="6"/>
+      <c r="S108" s="6"/>
+      <c r="T108" s="6"/>
+    </row>
+    <row r="109" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B109" s="5" t="s">
+      <c r="B109" s="4" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="6" t="s">
+    <row r="110" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B110" s="5" t="s">
+      <c r="B110" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C110" s="6"/>
-      <c r="D110" s="6"/>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
-      <c r="G110" s="6"/>
-      <c r="H110" s="6"/>
-      <c r="I110" s="6"/>
-      <c r="J110" s="6"/>
-      <c r="K110" s="6"/>
-      <c r="L110" s="6"/>
-      <c r="M110" s="6"/>
-      <c r="N110" s="6"/>
-      <c r="O110" s="6"/>
-      <c r="P110" s="6"/>
-      <c r="Q110" s="6"/>
-      <c r="R110" s="6"/>
-      <c r="S110" s="6"/>
-      <c r="T110" s="6"/>
-    </row>
-    <row r="111" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="6" t="s">
+    </row>
+    <row r="111" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B111" s="5" t="s">
+      <c r="B111" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="C111" s="6"/>
-      <c r="D111" s="6"/>
-      <c r="E111" s="6"/>
-      <c r="F111" s="6"/>
-      <c r="G111" s="6"/>
-      <c r="H111" s="6"/>
-      <c r="I111" s="6"/>
-      <c r="J111" s="6"/>
-      <c r="K111" s="6"/>
-      <c r="L111" s="6"/>
-      <c r="M111" s="6"/>
-      <c r="N111" s="6"/>
-      <c r="O111" s="6"/>
-      <c r="P111" s="6"/>
-      <c r="Q111" s="6"/>
-      <c r="R111" s="6"/>
-      <c r="S111" s="6"/>
-      <c r="T111" s="6"/>
-    </row>
-    <row r="112" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1" t="s">
+    </row>
+    <row r="112" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="B112" s="5" t="s">
+      <c r="B112" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C112" s="5" t="s">
+      <c r="C112" s="6"/>
+      <c r="D112" s="6"/>
+      <c r="E112" s="6"/>
+      <c r="F112" s="6"/>
+      <c r="G112" s="6"/>
+      <c r="H112" s="6"/>
+      <c r="I112" s="6"/>
+      <c r="J112" s="6"/>
+      <c r="K112" s="6"/>
+      <c r="L112" s="6"/>
+      <c r="M112" s="6"/>
+      <c r="N112" s="6"/>
+      <c r="O112" s="6"/>
+      <c r="P112" s="6"/>
+      <c r="Q112" s="6"/>
+      <c r="R112" s="6"/>
+      <c r="S112" s="6"/>
+      <c r="T112" s="6"/>
+    </row>
+    <row r="113" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D112" s="5" t="s">
+      <c r="B113" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="E112" s="5" t="s">
+      <c r="C113" s="6"/>
+      <c r="D113" s="6"/>
+      <c r="E113" s="6"/>
+      <c r="F113" s="6"/>
+      <c r="G113" s="6"/>
+      <c r="H113" s="6"/>
+      <c r="I113" s="6"/>
+      <c r="J113" s="6"/>
+      <c r="K113" s="6"/>
+      <c r="L113" s="6"/>
+      <c r="M113" s="6"/>
+      <c r="N113" s="6"/>
+      <c r="O113" s="6"/>
+      <c r="P113" s="6"/>
+      <c r="Q113" s="6"/>
+      <c r="R113" s="6"/>
+      <c r="S113" s="6"/>
+      <c r="T113" s="6"/>
+    </row>
+    <row r="114" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="F112" s="5" t="s">
+      <c r="B114" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="G112" s="5" t="s">
+      <c r="C114" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="H112" s="5" t="s">
+      <c r="D114" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="I112" s="5" t="s">
+      <c r="E114" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="J112" s="5" t="s">
+      <c r="F114" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="K112" s="5" t="s">
+      <c r="G114" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="L112" s="5" t="s">
+      <c r="H114" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="M112" s="5" t="s">
+      <c r="I114" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="N112" s="5" t="s">
+      <c r="J114" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="O112" s="5" t="s">
+      <c r="K114" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="P112" s="5" t="s">
+      <c r="L114" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="Q112" s="5" t="s">
+      <c r="M114" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="R112" s="5" t="s">
+      <c r="N114" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="S112" s="5" t="s">
+      <c r="O114" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="T112" s="5" t="s">
+      <c r="P114" s="4" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="113" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="1" t="s">
+      <c r="Q114" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="B113" s="5" t="s">
+      <c r="R114" s="4" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="114" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1" t="s">
+      <c r="S114" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="B114" s="5" t="s">
+      <c r="T114" s="4" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="6" t="s">
+    <row r="115" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B115" s="5" t="s">
+      <c r="B115" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="C115" s="6"/>
-      <c r="D115" s="6"/>
-      <c r="E115" s="6"/>
-      <c r="F115" s="6"/>
-      <c r="G115" s="6"/>
-      <c r="H115" s="6"/>
-      <c r="I115" s="6"/>
-      <c r="J115" s="6"/>
-      <c r="K115" s="6"/>
-      <c r="L115" s="6"/>
-      <c r="M115" s="6"/>
-      <c r="N115" s="6"/>
-      <c r="O115" s="6"/>
-      <c r="P115" s="6"/>
-      <c r="Q115" s="6"/>
-      <c r="R115" s="6"/>
-      <c r="S115" s="6"/>
-      <c r="T115" s="6"/>
-    </row>
-    <row r="116" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="116" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B116" s="7" t="s">
+      <c r="B116" s="4" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="54.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1" t="s">
+    <row r="117" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="B117" s="7" t="s">
+      <c r="B117" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="118" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C117" s="6"/>
+      <c r="D117" s="6"/>
+      <c r="E117" s="6"/>
+      <c r="F117" s="6"/>
+      <c r="G117" s="6"/>
+      <c r="H117" s="6"/>
+      <c r="I117" s="6"/>
+      <c r="J117" s="6"/>
+      <c r="K117" s="6"/>
+      <c r="L117" s="6"/>
+      <c r="M117" s="6"/>
+      <c r="N117" s="6"/>
+      <c r="O117" s="6"/>
+      <c r="P117" s="6"/>
+      <c r="Q117" s="6"/>
+      <c r="R117" s="6"/>
+      <c r="S117" s="6"/>
+      <c r="T117" s="6"/>
+    </row>
+    <row r="118" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B118" s="5" t="s">
+      <c r="B118" s="7" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="54.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B119" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="H119" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="I119" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="J119" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="K119" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="L119" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="M119" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="N119" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="O119" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="P119" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="Q119" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="R119" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="S119" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="T119" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="120" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B120" s="5" t="s">
+      <c r="B120" s="4" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B121" s="5" t="s">
+      <c r="B121" s="1" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="M121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="N121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="O121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="P121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="R121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="S121" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="T121" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B122" s="4" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B123" s="4" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B124" s="5" t="s">
+      <c r="B124" s="1" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B125" s="5" t="s">
+      <c r="B125" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="AX125" s="3"/>
-      <c r="AY125" s="3"/>
-      <c r="AZ125" s="3"/>
-      <c r="BA125" s="3"/>
-      <c r="BB125" s="3"/>
-      <c r="BC125" s="3"/>
-      <c r="BD125" s="3"/>
-      <c r="BE125" s="3"/>
-      <c r="BF125" s="3"/>
-      <c r="BG125" s="3"/>
-      <c r="BH125" s="3"/>
-      <c r="BI125" s="3"/>
-      <c r="BJ125" s="3"/>
-      <c r="BK125" s="3"/>
-      <c r="BL125" s="3"/>
-      <c r="BM125" s="3"/>
-      <c r="BN125" s="3"/>
-      <c r="BO125" s="3"/>
-      <c r="BP125" s="3"/>
-      <c r="BQ125" s="3"/>
-      <c r="BR125" s="3"/>
-      <c r="BS125" s="3"/>
-      <c r="BT125" s="3"/>
-      <c r="BU125" s="3"/>
-      <c r="BV125" s="3"/>
-      <c r="BW125" s="3"/>
-      <c r="BX125" s="3"/>
-      <c r="BY125" s="3"/>
-      <c r="BZ125" s="3"/>
-      <c r="CA125" s="3"/>
-      <c r="CB125" s="3"/>
-      <c r="CC125" s="3"/>
-      <c r="CD125" s="3"/>
-      <c r="CE125" s="3"/>
-      <c r="CF125" s="3"/>
-      <c r="CG125" s="3"/>
-      <c r="CH125" s="3"/>
-      <c r="CI125" s="3"/>
-      <c r="CJ125" s="3"/>
-    </row>
-    <row r="126" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="126" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B126" s="5" t="s">
+      <c r="B126" s="4" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B127" s="5" t="s">
+      <c r="B127" s="4" t="s">
         <v>301</v>
       </c>
       <c r="AX127" s="3"/>
@@ -6094,142 +6142,197 @@
       <c r="CI127" s="3"/>
       <c r="CJ127" s="3"/>
     </row>
-    <row r="128" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B128" s="5" t="s">
+      <c r="B128" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="AX128" s="3"/>
-      <c r="AY128" s="3"/>
-      <c r="AZ128" s="3"/>
-      <c r="BA128" s="3"/>
-      <c r="BB128" s="3"/>
-      <c r="BC128" s="3"/>
-      <c r="BD128" s="3"/>
-      <c r="BE128" s="3"/>
-      <c r="BF128" s="3"/>
-      <c r="BG128" s="3"/>
-      <c r="BH128" s="3"/>
-      <c r="BI128" s="3"/>
-      <c r="BJ128" s="3"/>
-      <c r="BK128" s="3"/>
-      <c r="BL128" s="3"/>
-      <c r="BM128" s="3"/>
-      <c r="BN128" s="3"/>
-      <c r="BO128" s="3"/>
-      <c r="BP128" s="3"/>
-      <c r="BQ128" s="3"/>
-      <c r="BR128" s="3"/>
-      <c r="BS128" s="3"/>
-      <c r="BT128" s="3"/>
-      <c r="BU128" s="3"/>
-      <c r="BV128" s="3"/>
-      <c r="BW128" s="3"/>
-      <c r="BX128" s="3"/>
-      <c r="BY128" s="3"/>
-      <c r="BZ128" s="3"/>
-      <c r="CA128" s="3"/>
-      <c r="CB128" s="3"/>
-      <c r="CC128" s="3"/>
-      <c r="CD128" s="3"/>
-      <c r="CE128" s="3"/>
-      <c r="CF128" s="3"/>
-      <c r="CG128" s="3"/>
-      <c r="CH128" s="3"/>
-      <c r="CI128" s="3"/>
-      <c r="CJ128" s="3"/>
-    </row>
-    <row r="129" s="3" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="129" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B129" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="C129" s="1"/>
-      <c r="D129" s="1"/>
-      <c r="E129" s="1"/>
-      <c r="F129" s="1"/>
-      <c r="G129" s="1"/>
-      <c r="H129" s="1"/>
-      <c r="I129" s="1"/>
-      <c r="J129" s="1"/>
-      <c r="K129" s="1"/>
-      <c r="L129" s="1"/>
-      <c r="M129" s="1"/>
-      <c r="N129" s="1"/>
-      <c r="O129" s="1"/>
-      <c r="P129" s="1"/>
-      <c r="Q129" s="1"/>
-      <c r="R129" s="1"/>
-      <c r="S129" s="1"/>
-      <c r="T129" s="1"/>
-      <c r="U129" s="1"/>
-      <c r="V129" s="1"/>
-      <c r="W129" s="1"/>
-      <c r="X129" s="1"/>
-      <c r="Y129" s="1"/>
-      <c r="Z129" s="1"/>
-      <c r="AA129" s="1"/>
-      <c r="AB129" s="1"/>
-      <c r="AC129" s="1"/>
-      <c r="AD129" s="1"/>
-      <c r="AE129" s="1"/>
-      <c r="AF129" s="1"/>
-      <c r="AG129" s="1"/>
-      <c r="AH129" s="1"/>
-      <c r="AI129" s="1"/>
-      <c r="AJ129" s="1"/>
-      <c r="AK129" s="1"/>
-      <c r="AL129" s="1"/>
-      <c r="AM129" s="1"/>
-      <c r="AN129" s="1"/>
-      <c r="AO129" s="1"/>
-      <c r="AP129" s="1"/>
-      <c r="AQ129" s="1"/>
-      <c r="AR129" s="1"/>
-      <c r="AS129" s="1"/>
-      <c r="AT129" s="1"/>
-      <c r="AU129" s="1"/>
-      <c r="AV129" s="1"/>
-      <c r="AW129" s="1"/>
-    </row>
-    <row r="130" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B129" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="AX129" s="3"/>
+      <c r="AY129" s="3"/>
+      <c r="AZ129" s="3"/>
+      <c r="BA129" s="3"/>
+      <c r="BB129" s="3"/>
+      <c r="BC129" s="3"/>
+      <c r="BD129" s="3"/>
+      <c r="BE129" s="3"/>
+      <c r="BF129" s="3"/>
+      <c r="BG129" s="3"/>
+      <c r="BH129" s="3"/>
+      <c r="BI129" s="3"/>
+      <c r="BJ129" s="3"/>
+      <c r="BK129" s="3"/>
+      <c r="BL129" s="3"/>
+      <c r="BM129" s="3"/>
+      <c r="BN129" s="3"/>
+      <c r="BO129" s="3"/>
+      <c r="BP129" s="3"/>
+      <c r="BQ129" s="3"/>
+      <c r="BR129" s="3"/>
+      <c r="BS129" s="3"/>
+      <c r="BT129" s="3"/>
+      <c r="BU129" s="3"/>
+      <c r="BV129" s="3"/>
+      <c r="BW129" s="3"/>
+      <c r="BX129" s="3"/>
+      <c r="BY129" s="3"/>
+      <c r="BZ129" s="3"/>
+      <c r="CA129" s="3"/>
+      <c r="CB129" s="3"/>
+      <c r="CC129" s="3"/>
+      <c r="CD129" s="3"/>
+      <c r="CE129" s="3"/>
+      <c r="CF129" s="3"/>
+      <c r="CG129" s="3"/>
+      <c r="CH129" s="3"/>
+      <c r="CI129" s="3"/>
+      <c r="CJ129" s="3"/>
+    </row>
+    <row r="130" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="B130" s="5" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="131" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B130" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="AX130" s="3"/>
+      <c r="AY130" s="3"/>
+      <c r="AZ130" s="3"/>
+      <c r="BA130" s="3"/>
+      <c r="BB130" s="3"/>
+      <c r="BC130" s="3"/>
+      <c r="BD130" s="3"/>
+      <c r="BE130" s="3"/>
+      <c r="BF130" s="3"/>
+      <c r="BG130" s="3"/>
+      <c r="BH130" s="3"/>
+      <c r="BI130" s="3"/>
+      <c r="BJ130" s="3"/>
+      <c r="BK130" s="3"/>
+      <c r="BL130" s="3"/>
+      <c r="BM130" s="3"/>
+      <c r="BN130" s="3"/>
+      <c r="BO130" s="3"/>
+      <c r="BP130" s="3"/>
+      <c r="BQ130" s="3"/>
+      <c r="BR130" s="3"/>
+      <c r="BS130" s="3"/>
+      <c r="BT130" s="3"/>
+      <c r="BU130" s="3"/>
+      <c r="BV130" s="3"/>
+      <c r="BW130" s="3"/>
+      <c r="BX130" s="3"/>
+      <c r="BY130" s="3"/>
+      <c r="BZ130" s="3"/>
+      <c r="CA130" s="3"/>
+      <c r="CB130" s="3"/>
+      <c r="CC130" s="3"/>
+      <c r="CD130" s="3"/>
+      <c r="CE130" s="3"/>
+      <c r="CF130" s="3"/>
+      <c r="CG130" s="3"/>
+      <c r="CH130" s="3"/>
+      <c r="CI130" s="3"/>
+      <c r="CJ130" s="3"/>
+    </row>
+    <row r="131" s="3" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="B131" s="8" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="132" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B131" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1"/>
+      <c r="E131" s="1"/>
+      <c r="F131" s="1"/>
+      <c r="G131" s="1"/>
+      <c r="H131" s="1"/>
+      <c r="I131" s="1"/>
+      <c r="J131" s="1"/>
+      <c r="K131" s="1"/>
+      <c r="L131" s="1"/>
+      <c r="M131" s="1"/>
+      <c r="N131" s="1"/>
+      <c r="O131" s="1"/>
+      <c r="P131" s="1"/>
+      <c r="Q131" s="1"/>
+      <c r="R131" s="1"/>
+      <c r="S131" s="1"/>
+      <c r="T131" s="1"/>
+      <c r="U131" s="1"/>
+      <c r="V131" s="1"/>
+      <c r="W131" s="1"/>
+      <c r="X131" s="1"/>
+      <c r="Y131" s="1"/>
+      <c r="Z131" s="1"/>
+      <c r="AA131" s="1"/>
+      <c r="AB131" s="1"/>
+      <c r="AC131" s="1"/>
+      <c r="AD131" s="1"/>
+      <c r="AE131" s="1"/>
+      <c r="AF131" s="1"/>
+      <c r="AG131" s="1"/>
+      <c r="AH131" s="1"/>
+      <c r="AI131" s="1"/>
+      <c r="AJ131" s="1"/>
+      <c r="AK131" s="1"/>
+      <c r="AL131" s="1"/>
+      <c r="AM131" s="1"/>
+      <c r="AN131" s="1"/>
+      <c r="AO131" s="1"/>
+      <c r="AP131" s="1"/>
+      <c r="AQ131" s="1"/>
+      <c r="AR131" s="1"/>
+      <c r="AS131" s="1"/>
+      <c r="AT131" s="1"/>
+      <c r="AU131" s="1"/>
+      <c r="AV131" s="1"/>
+      <c r="AW131" s="1"/>
+    </row>
+    <row r="132" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B132" s="8" t="s">
+      <c r="B132" s="4" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B133" s="5" t="s">
+      <c r="B133" s="8" t="s">
         <v>312</v>
       </c>
     </row>
+    <row r="134" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B134" s="8" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>316</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:T132"/>
+  <autoFilter ref="A2:T134"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/JP (Exclude Game)/Data/chara_talk.xlsx
+++ b/JP (Exclude Game)/Data/chara_talk.xlsx
@@ -11,7 +11,7 @@
     <sheet name="1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$134</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$135</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="319">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -140,6 +140,15 @@
   </si>
   <si>
     <t xml:space="preserve">夢人</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ﾋﾟｷﾞｬｰ
+ﾋﾟｷﾞｬｧｧｧ
+ﾋﾟｷﾞｬｱｱｱｧｧｧ
+ﾋﾟ…</t>
   </si>
   <si>
     <t xml:space="preserve">play_baby</t>
@@ -1889,9 +1898,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>2080080</xdr:colOff>
+      <xdr:colOff>2079720</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>124200</xdr:rowOff>
+      <xdr:rowOff>123840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1901,7 +1910,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="50980680" cy="124200"/>
+          <a:ext cx="50980320" cy="123840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1934,9 +1943,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>517680</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>316440</xdr:rowOff>
+      <xdr:colOff>517320</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>316080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1946,7 +1955,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="55188720" cy="45504360"/>
+          <a:ext cx="55188360" cy="46053360"/>
         </a:xfrm>
         <a:solidFill>
           <a:srgbClr val="ffffff"/>
@@ -2081,7 +2090,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CJ135"/>
+  <dimension ref="A1:CJ136"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.04"/>
@@ -2315,7 +2324,7 @@
       <c r="AU3" s="3"/>
       <c r="AV3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>39</v>
       </c>
@@ -2351,7 +2360,7 @@
       <c r="AU4" s="3"/>
       <c r="AV4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>41</v>
       </c>
@@ -2387,11 +2396,11 @@
       <c r="AU5" s="3"/>
       <c r="AV5" s="3"/>
     </row>
-    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>44</v>
       </c>
       <c r="U6" s="3"/>
@@ -2423,11 +2432,11 @@
       <c r="AU6" s="3"/>
       <c r="AV6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>46</v>
       </c>
       <c r="U7" s="3"/>
@@ -2459,7 +2468,7 @@
       <c r="AU7" s="3"/>
       <c r="AV7" s="3"/>
     </row>
-    <row r="8" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>47</v>
       </c>
@@ -2495,11 +2504,11 @@
       <c r="AU8" s="3"/>
       <c r="AV8" s="3"/>
     </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="4" t="s">
         <v>50</v>
       </c>
       <c r="U9" s="3"/>
@@ -2603,11 +2612,11 @@
       <c r="AU11" s="3"/>
       <c r="AV11" s="3"/>
     </row>
-    <row r="12" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="1" t="s">
         <v>56</v>
       </c>
       <c r="U12" s="3"/>
@@ -2639,7 +2648,7 @@
       <c r="AU12" s="3"/>
       <c r="AV12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>57</v>
       </c>
@@ -2675,7 +2684,7 @@
       <c r="AU13" s="3"/>
       <c r="AV13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>59</v>
       </c>
@@ -2711,7 +2720,7 @@
       <c r="AU14" s="3"/>
       <c r="AV14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>61</v>
       </c>
@@ -2783,7 +2792,7 @@
       <c r="AU16" s="3"/>
       <c r="AV16" s="3"/>
     </row>
-    <row r="17" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>65</v>
       </c>
@@ -2819,7 +2828,7 @@
       <c r="AU17" s="3"/>
       <c r="AV17" s="3"/>
     </row>
-    <row r="18" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>67</v>
       </c>
@@ -2855,7 +2864,7 @@
       <c r="AU18" s="3"/>
       <c r="AV18" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>69</v>
       </c>
@@ -2891,7 +2900,7 @@
       <c r="AU19" s="3"/>
       <c r="AV19" s="3"/>
     </row>
-    <row r="20" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>71</v>
       </c>
@@ -2927,7 +2936,7 @@
       <c r="AU20" s="3"/>
       <c r="AV20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>73</v>
       </c>
@@ -2963,8 +2972,8 @@
       <c r="AU21" s="3"/>
       <c r="AV21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+    <row r="22" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -2999,14 +3008,13 @@
       <c r="AU22" s="3"/>
       <c r="AV22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
         <v>77</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C23" s="4"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
@@ -3036,13 +3044,14 @@
       <c r="AU23" s="3"/>
       <c r="AV23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
         <v>79</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>80</v>
       </c>
+      <c r="C24" s="4"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -3073,13 +3082,12 @@
       <c r="AV24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="4" t="s">
         <v>81</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="4"/>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
@@ -3117,7 +3125,6 @@
         <v>84</v>
       </c>
       <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -3147,7 +3154,7 @@
       <c r="AU26" s="3"/>
       <c r="AV26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>85</v>
       </c>
@@ -3185,7 +3192,7 @@
       <c r="AU27" s="3"/>
       <c r="AV27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>87</v>
       </c>
@@ -3223,7 +3230,7 @@
       <c r="AU28" s="3"/>
       <c r="AV28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>89</v>
       </c>
@@ -3231,6 +3238,7 @@
         <v>90</v>
       </c>
       <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
@@ -3260,7 +3268,7 @@
       <c r="AU29" s="3"/>
       <c r="AV29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>91</v>
       </c>
@@ -3297,13 +3305,14 @@
       <c r="AU30" s="3"/>
       <c r="AV30" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>94</v>
       </c>
+      <c r="C31" s="4"/>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
@@ -3333,7 +3342,7 @@
       <c r="AU31" s="3"/>
       <c r="AV31" s="3"/>
     </row>
-    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>95</v>
       </c>
@@ -3369,15 +3378,13 @@
       <c r="AU32" s="3"/>
       <c r="AV32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -3407,13 +3414,15 @@
       <c r="AU33" s="3"/>
       <c r="AV33" s="3"/>
     </row>
-    <row r="34" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>99</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>100</v>
       </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
@@ -3443,11 +3452,11 @@
       <c r="AU34" s="3"/>
       <c r="AV34" s="3"/>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="4" t="s">
         <v>102</v>
       </c>
       <c r="U35" s="3"/>
@@ -3479,14 +3488,13 @@
       <c r="AU35" s="3"/>
       <c r="AV35" s="3"/>
     </row>
-    <row r="36" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C36" s="4"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
@@ -3516,8 +3524,8 @@
       <c r="AU36" s="3"/>
       <c r="AV36" s="3"/>
     </row>
-    <row r="37" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+    <row r="37" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="s">
         <v>105</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -3553,14 +3561,14 @@
       <c r="AU37" s="3"/>
       <c r="AV37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>107</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D38" s="4"/>
+      <c r="C38" s="4"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
@@ -3590,14 +3598,14 @@
       <c r="AU38" s="3"/>
       <c r="AV38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>109</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
@@ -3627,14 +3635,14 @@
       <c r="AU39" s="3"/>
       <c r="AV39" s="3"/>
     </row>
-    <row r="40" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="E40" s="4"/>
+      <c r="C40" s="4"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
@@ -3664,13 +3672,14 @@
       <c r="AU40" s="3"/>
       <c r="AV40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>114</v>
       </c>
+      <c r="E41" s="4"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
@@ -3700,7 +3709,7 @@
       <c r="AU41" s="3"/>
       <c r="AV41" s="3"/>
     </row>
-    <row r="42" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>115</v>
       </c>
@@ -3736,7 +3745,7 @@
       <c r="AU42" s="3"/>
       <c r="AV42" s="3"/>
     </row>
-    <row r="43" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>117</v>
       </c>
@@ -3772,7 +3781,7 @@
       <c r="AU43" s="3"/>
       <c r="AV43" s="3"/>
     </row>
-    <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>119</v>
       </c>
@@ -3808,7 +3817,7 @@
       <c r="AU44" s="3"/>
       <c r="AV44" s="3"/>
     </row>
-    <row r="45" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>121</v>
       </c>
@@ -3844,15 +3853,13 @@
       <c r="AU45" s="3"/>
       <c r="AV45" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>123</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
@@ -3882,7 +3889,7 @@
       <c r="AU46" s="3"/>
       <c r="AV46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>125</v>
       </c>
@@ -3920,14 +3927,15 @@
       <c r="AU47" s="3"/>
       <c r="AV47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>127</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
@@ -3957,13 +3965,14 @@
       <c r="AU48" s="3"/>
       <c r="AV48" s="3"/>
     </row>
-    <row r="49" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>129</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>130</v>
       </c>
+      <c r="F49" s="4"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
@@ -4065,11 +4074,11 @@
       <c r="AU51" s="3"/>
       <c r="AV51" s="3"/>
     </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="4" t="s">
         <v>136</v>
       </c>
       <c r="U52" s="3"/>
@@ -4101,11 +4110,11 @@
       <c r="AU52" s="3"/>
       <c r="AV52" s="3"/>
     </row>
-    <row r="53" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="1" t="s">
         <v>138</v>
       </c>
       <c r="U53" s="3"/>
@@ -4137,7 +4146,7 @@
       <c r="AU53" s="3"/>
       <c r="AV53" s="3"/>
     </row>
-    <row r="54" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
         <v>139</v>
       </c>
@@ -4173,7 +4182,7 @@
       <c r="AU54" s="3"/>
       <c r="AV54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
         <v>141</v>
       </c>
@@ -4209,7 +4218,7 @@
       <c r="AU55" s="3"/>
       <c r="AV55" s="3"/>
     </row>
-    <row r="56" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
         <v>143</v>
       </c>
@@ -4246,30 +4255,12 @@
       <c r="AV56" s="3"/>
     </row>
     <row r="57" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="6"/>
-      <c r="M57" s="6"/>
-      <c r="N57" s="6"/>
-      <c r="O57" s="6"/>
-      <c r="P57" s="6"/>
-      <c r="Q57" s="6"/>
-      <c r="R57" s="6"/>
-      <c r="S57" s="6"/>
-      <c r="T57" s="6"/>
       <c r="U57" s="3"/>
       <c r="V57" s="3"/>
       <c r="W57" s="3"/>
@@ -4299,11 +4290,11 @@
       <c r="AU57" s="3"/>
       <c r="AV57" s="3"/>
     </row>
-    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="4" t="s">
         <v>148</v>
       </c>
       <c r="C58" s="6"/>
@@ -4353,11 +4344,11 @@
       <c r="AU58" s="3"/>
       <c r="AV58" s="3"/>
     </row>
-    <row r="59" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="6" t="s">
         <v>150</v>
       </c>
       <c r="C59" s="6"/>
@@ -4407,13 +4398,31 @@
       <c r="AU59" s="3"/>
       <c r="AV59" s="3"/>
     </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
+    <row r="60" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="4" t="s">
         <v>152</v>
       </c>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
+      <c r="N60" s="6"/>
+      <c r="O60" s="6"/>
+      <c r="P60" s="6"/>
+      <c r="Q60" s="6"/>
+      <c r="R60" s="6"/>
+      <c r="S60" s="6"/>
+      <c r="T60" s="6"/>
       <c r="U60" s="3"/>
       <c r="V60" s="3"/>
       <c r="W60" s="3"/>
@@ -4551,11 +4560,11 @@
       <c r="AU63" s="3"/>
       <c r="AV63" s="3"/>
     </row>
-    <row r="64" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="1" t="s">
         <v>160</v>
       </c>
       <c r="U64" s="3"/>
@@ -4587,7 +4596,7 @@
       <c r="AU64" s="3"/>
       <c r="AV64" s="3"/>
     </row>
-    <row r="65" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
         <v>161</v>
       </c>
@@ -4623,11 +4632,11 @@
       <c r="AU65" s="3"/>
       <c r="AV65" s="3"/>
     </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="4" t="s">
         <v>164</v>
       </c>
       <c r="U66" s="3"/>
@@ -4659,11 +4668,11 @@
       <c r="AU66" s="3"/>
       <c r="AV66" s="3"/>
     </row>
-    <row r="67" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="1" t="s">
         <v>166</v>
       </c>
       <c r="U67" s="3"/>
@@ -4695,11 +4704,11 @@
       <c r="AU67" s="3"/>
       <c r="AV67" s="3"/>
     </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="4" t="s">
         <v>168</v>
       </c>
       <c r="U68" s="3"/>
@@ -4803,11 +4812,11 @@
       <c r="AU70" s="3"/>
       <c r="AV70" s="3"/>
     </row>
-    <row r="71" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="1" t="s">
         <v>174</v>
       </c>
       <c r="U71" s="3"/>
@@ -4839,9 +4848,12 @@
       <c r="AU71" s="3"/>
       <c r="AV71" s="3"/>
     </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
         <v>175</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>176</v>
       </c>
       <c r="U72" s="3"/>
       <c r="V72" s="3"/>
@@ -4872,11 +4884,8 @@
       <c r="AU72" s="3"/>
       <c r="AV72" s="3"/>
     </row>
-    <row r="73" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B73" s="4" t="s">
         <v>177</v>
       </c>
       <c r="U73" s="3"/>
@@ -4908,11 +4917,11 @@
       <c r="AU73" s="3"/>
       <c r="AV73" s="3"/>
     </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="4" t="s">
         <v>179</v>
       </c>
       <c r="U74" s="3"/>
@@ -4944,12 +4953,12 @@
       <c r="AU74" s="3"/>
       <c r="AV74" s="3"/>
     </row>
-    <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B75" s="4" t="s">
-        <v>160</v>
+      <c r="B75" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="U75" s="3"/>
       <c r="V75" s="3"/>
@@ -4980,12 +4989,12 @@
       <c r="AU75" s="3"/>
       <c r="AV75" s="3"/>
     </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B76" s="1" t="s">
         <v>182</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>162</v>
       </c>
       <c r="U76" s="3"/>
       <c r="V76" s="3"/>
@@ -5016,11 +5025,11 @@
       <c r="AU76" s="3"/>
       <c r="AV76" s="3"/>
     </row>
-    <row r="77" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="1" t="s">
         <v>184</v>
       </c>
       <c r="U77" s="3"/>
@@ -5052,7 +5061,7 @@
       <c r="AU77" s="3"/>
       <c r="AV77" s="3"/>
     </row>
-    <row r="78" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
         <v>185</v>
       </c>
@@ -5088,7 +5097,7 @@
       <c r="AU78" s="3"/>
       <c r="AV78" s="3"/>
     </row>
-    <row r="79" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
         <v>187</v>
       </c>
@@ -5124,7 +5133,7 @@
       <c r="AU79" s="3"/>
       <c r="AV79" s="3"/>
     </row>
-    <row r="80" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
         <v>189</v>
       </c>
@@ -5160,7 +5169,7 @@
       <c r="AU80" s="3"/>
       <c r="AV80" s="3"/>
     </row>
-    <row r="81" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
         <v>191</v>
       </c>
@@ -5196,11 +5205,11 @@
       <c r="AU81" s="3"/>
       <c r="AV81" s="3"/>
     </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="4" t="s">
         <v>194</v>
       </c>
       <c r="U82" s="3"/>
@@ -5232,11 +5241,11 @@
       <c r="AU82" s="3"/>
       <c r="AV82" s="3"/>
     </row>
-    <row r="83" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="1" t="s">
         <v>196</v>
       </c>
       <c r="U83" s="3"/>
@@ -5268,7 +5277,7 @@
       <c r="AU83" s="3"/>
       <c r="AV83" s="3"/>
     </row>
-    <row r="84" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
         <v>197</v>
       </c>
@@ -5304,11 +5313,11 @@
       <c r="AU84" s="3"/>
       <c r="AV84" s="3"/>
     </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="4" t="s">
         <v>200</v>
       </c>
       <c r="U85" s="3"/>
@@ -5412,7 +5421,7 @@
       <c r="AU87" s="3"/>
       <c r="AV87" s="3"/>
     </row>
-    <row r="88" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
         <v>205</v>
       </c>
@@ -5448,7 +5457,7 @@
       <c r="AU88" s="3"/>
       <c r="AV88" s="3"/>
     </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
         <v>207</v>
       </c>
@@ -5484,11 +5493,11 @@
       <c r="AU89" s="3"/>
       <c r="AV89" s="3"/>
     </row>
-    <row r="90" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="1" t="s">
         <v>210</v>
       </c>
       <c r="U90" s="3"/>
@@ -5520,11 +5529,11 @@
       <c r="AU90" s="3"/>
       <c r="AV90" s="3"/>
     </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="4" t="s">
         <v>212</v>
       </c>
       <c r="U91" s="3"/>
@@ -5556,11 +5565,11 @@
       <c r="AU91" s="3"/>
       <c r="AV91" s="3"/>
     </row>
-    <row r="92" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="1" t="s">
         <v>214</v>
       </c>
       <c r="U92" s="3"/>
@@ -5592,13 +5601,41 @@
       <c r="AU92" s="3"/>
       <c r="AV92" s="3"/>
     </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" s="4" t="s">
         <v>216</v>
       </c>
+      <c r="U93" s="3"/>
+      <c r="V93" s="3"/>
+      <c r="W93" s="3"/>
+      <c r="X93" s="3"/>
+      <c r="Y93" s="3"/>
+      <c r="Z93" s="3"/>
+      <c r="AA93" s="3"/>
+      <c r="AB93" s="3"/>
+      <c r="AC93" s="3"/>
+      <c r="AD93" s="3"/>
+      <c r="AE93" s="3"/>
+      <c r="AF93" s="3"/>
+      <c r="AG93" s="3"/>
+      <c r="AH93" s="3"/>
+      <c r="AI93" s="3"/>
+      <c r="AJ93" s="3"/>
+      <c r="AK93" s="3"/>
+      <c r="AL93" s="3"/>
+      <c r="AM93" s="3"/>
+      <c r="AN93" s="3"/>
+      <c r="AO93" s="3"/>
+      <c r="AP93" s="3"/>
+      <c r="AQ93" s="3"/>
+      <c r="AR93" s="3"/>
+      <c r="AS93" s="3"/>
+      <c r="AT93" s="3"/>
+      <c r="AU93" s="3"/>
+      <c r="AV93" s="3"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
@@ -5612,16 +5649,16 @@
       <c r="A95" s="1" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="96" customFormat="false" ht="335.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B95" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B96" s="4" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="335.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
         <v>222</v>
       </c>
@@ -5629,7 +5666,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
         <v>224</v>
       </c>
@@ -5637,39 +5674,39 @@
         <v>225</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="6" t="s">
+    <row r="99" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
         <v>226</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6"/>
-      <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
-      <c r="G99" s="6"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="6"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="6"/>
-      <c r="L99" s="6"/>
-      <c r="M99" s="6"/>
-      <c r="N99" s="6"/>
-      <c r="O99" s="6"/>
-      <c r="P99" s="6"/>
-      <c r="Q99" s="6"/>
-      <c r="R99" s="6"/>
-      <c r="S99" s="6"/>
-      <c r="T99" s="6"/>
-    </row>
-    <row r="100" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="s">
+    </row>
+    <row r="100" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="6" t="s">
         <v>228</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>229</v>
       </c>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="6"/>
+      <c r="J100" s="6"/>
+      <c r="K100" s="6"/>
+      <c r="L100" s="6"/>
+      <c r="M100" s="6"/>
+      <c r="N100" s="6"/>
+      <c r="O100" s="6"/>
+      <c r="P100" s="6"/>
+      <c r="Q100" s="6"/>
+      <c r="R100" s="6"/>
+      <c r="S100" s="6"/>
+      <c r="T100" s="6"/>
     </row>
     <row r="101" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
@@ -5679,7 +5716,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
         <v>232</v>
       </c>
@@ -5687,7 +5724,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
         <v>234</v>
       </c>
@@ -5695,7 +5732,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
         <v>236</v>
       </c>
@@ -5703,7 +5740,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
         <v>238</v>
       </c>
@@ -5711,93 +5748,93 @@
         <v>239</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="6" t="s">
+    <row r="106" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="1" t="s">
         <v>240</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="C106" s="6"/>
-      <c r="D106" s="6"/>
-      <c r="E106" s="6"/>
-      <c r="F106" s="6"/>
-      <c r="G106" s="6"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="6"/>
-      <c r="J106" s="6"/>
-      <c r="K106" s="6"/>
-      <c r="L106" s="6"/>
-      <c r="M106" s="6"/>
-      <c r="N106" s="6"/>
-      <c r="O106" s="6"/>
-      <c r="P106" s="6"/>
-      <c r="Q106" s="6"/>
-      <c r="R106" s="6"/>
-      <c r="S106" s="6"/>
-      <c r="T106" s="6"/>
-    </row>
-    <row r="107" customFormat="false" ht="252.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="5" t="s">
+    </row>
+    <row r="107" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="6" t="s">
         <v>242</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4"/>
-      <c r="E107" s="4"/>
-      <c r="F107" s="4"/>
-      <c r="G107" s="4"/>
-      <c r="H107" s="4"/>
-      <c r="I107" s="4"/>
-      <c r="J107" s="4"/>
-      <c r="K107" s="4"/>
-      <c r="L107" s="4"/>
-      <c r="M107" s="4"/>
-      <c r="N107" s="4"/>
-      <c r="O107" s="4"/>
-      <c r="P107" s="4"/>
-      <c r="Q107" s="4"/>
-      <c r="R107" s="4"/>
-      <c r="S107" s="4"/>
-      <c r="T107" s="4"/>
-    </row>
-    <row r="108" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="6" t="s">
+      <c r="C107" s="6"/>
+      <c r="D107" s="6"/>
+      <c r="E107" s="6"/>
+      <c r="F107" s="6"/>
+      <c r="G107" s="6"/>
+      <c r="H107" s="6"/>
+      <c r="I107" s="6"/>
+      <c r="J107" s="6"/>
+      <c r="K107" s="6"/>
+      <c r="L107" s="6"/>
+      <c r="M107" s="6"/>
+      <c r="N107" s="6"/>
+      <c r="O107" s="6"/>
+      <c r="P107" s="6"/>
+      <c r="Q107" s="6"/>
+      <c r="R107" s="6"/>
+      <c r="S107" s="6"/>
+      <c r="T107" s="6"/>
+    </row>
+    <row r="108" customFormat="false" ht="252.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="5" t="s">
         <v>244</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="C108" s="6"/>
-      <c r="D108" s="6"/>
-      <c r="E108" s="6"/>
-      <c r="F108" s="6"/>
-      <c r="G108" s="6"/>
-      <c r="H108" s="6"/>
-      <c r="I108" s="6"/>
-      <c r="J108" s="6"/>
-      <c r="K108" s="6"/>
-      <c r="L108" s="6"/>
-      <c r="M108" s="6"/>
-      <c r="N108" s="6"/>
-      <c r="O108" s="6"/>
-      <c r="P108" s="6"/>
-      <c r="Q108" s="6"/>
-      <c r="R108" s="6"/>
-      <c r="S108" s="6"/>
-      <c r="T108" s="6"/>
-    </row>
-    <row r="109" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1" t="s">
+      <c r="C108" s="4"/>
+      <c r="D108" s="4"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="4"/>
+      <c r="H108" s="4"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
+      <c r="K108" s="4"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4"/>
+      <c r="N108" s="4"/>
+      <c r="O108" s="4"/>
+      <c r="P108" s="4"/>
+      <c r="Q108" s="4"/>
+      <c r="R108" s="4"/>
+      <c r="S108" s="4"/>
+      <c r="T108" s="4"/>
+    </row>
+    <row r="109" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="6" t="s">
         <v>246</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="110" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C109" s="6"/>
+      <c r="D109" s="6"/>
+      <c r="E109" s="6"/>
+      <c r="F109" s="6"/>
+      <c r="G109" s="6"/>
+      <c r="H109" s="6"/>
+      <c r="I109" s="6"/>
+      <c r="J109" s="6"/>
+      <c r="K109" s="6"/>
+      <c r="L109" s="6"/>
+      <c r="M109" s="6"/>
+      <c r="N109" s="6"/>
+      <c r="O109" s="6"/>
+      <c r="P109" s="6"/>
+      <c r="Q109" s="6"/>
+      <c r="R109" s="6"/>
+      <c r="S109" s="6"/>
+      <c r="T109" s="6"/>
+    </row>
+    <row r="110" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
         <v>248</v>
       </c>
@@ -5805,7 +5842,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
         <v>250</v>
       </c>
@@ -5813,31 +5850,13 @@
         <v>251</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="6" t="s">
+    <row r="112" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="1" t="s">
         <v>252</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C112" s="6"/>
-      <c r="D112" s="6"/>
-      <c r="E112" s="6"/>
-      <c r="F112" s="6"/>
-      <c r="G112" s="6"/>
-      <c r="H112" s="6"/>
-      <c r="I112" s="6"/>
-      <c r="J112" s="6"/>
-      <c r="K112" s="6"/>
-      <c r="L112" s="6"/>
-      <c r="M112" s="6"/>
-      <c r="N112" s="6"/>
-      <c r="O112" s="6"/>
-      <c r="P112" s="6"/>
-      <c r="Q112" s="6"/>
-      <c r="R112" s="6"/>
-      <c r="S112" s="6"/>
-      <c r="T112" s="6"/>
     </row>
     <row r="113" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="6" t="s">
@@ -5865,77 +5884,95 @@
       <c r="S113" s="6"/>
       <c r="T113" s="6"/>
     </row>
-    <row r="114" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1" t="s">
+    <row r="114" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="6" t="s">
         <v>256</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="C114" s="6"/>
+      <c r="D114" s="6"/>
+      <c r="E114" s="6"/>
+      <c r="F114" s="6"/>
+      <c r="G114" s="6"/>
+      <c r="H114" s="6"/>
+      <c r="I114" s="6"/>
+      <c r="J114" s="6"/>
+      <c r="K114" s="6"/>
+      <c r="L114" s="6"/>
+      <c r="M114" s="6"/>
+      <c r="N114" s="6"/>
+      <c r="O114" s="6"/>
+      <c r="P114" s="6"/>
+      <c r="Q114" s="6"/>
+      <c r="R114" s="6"/>
+      <c r="S114" s="6"/>
+      <c r="T114" s="6"/>
+    </row>
+    <row r="115" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="D114" s="4" t="s">
+      <c r="B115" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="E114" s="4" t="s">
+      <c r="C115" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="F114" s="4" t="s">
+      <c r="D115" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="G114" s="4" t="s">
+      <c r="E115" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="H114" s="4" t="s">
+      <c r="F115" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="I114" s="4" t="s">
+      <c r="G115" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="J114" s="4" t="s">
+      <c r="H115" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="K114" s="4" t="s">
+      <c r="I115" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="L114" s="4" t="s">
+      <c r="J115" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="M114" s="4" t="s">
+      <c r="K115" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="N114" s="4" t="s">
+      <c r="L115" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="O114" s="4" t="s">
+      <c r="M115" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="P114" s="4" t="s">
+      <c r="N115" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="Q114" s="4" t="s">
+      <c r="O115" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="R114" s="4" t="s">
+      <c r="P115" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="S114" s="4" t="s">
+      <c r="Q115" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="T114" s="4" t="s">
+      <c r="R115" s="4" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="115" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1" t="s">
+      <c r="S115" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="T115" s="4" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
         <v>278</v>
       </c>
@@ -5943,41 +5980,41 @@
         <v>279</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="6" t="s">
+    <row r="117" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="s">
         <v>280</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="C117" s="6"/>
-      <c r="D117" s="6"/>
-      <c r="E117" s="6"/>
-      <c r="F117" s="6"/>
-      <c r="G117" s="6"/>
-      <c r="H117" s="6"/>
-      <c r="I117" s="6"/>
-      <c r="J117" s="6"/>
-      <c r="K117" s="6"/>
-      <c r="L117" s="6"/>
-      <c r="M117" s="6"/>
-      <c r="N117" s="6"/>
-      <c r="O117" s="6"/>
-      <c r="P117" s="6"/>
-      <c r="Q117" s="6"/>
-      <c r="R117" s="6"/>
-      <c r="S117" s="6"/>
-      <c r="T117" s="6"/>
-    </row>
-    <row r="118" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="1" t="s">
+    </row>
+    <row r="118" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="B118" s="7" t="s">
+      <c r="B118" s="4" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="119" customFormat="false" ht="54.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C118" s="6"/>
+      <c r="D118" s="6"/>
+      <c r="E118" s="6"/>
+      <c r="F118" s="6"/>
+      <c r="G118" s="6"/>
+      <c r="H118" s="6"/>
+      <c r="I118" s="6"/>
+      <c r="J118" s="6"/>
+      <c r="K118" s="6"/>
+      <c r="L118" s="6"/>
+      <c r="M118" s="6"/>
+      <c r="N118" s="6"/>
+      <c r="O118" s="6"/>
+      <c r="P118" s="6"/>
+      <c r="Q118" s="6"/>
+      <c r="R118" s="6"/>
+      <c r="S118" s="6"/>
+      <c r="T118" s="6"/>
+    </row>
+    <row r="119" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
         <v>284</v>
       </c>
@@ -5985,85 +6022,85 @@
         <v>285</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="54.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B120" s="4" t="s">
+      <c r="B120" s="7" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B121" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="H121" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="I121" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="J121" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="K121" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="L121" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="M121" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="N121" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="O121" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="P121" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q121" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="R121" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="S121" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="T121" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B122" s="1" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="123" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="M122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="N122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="O122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="P122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="R122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="S122" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="T122" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
         <v>292</v>
       </c>
@@ -6071,11 +6108,11 @@
         <v>293</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B124" s="4" t="s">
         <v>295</v>
       </c>
     </row>
@@ -6087,68 +6124,68 @@
         <v>297</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B126" s="4" t="s">
+      <c r="B126" s="1" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
         <v>300</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="AX127" s="3"/>
-      <c r="AY127" s="3"/>
-      <c r="AZ127" s="3"/>
-      <c r="BA127" s="3"/>
-      <c r="BB127" s="3"/>
-      <c r="BC127" s="3"/>
-      <c r="BD127" s="3"/>
-      <c r="BE127" s="3"/>
-      <c r="BF127" s="3"/>
-      <c r="BG127" s="3"/>
-      <c r="BH127" s="3"/>
-      <c r="BI127" s="3"/>
-      <c r="BJ127" s="3"/>
-      <c r="BK127" s="3"/>
-      <c r="BL127" s="3"/>
-      <c r="BM127" s="3"/>
-      <c r="BN127" s="3"/>
-      <c r="BO127" s="3"/>
-      <c r="BP127" s="3"/>
-      <c r="BQ127" s="3"/>
-      <c r="BR127" s="3"/>
-      <c r="BS127" s="3"/>
-      <c r="BT127" s="3"/>
-      <c r="BU127" s="3"/>
-      <c r="BV127" s="3"/>
-      <c r="BW127" s="3"/>
-      <c r="BX127" s="3"/>
-      <c r="BY127" s="3"/>
-      <c r="BZ127" s="3"/>
-      <c r="CA127" s="3"/>
-      <c r="CB127" s="3"/>
-      <c r="CC127" s="3"/>
-      <c r="CD127" s="3"/>
-      <c r="CE127" s="3"/>
-      <c r="CF127" s="3"/>
-      <c r="CG127" s="3"/>
-      <c r="CH127" s="3"/>
-      <c r="CI127" s="3"/>
-      <c r="CJ127" s="3"/>
-    </row>
-    <row r="128" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="128" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
         <v>302</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>303</v>
       </c>
+      <c r="AX128" s="3"/>
+      <c r="AY128" s="3"/>
+      <c r="AZ128" s="3"/>
+      <c r="BA128" s="3"/>
+      <c r="BB128" s="3"/>
+      <c r="BC128" s="3"/>
+      <c r="BD128" s="3"/>
+      <c r="BE128" s="3"/>
+      <c r="BF128" s="3"/>
+      <c r="BG128" s="3"/>
+      <c r="BH128" s="3"/>
+      <c r="BI128" s="3"/>
+      <c r="BJ128" s="3"/>
+      <c r="BK128" s="3"/>
+      <c r="BL128" s="3"/>
+      <c r="BM128" s="3"/>
+      <c r="BN128" s="3"/>
+      <c r="BO128" s="3"/>
+      <c r="BP128" s="3"/>
+      <c r="BQ128" s="3"/>
+      <c r="BR128" s="3"/>
+      <c r="BS128" s="3"/>
+      <c r="BT128" s="3"/>
+      <c r="BU128" s="3"/>
+      <c r="BV128" s="3"/>
+      <c r="BW128" s="3"/>
+      <c r="BX128" s="3"/>
+      <c r="BY128" s="3"/>
+      <c r="BZ128" s="3"/>
+      <c r="CA128" s="3"/>
+      <c r="CB128" s="3"/>
+      <c r="CC128" s="3"/>
+      <c r="CD128" s="3"/>
+      <c r="CE128" s="3"/>
+      <c r="CF128" s="3"/>
+      <c r="CG128" s="3"/>
+      <c r="CH128" s="3"/>
+      <c r="CI128" s="3"/>
+      <c r="CJ128" s="3"/>
     </row>
     <row r="129" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
@@ -6157,47 +6194,8 @@
       <c r="B129" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="AX129" s="3"/>
-      <c r="AY129" s="3"/>
-      <c r="AZ129" s="3"/>
-      <c r="BA129" s="3"/>
-      <c r="BB129" s="3"/>
-      <c r="BC129" s="3"/>
-      <c r="BD129" s="3"/>
-      <c r="BE129" s="3"/>
-      <c r="BF129" s="3"/>
-      <c r="BG129" s="3"/>
-      <c r="BH129" s="3"/>
-      <c r="BI129" s="3"/>
-      <c r="BJ129" s="3"/>
-      <c r="BK129" s="3"/>
-      <c r="BL129" s="3"/>
-      <c r="BM129" s="3"/>
-      <c r="BN129" s="3"/>
-      <c r="BO129" s="3"/>
-      <c r="BP129" s="3"/>
-      <c r="BQ129" s="3"/>
-      <c r="BR129" s="3"/>
-      <c r="BS129" s="3"/>
-      <c r="BT129" s="3"/>
-      <c r="BU129" s="3"/>
-      <c r="BV129" s="3"/>
-      <c r="BW129" s="3"/>
-      <c r="BX129" s="3"/>
-      <c r="BY129" s="3"/>
-      <c r="BZ129" s="3"/>
-      <c r="CA129" s="3"/>
-      <c r="CB129" s="3"/>
-      <c r="CC129" s="3"/>
-      <c r="CD129" s="3"/>
-      <c r="CE129" s="3"/>
-      <c r="CF129" s="3"/>
-      <c r="CG129" s="3"/>
-      <c r="CH129" s="3"/>
-      <c r="CI129" s="3"/>
-      <c r="CJ129" s="3"/>
-    </row>
-    <row r="130" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="130" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
         <v>306</v>
       </c>
@@ -6244,78 +6242,117 @@
       <c r="CI130" s="3"/>
       <c r="CJ130" s="3"/>
     </row>
-    <row r="131" s="3" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
         <v>308</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
-      <c r="E131" s="1"/>
-      <c r="F131" s="1"/>
-      <c r="G131" s="1"/>
-      <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1"/>
-      <c r="K131" s="1"/>
-      <c r="L131" s="1"/>
-      <c r="M131" s="1"/>
-      <c r="N131" s="1"/>
-      <c r="O131" s="1"/>
-      <c r="P131" s="1"/>
-      <c r="Q131" s="1"/>
-      <c r="R131" s="1"/>
-      <c r="S131" s="1"/>
-      <c r="T131" s="1"/>
-      <c r="U131" s="1"/>
-      <c r="V131" s="1"/>
-      <c r="W131" s="1"/>
-      <c r="X131" s="1"/>
-      <c r="Y131" s="1"/>
-      <c r="Z131" s="1"/>
-      <c r="AA131" s="1"/>
-      <c r="AB131" s="1"/>
-      <c r="AC131" s="1"/>
-      <c r="AD131" s="1"/>
-      <c r="AE131" s="1"/>
-      <c r="AF131" s="1"/>
-      <c r="AG131" s="1"/>
-      <c r="AH131" s="1"/>
-      <c r="AI131" s="1"/>
-      <c r="AJ131" s="1"/>
-      <c r="AK131" s="1"/>
-      <c r="AL131" s="1"/>
-      <c r="AM131" s="1"/>
-      <c r="AN131" s="1"/>
-      <c r="AO131" s="1"/>
-      <c r="AP131" s="1"/>
-      <c r="AQ131" s="1"/>
-      <c r="AR131" s="1"/>
-      <c r="AS131" s="1"/>
-      <c r="AT131" s="1"/>
-      <c r="AU131" s="1"/>
-      <c r="AV131" s="1"/>
-      <c r="AW131" s="1"/>
-    </row>
-    <row r="132" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>309</v>
+      </c>
+      <c r="AX131" s="3"/>
+      <c r="AY131" s="3"/>
+      <c r="AZ131" s="3"/>
+      <c r="BA131" s="3"/>
+      <c r="BB131" s="3"/>
+      <c r="BC131" s="3"/>
+      <c r="BD131" s="3"/>
+      <c r="BE131" s="3"/>
+      <c r="BF131" s="3"/>
+      <c r="BG131" s="3"/>
+      <c r="BH131" s="3"/>
+      <c r="BI131" s="3"/>
+      <c r="BJ131" s="3"/>
+      <c r="BK131" s="3"/>
+      <c r="BL131" s="3"/>
+      <c r="BM131" s="3"/>
+      <c r="BN131" s="3"/>
+      <c r="BO131" s="3"/>
+      <c r="BP131" s="3"/>
+      <c r="BQ131" s="3"/>
+      <c r="BR131" s="3"/>
+      <c r="BS131" s="3"/>
+      <c r="BT131" s="3"/>
+      <c r="BU131" s="3"/>
+      <c r="BV131" s="3"/>
+      <c r="BW131" s="3"/>
+      <c r="BX131" s="3"/>
+      <c r="BY131" s="3"/>
+      <c r="BZ131" s="3"/>
+      <c r="CA131" s="3"/>
+      <c r="CB131" s="3"/>
+      <c r="CC131" s="3"/>
+      <c r="CD131" s="3"/>
+      <c r="CE131" s="3"/>
+      <c r="CF131" s="3"/>
+      <c r="CG131" s="3"/>
+      <c r="CH131" s="3"/>
+      <c r="CI131" s="3"/>
+      <c r="CJ131" s="3"/>
+    </row>
+    <row r="132" s="3" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>162</v>
+      </c>
+      <c r="C132" s="1"/>
+      <c r="D132" s="1"/>
+      <c r="E132" s="1"/>
+      <c r="F132" s="1"/>
+      <c r="G132" s="1"/>
+      <c r="H132" s="1"/>
+      <c r="I132" s="1"/>
+      <c r="J132" s="1"/>
+      <c r="K132" s="1"/>
+      <c r="L132" s="1"/>
+      <c r="M132" s="1"/>
+      <c r="N132" s="1"/>
+      <c r="O132" s="1"/>
+      <c r="P132" s="1"/>
+      <c r="Q132" s="1"/>
+      <c r="R132" s="1"/>
+      <c r="S132" s="1"/>
+      <c r="T132" s="1"/>
+      <c r="U132" s="1"/>
+      <c r="V132" s="1"/>
+      <c r="W132" s="1"/>
+      <c r="X132" s="1"/>
+      <c r="Y132" s="1"/>
+      <c r="Z132" s="1"/>
+      <c r="AA132" s="1"/>
+      <c r="AB132" s="1"/>
+      <c r="AC132" s="1"/>
+      <c r="AD132" s="1"/>
+      <c r="AE132" s="1"/>
+      <c r="AF132" s="1"/>
+      <c r="AG132" s="1"/>
+      <c r="AH132" s="1"/>
+      <c r="AI132" s="1"/>
+      <c r="AJ132" s="1"/>
+      <c r="AK132" s="1"/>
+      <c r="AL132" s="1"/>
+      <c r="AM132" s="1"/>
+      <c r="AN132" s="1"/>
+      <c r="AO132" s="1"/>
+      <c r="AP132" s="1"/>
+      <c r="AQ132" s="1"/>
+      <c r="AR132" s="1"/>
+      <c r="AS132" s="1"/>
+      <c r="AT132" s="1"/>
+      <c r="AU132" s="1"/>
+      <c r="AV132" s="1"/>
+      <c r="AW132" s="1"/>
+    </row>
+    <row r="133" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B133" s="8" t="s">
+      <c r="B133" s="4" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
         <v>313</v>
       </c>
@@ -6323,16 +6360,24 @@
         <v>314</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B135" s="4" t="s">
+      <c r="B135" s="8" t="s">
         <v>316</v>
       </c>
     </row>
+    <row r="136" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:T134"/>
+  <autoFilter ref="A2:T135"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/JP (Exclude Game)/Data/chara_talk.xlsx
+++ b/JP (Exclude Game)/Data/chara_talk.xlsx
@@ -11,7 +11,7 @@
     <sheet name="1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$135</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$136</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="321">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -140,6 +140,15 @@
   </si>
   <si>
     <t xml:space="preserve">夢人</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ahoy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アホーイ！
+出航！
+乗り込めー！
+行こう！</t>
   </si>
   <si>
     <t xml:space="preserve">fusion</t>
@@ -1898,9 +1907,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>2079720</xdr:colOff>
+      <xdr:colOff>2079360</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>123840</xdr:rowOff>
+      <xdr:rowOff>123480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1910,7 +1919,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="50980320" cy="123840"/>
+          <a:ext cx="50979960" cy="123480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1943,9 +1952,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>517320</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>316080</xdr:rowOff>
+      <xdr:colOff>516960</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>315720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1955,7 +1964,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="55188360" cy="46053360"/>
+          <a:ext cx="55188000" cy="46602000"/>
         </a:xfrm>
         <a:solidFill>
           <a:srgbClr val="ffffff"/>
@@ -2090,7 +2099,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CJ136"/>
+  <dimension ref="A1:CJ137"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.04"/>
@@ -2360,7 +2369,7 @@
       <c r="AU4" s="3"/>
       <c r="AV4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>41</v>
       </c>
@@ -2396,7 +2405,7 @@
       <c r="AU5" s="3"/>
       <c r="AV5" s="3"/>
     </row>
-    <row r="6" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>43</v>
       </c>
@@ -2432,11 +2441,11 @@
       <c r="AU6" s="3"/>
       <c r="AV6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>46</v>
       </c>
       <c r="U7" s="3"/>
@@ -2468,11 +2477,11 @@
       <c r="AU7" s="3"/>
       <c r="AV7" s="3"/>
     </row>
-    <row r="8" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>48</v>
       </c>
       <c r="U8" s="3"/>
@@ -2504,7 +2513,7 @@
       <c r="AU8" s="3"/>
       <c r="AV8" s="3"/>
     </row>
-    <row r="9" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>49</v>
       </c>
@@ -2540,11 +2549,11 @@
       <c r="AU9" s="3"/>
       <c r="AV9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="4" t="s">
         <v>52</v>
       </c>
       <c r="U10" s="3"/>
@@ -2648,11 +2657,11 @@
       <c r="AU12" s="3"/>
       <c r="AV12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="1" t="s">
         <v>58</v>
       </c>
       <c r="U13" s="3"/>
@@ -2684,7 +2693,7 @@
       <c r="AU13" s="3"/>
       <c r="AV13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>59</v>
       </c>
@@ -2720,7 +2729,7 @@
       <c r="AU14" s="3"/>
       <c r="AV14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>61</v>
       </c>
@@ -2756,7 +2765,7 @@
       <c r="AU15" s="3"/>
       <c r="AV15" s="3"/>
     </row>
-    <row r="16" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>63</v>
       </c>
@@ -2828,7 +2837,7 @@
       <c r="AU17" s="3"/>
       <c r="AV17" s="3"/>
     </row>
-    <row r="18" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>67</v>
       </c>
@@ -2864,7 +2873,7 @@
       <c r="AU18" s="3"/>
       <c r="AV18" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>69</v>
       </c>
@@ -2900,7 +2909,7 @@
       <c r="AU19" s="3"/>
       <c r="AV19" s="3"/>
     </row>
-    <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>71</v>
       </c>
@@ -2936,7 +2945,7 @@
       <c r="AU20" s="3"/>
       <c r="AV20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>73</v>
       </c>
@@ -2972,7 +2981,7 @@
       <c r="AU21" s="3"/>
       <c r="AV21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>75</v>
       </c>
@@ -3008,8 +3017,8 @@
       <c r="AU22" s="3"/>
       <c r="AV22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+    <row r="23" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -3044,14 +3053,13 @@
       <c r="AU23" s="3"/>
       <c r="AV23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
         <v>79</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C24" s="4"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -3081,13 +3089,14 @@
       <c r="AU24" s="3"/>
       <c r="AV24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
         <v>81</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>82</v>
       </c>
+      <c r="C25" s="4"/>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
@@ -3118,13 +3127,12 @@
       <c r="AV25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C26" s="4"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -3162,7 +3170,6 @@
         <v>86</v>
       </c>
       <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -3192,7 +3199,7 @@
       <c r="AU27" s="3"/>
       <c r="AV27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>87</v>
       </c>
@@ -3230,7 +3237,7 @@
       <c r="AU28" s="3"/>
       <c r="AV28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>89</v>
       </c>
@@ -3268,7 +3275,7 @@
       <c r="AU29" s="3"/>
       <c r="AV29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>91</v>
       </c>
@@ -3276,6 +3283,7 @@
         <v>92</v>
       </c>
       <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -3305,7 +3313,7 @@
       <c r="AU30" s="3"/>
       <c r="AV30" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>93</v>
       </c>
@@ -3342,13 +3350,14 @@
       <c r="AU31" s="3"/>
       <c r="AV31" s="3"/>
     </row>
-    <row r="32" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>95</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>96</v>
       </c>
+      <c r="C32" s="4"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
@@ -3378,7 +3387,7 @@
       <c r="AU32" s="3"/>
       <c r="AV32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>97</v>
       </c>
@@ -3414,15 +3423,13 @@
       <c r="AU33" s="3"/>
       <c r="AV33" s="3"/>
     </row>
-    <row r="34" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>99</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
@@ -3452,13 +3459,15 @@
       <c r="AU34" s="3"/>
       <c r="AV34" s="3"/>
     </row>
-    <row r="35" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>101</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>102</v>
       </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -3488,11 +3497,11 @@
       <c r="AU35" s="3"/>
       <c r="AV35" s="3"/>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="4" t="s">
         <v>104</v>
       </c>
       <c r="U36" s="3"/>
@@ -3524,14 +3533,13 @@
       <c r="AU36" s="3"/>
       <c r="AV36" s="3"/>
     </row>
-    <row r="37" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C37" s="4"/>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
@@ -3561,8 +3569,8 @@
       <c r="AU37" s="3"/>
       <c r="AV37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
+    <row r="38" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
         <v>107</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -3598,14 +3606,14 @@
       <c r="AU38" s="3"/>
       <c r="AV38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>109</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D39" s="4"/>
+      <c r="C39" s="4"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
@@ -3635,14 +3643,14 @@
       <c r="AU39" s="3"/>
       <c r="AV39" s="3"/>
     </row>
-    <row r="40" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
@@ -3672,14 +3680,14 @@
       <c r="AU40" s="3"/>
       <c r="AV40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E41" s="4"/>
+      <c r="C41" s="4"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
@@ -3709,13 +3717,14 @@
       <c r="AU41" s="3"/>
       <c r="AV41" s="3"/>
     </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>115</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>116</v>
       </c>
+      <c r="E42" s="4"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
@@ -3745,7 +3754,7 @@
       <c r="AU42" s="3"/>
       <c r="AV42" s="3"/>
     </row>
-    <row r="43" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>117</v>
       </c>
@@ -3781,7 +3790,7 @@
       <c r="AU43" s="3"/>
       <c r="AV43" s="3"/>
     </row>
-    <row r="44" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>119</v>
       </c>
@@ -3817,7 +3826,7 @@
       <c r="AU44" s="3"/>
       <c r="AV44" s="3"/>
     </row>
-    <row r="45" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>121</v>
       </c>
@@ -3853,7 +3862,7 @@
       <c r="AU45" s="3"/>
       <c r="AV45" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>123</v>
       </c>
@@ -3889,15 +3898,13 @@
       <c r="AU46" s="3"/>
       <c r="AV46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>125</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
@@ -3927,7 +3934,7 @@
       <c r="AU47" s="3"/>
       <c r="AV47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>127</v>
       </c>
@@ -3965,14 +3972,15 @@
       <c r="AU48" s="3"/>
       <c r="AV48" s="3"/>
     </row>
-    <row r="49" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>129</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
@@ -4002,13 +4010,14 @@
       <c r="AU49" s="3"/>
       <c r="AV49" s="3"/>
     </row>
-    <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
         <v>131</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>132</v>
       </c>
+      <c r="F50" s="4"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
@@ -4110,11 +4119,11 @@
       <c r="AU52" s="3"/>
       <c r="AV52" s="3"/>
     </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="4" t="s">
         <v>138</v>
       </c>
       <c r="U53" s="3"/>
@@ -4146,11 +4155,11 @@
       <c r="AU53" s="3"/>
       <c r="AV53" s="3"/>
     </row>
-    <row r="54" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="1" t="s">
         <v>140</v>
       </c>
       <c r="U54" s="3"/>
@@ -4182,7 +4191,7 @@
       <c r="AU54" s="3"/>
       <c r="AV54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
         <v>141</v>
       </c>
@@ -4218,7 +4227,7 @@
       <c r="AU55" s="3"/>
       <c r="AV55" s="3"/>
     </row>
-    <row r="56" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
         <v>143</v>
       </c>
@@ -4254,7 +4263,7 @@
       <c r="AU56" s="3"/>
       <c r="AV56" s="3"/>
     </row>
-    <row r="57" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
         <v>145</v>
       </c>
@@ -4291,30 +4300,12 @@
       <c r="AV57" s="3"/>
     </row>
     <row r="58" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="1" t="s">
         <v>147</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
-      <c r="M58" s="6"/>
-      <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
-      <c r="P58" s="6"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="6"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
       <c r="U58" s="3"/>
       <c r="V58" s="3"/>
       <c r="W58" s="3"/>
@@ -4344,11 +4335,11 @@
       <c r="AU58" s="3"/>
       <c r="AV58" s="3"/>
     </row>
-    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="4" t="s">
         <v>150</v>
       </c>
       <c r="C59" s="6"/>
@@ -4398,11 +4389,11 @@
       <c r="AU59" s="3"/>
       <c r="AV59" s="3"/>
     </row>
-    <row r="60" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="6" t="s">
         <v>152</v>
       </c>
       <c r="C60" s="6"/>
@@ -4452,13 +4443,31 @@
       <c r="AU60" s="3"/>
       <c r="AV60" s="3"/>
     </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
+    <row r="61" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="4" t="s">
         <v>154</v>
       </c>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
+      <c r="N61" s="6"/>
+      <c r="O61" s="6"/>
+      <c r="P61" s="6"/>
+      <c r="Q61" s="6"/>
+      <c r="R61" s="6"/>
+      <c r="S61" s="6"/>
+      <c r="T61" s="6"/>
       <c r="U61" s="3"/>
       <c r="V61" s="3"/>
       <c r="W61" s="3"/>
@@ -4596,11 +4605,11 @@
       <c r="AU64" s="3"/>
       <c r="AV64" s="3"/>
     </row>
-    <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="1" t="s">
         <v>162</v>
       </c>
       <c r="U65" s="3"/>
@@ -4632,7 +4641,7 @@
       <c r="AU65" s="3"/>
       <c r="AV65" s="3"/>
     </row>
-    <row r="66" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
         <v>163</v>
       </c>
@@ -4668,11 +4677,11 @@
       <c r="AU66" s="3"/>
       <c r="AV66" s="3"/>
     </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="4" t="s">
         <v>166</v>
       </c>
       <c r="U67" s="3"/>
@@ -4704,11 +4713,11 @@
       <c r="AU67" s="3"/>
       <c r="AV67" s="3"/>
     </row>
-    <row r="68" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="1" t="s">
         <v>168</v>
       </c>
       <c r="U68" s="3"/>
@@ -4740,11 +4749,11 @@
       <c r="AU68" s="3"/>
       <c r="AV68" s="3"/>
     </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="4" t="s">
         <v>170</v>
       </c>
       <c r="U69" s="3"/>
@@ -4848,11 +4857,11 @@
       <c r="AU71" s="3"/>
       <c r="AV71" s="3"/>
     </row>
-    <row r="72" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="1" t="s">
         <v>176</v>
       </c>
       <c r="U72" s="3"/>
@@ -4884,9 +4893,12 @@
       <c r="AU72" s="3"/>
       <c r="AV72" s="3"/>
     </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>177</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="U73" s="3"/>
       <c r="V73" s="3"/>
@@ -4917,11 +4929,8 @@
       <c r="AU73" s="3"/>
       <c r="AV73" s="3"/>
     </row>
-    <row r="74" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B74" s="4" t="s">
         <v>179</v>
       </c>
       <c r="U74" s="3"/>
@@ -4953,11 +4962,11 @@
       <c r="AU74" s="3"/>
       <c r="AV74" s="3"/>
     </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="4" t="s">
         <v>181</v>
       </c>
       <c r="U75" s="3"/>
@@ -4989,12 +4998,12 @@
       <c r="AU75" s="3"/>
       <c r="AV75" s="3"/>
     </row>
-    <row r="76" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B76" s="4" t="s">
-        <v>162</v>
+      <c r="B76" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="U76" s="3"/>
       <c r="V76" s="3"/>
@@ -5025,12 +5034,12 @@
       <c r="AU76" s="3"/>
       <c r="AV76" s="3"/>
     </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B77" s="1" t="s">
         <v>184</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="U77" s="3"/>
       <c r="V77" s="3"/>
@@ -5061,11 +5070,11 @@
       <c r="AU77" s="3"/>
       <c r="AV77" s="3"/>
     </row>
-    <row r="78" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="1" t="s">
         <v>186</v>
       </c>
       <c r="U78" s="3"/>
@@ -5097,7 +5106,7 @@
       <c r="AU78" s="3"/>
       <c r="AV78" s="3"/>
     </row>
-    <row r="79" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
         <v>187</v>
       </c>
@@ -5133,7 +5142,7 @@
       <c r="AU79" s="3"/>
       <c r="AV79" s="3"/>
     </row>
-    <row r="80" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
         <v>189</v>
       </c>
@@ -5169,7 +5178,7 @@
       <c r="AU80" s="3"/>
       <c r="AV80" s="3"/>
     </row>
-    <row r="81" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
         <v>191</v>
       </c>
@@ -5205,7 +5214,7 @@
       <c r="AU81" s="3"/>
       <c r="AV81" s="3"/>
     </row>
-    <row r="82" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
         <v>193</v>
       </c>
@@ -5241,11 +5250,11 @@
       <c r="AU82" s="3"/>
       <c r="AV82" s="3"/>
     </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="4" t="s">
         <v>196</v>
       </c>
       <c r="U83" s="3"/>
@@ -5277,11 +5286,11 @@
       <c r="AU83" s="3"/>
       <c r="AV83" s="3"/>
     </row>
-    <row r="84" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="1" t="s">
         <v>198</v>
       </c>
       <c r="U84" s="3"/>
@@ -5313,7 +5322,7 @@
       <c r="AU84" s="3"/>
       <c r="AV84" s="3"/>
     </row>
-    <row r="85" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
         <v>199</v>
       </c>
@@ -5349,11 +5358,11 @@
       <c r="AU85" s="3"/>
       <c r="AV85" s="3"/>
     </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="4" t="s">
         <v>202</v>
       </c>
       <c r="U86" s="3"/>
@@ -5457,7 +5466,7 @@
       <c r="AU88" s="3"/>
       <c r="AV88" s="3"/>
     </row>
-    <row r="89" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
         <v>207</v>
       </c>
@@ -5493,7 +5502,7 @@
       <c r="AU89" s="3"/>
       <c r="AV89" s="3"/>
     </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
         <v>209</v>
       </c>
@@ -5529,11 +5538,11 @@
       <c r="AU90" s="3"/>
       <c r="AV90" s="3"/>
     </row>
-    <row r="91" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="1" t="s">
         <v>212</v>
       </c>
       <c r="U91" s="3"/>
@@ -5565,11 +5574,11 @@
       <c r="AU91" s="3"/>
       <c r="AV91" s="3"/>
     </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="4" t="s">
         <v>214</v>
       </c>
       <c r="U92" s="3"/>
@@ -5601,11 +5610,11 @@
       <c r="AU92" s="3"/>
       <c r="AV92" s="3"/>
     </row>
-    <row r="93" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="1" t="s">
         <v>216</v>
       </c>
       <c r="U93" s="3"/>
@@ -5637,13 +5646,41 @@
       <c r="AU93" s="3"/>
       <c r="AV93" s="3"/>
     </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B94" s="4" t="s">
         <v>218</v>
       </c>
+      <c r="U94" s="3"/>
+      <c r="V94" s="3"/>
+      <c r="W94" s="3"/>
+      <c r="X94" s="3"/>
+      <c r="Y94" s="3"/>
+      <c r="Z94" s="3"/>
+      <c r="AA94" s="3"/>
+      <c r="AB94" s="3"/>
+      <c r="AC94" s="3"/>
+      <c r="AD94" s="3"/>
+      <c r="AE94" s="3"/>
+      <c r="AF94" s="3"/>
+      <c r="AG94" s="3"/>
+      <c r="AH94" s="3"/>
+      <c r="AI94" s="3"/>
+      <c r="AJ94" s="3"/>
+      <c r="AK94" s="3"/>
+      <c r="AL94" s="3"/>
+      <c r="AM94" s="3"/>
+      <c r="AN94" s="3"/>
+      <c r="AO94" s="3"/>
+      <c r="AP94" s="3"/>
+      <c r="AQ94" s="3"/>
+      <c r="AR94" s="3"/>
+      <c r="AS94" s="3"/>
+      <c r="AT94" s="3"/>
+      <c r="AU94" s="3"/>
+      <c r="AV94" s="3"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
@@ -5657,16 +5694,16 @@
       <c r="A96" s="1" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="97" customFormat="false" ht="335.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B96" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B97" s="4" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="335.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
         <v>224</v>
       </c>
@@ -5674,7 +5711,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
         <v>226</v>
       </c>
@@ -5682,39 +5719,39 @@
         <v>227</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="6" t="s">
+    <row r="100" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
         <v>228</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="C100" s="6"/>
-      <c r="D100" s="6"/>
-      <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="6"/>
-      <c r="J100" s="6"/>
-      <c r="K100" s="6"/>
-      <c r="L100" s="6"/>
-      <c r="M100" s="6"/>
-      <c r="N100" s="6"/>
-      <c r="O100" s="6"/>
-      <c r="P100" s="6"/>
-      <c r="Q100" s="6"/>
-      <c r="R100" s="6"/>
-      <c r="S100" s="6"/>
-      <c r="T100" s="6"/>
-    </row>
-    <row r="101" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
+    </row>
+    <row r="101" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="6" t="s">
         <v>230</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>231</v>
       </c>
+      <c r="C101" s="6"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="6"/>
+      <c r="F101" s="6"/>
+      <c r="G101" s="6"/>
+      <c r="H101" s="6"/>
+      <c r="I101" s="6"/>
+      <c r="J101" s="6"/>
+      <c r="K101" s="6"/>
+      <c r="L101" s="6"/>
+      <c r="M101" s="6"/>
+      <c r="N101" s="6"/>
+      <c r="O101" s="6"/>
+      <c r="P101" s="6"/>
+      <c r="Q101" s="6"/>
+      <c r="R101" s="6"/>
+      <c r="S101" s="6"/>
+      <c r="T101" s="6"/>
     </row>
     <row r="102" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
@@ -5724,7 +5761,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
         <v>234</v>
       </c>
@@ -5732,7 +5769,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
         <v>236</v>
       </c>
@@ -5740,7 +5777,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
         <v>238</v>
       </c>
@@ -5748,7 +5785,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
         <v>240</v>
       </c>
@@ -5756,93 +5793,93 @@
         <v>241</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="6" t="s">
+    <row r="107" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="1" t="s">
         <v>242</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="C107" s="6"/>
-      <c r="D107" s="6"/>
-      <c r="E107" s="6"/>
-      <c r="F107" s="6"/>
-      <c r="G107" s="6"/>
-      <c r="H107" s="6"/>
-      <c r="I107" s="6"/>
-      <c r="J107" s="6"/>
-      <c r="K107" s="6"/>
-      <c r="L107" s="6"/>
-      <c r="M107" s="6"/>
-      <c r="N107" s="6"/>
-      <c r="O107" s="6"/>
-      <c r="P107" s="6"/>
-      <c r="Q107" s="6"/>
-      <c r="R107" s="6"/>
-      <c r="S107" s="6"/>
-      <c r="T107" s="6"/>
-    </row>
-    <row r="108" customFormat="false" ht="252.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="5" t="s">
+    </row>
+    <row r="108" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="6" t="s">
         <v>244</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="C108" s="4"/>
-      <c r="D108" s="4"/>
-      <c r="E108" s="4"/>
-      <c r="F108" s="4"/>
-      <c r="G108" s="4"/>
-      <c r="H108" s="4"/>
-      <c r="I108" s="4"/>
-      <c r="J108" s="4"/>
-      <c r="K108" s="4"/>
-      <c r="L108" s="4"/>
-      <c r="M108" s="4"/>
-      <c r="N108" s="4"/>
-      <c r="O108" s="4"/>
-      <c r="P108" s="4"/>
-      <c r="Q108" s="4"/>
-      <c r="R108" s="4"/>
-      <c r="S108" s="4"/>
-      <c r="T108" s="4"/>
-    </row>
-    <row r="109" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="6" t="s">
+      <c r="C108" s="6"/>
+      <c r="D108" s="6"/>
+      <c r="E108" s="6"/>
+      <c r="F108" s="6"/>
+      <c r="G108" s="6"/>
+      <c r="H108" s="6"/>
+      <c r="I108" s="6"/>
+      <c r="J108" s="6"/>
+      <c r="K108" s="6"/>
+      <c r="L108" s="6"/>
+      <c r="M108" s="6"/>
+      <c r="N108" s="6"/>
+      <c r="O108" s="6"/>
+      <c r="P108" s="6"/>
+      <c r="Q108" s="6"/>
+      <c r="R108" s="6"/>
+      <c r="S108" s="6"/>
+      <c r="T108" s="6"/>
+    </row>
+    <row r="109" customFormat="false" ht="252.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="5" t="s">
         <v>246</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C109" s="6"/>
-      <c r="D109" s="6"/>
-      <c r="E109" s="6"/>
-      <c r="F109" s="6"/>
-      <c r="G109" s="6"/>
-      <c r="H109" s="6"/>
-      <c r="I109" s="6"/>
-      <c r="J109" s="6"/>
-      <c r="K109" s="6"/>
-      <c r="L109" s="6"/>
-      <c r="M109" s="6"/>
-      <c r="N109" s="6"/>
-      <c r="O109" s="6"/>
-      <c r="P109" s="6"/>
-      <c r="Q109" s="6"/>
-      <c r="R109" s="6"/>
-      <c r="S109" s="6"/>
-      <c r="T109" s="6"/>
-    </row>
-    <row r="110" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="1" t="s">
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="4"/>
+      <c r="H109" s="4"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
+      <c r="K109" s="4"/>
+      <c r="L109" s="4"/>
+      <c r="M109" s="4"/>
+      <c r="N109" s="4"/>
+      <c r="O109" s="4"/>
+      <c r="P109" s="4"/>
+      <c r="Q109" s="4"/>
+      <c r="R109" s="4"/>
+      <c r="S109" s="4"/>
+      <c r="T109" s="4"/>
+    </row>
+    <row r="110" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="6" t="s">
         <v>248</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="111" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C110" s="6"/>
+      <c r="D110" s="6"/>
+      <c r="E110" s="6"/>
+      <c r="F110" s="6"/>
+      <c r="G110" s="6"/>
+      <c r="H110" s="6"/>
+      <c r="I110" s="6"/>
+      <c r="J110" s="6"/>
+      <c r="K110" s="6"/>
+      <c r="L110" s="6"/>
+      <c r="M110" s="6"/>
+      <c r="N110" s="6"/>
+      <c r="O110" s="6"/>
+      <c r="P110" s="6"/>
+      <c r="Q110" s="6"/>
+      <c r="R110" s="6"/>
+      <c r="S110" s="6"/>
+      <c r="T110" s="6"/>
+    </row>
+    <row r="111" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
         <v>250</v>
       </c>
@@ -5850,7 +5887,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
         <v>252</v>
       </c>
@@ -5858,31 +5895,13 @@
         <v>253</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="6" t="s">
+    <row r="113" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="1" t="s">
         <v>254</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="C113" s="6"/>
-      <c r="D113" s="6"/>
-      <c r="E113" s="6"/>
-      <c r="F113" s="6"/>
-      <c r="G113" s="6"/>
-      <c r="H113" s="6"/>
-      <c r="I113" s="6"/>
-      <c r="J113" s="6"/>
-      <c r="K113" s="6"/>
-      <c r="L113" s="6"/>
-      <c r="M113" s="6"/>
-      <c r="N113" s="6"/>
-      <c r="O113" s="6"/>
-      <c r="P113" s="6"/>
-      <c r="Q113" s="6"/>
-      <c r="R113" s="6"/>
-      <c r="S113" s="6"/>
-      <c r="T113" s="6"/>
     </row>
     <row r="114" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="6" t="s">
@@ -5910,77 +5929,95 @@
       <c r="S114" s="6"/>
       <c r="T114" s="6"/>
     </row>
-    <row r="115" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1" t="s">
+    <row r="115" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="6" t="s">
         <v>258</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="C115" s="6"/>
+      <c r="D115" s="6"/>
+      <c r="E115" s="6"/>
+      <c r="F115" s="6"/>
+      <c r="G115" s="6"/>
+      <c r="H115" s="6"/>
+      <c r="I115" s="6"/>
+      <c r="J115" s="6"/>
+      <c r="K115" s="6"/>
+      <c r="L115" s="6"/>
+      <c r="M115" s="6"/>
+      <c r="N115" s="6"/>
+      <c r="O115" s="6"/>
+      <c r="P115" s="6"/>
+      <c r="Q115" s="6"/>
+      <c r="R115" s="6"/>
+      <c r="S115" s="6"/>
+      <c r="T115" s="6"/>
+    </row>
+    <row r="116" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D115" s="4" t="s">
+      <c r="B116" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="E115" s="4" t="s">
+      <c r="C116" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="F115" s="4" t="s">
+      <c r="D116" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="G115" s="4" t="s">
+      <c r="E116" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="H115" s="4" t="s">
+      <c r="F116" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="I115" s="4" t="s">
+      <c r="G116" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="J115" s="4" t="s">
+      <c r="H116" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="K115" s="4" t="s">
+      <c r="I116" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="L115" s="4" t="s">
+      <c r="J116" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="M115" s="4" t="s">
+      <c r="K116" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="N115" s="4" t="s">
+      <c r="L116" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="O115" s="4" t="s">
+      <c r="M116" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="P115" s="4" t="s">
+      <c r="N116" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="Q115" s="4" t="s">
+      <c r="O116" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="R115" s="4" t="s">
+      <c r="P116" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="S115" s="4" t="s">
+      <c r="Q116" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="T115" s="4" t="s">
+      <c r="R116" s="4" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="116" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="1" t="s">
+      <c r="S116" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="T116" s="4" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
         <v>280</v>
       </c>
@@ -5988,41 +6025,41 @@
         <v>281</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="6" t="s">
+    <row r="118" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1" t="s">
         <v>282</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="C118" s="6"/>
-      <c r="D118" s="6"/>
-      <c r="E118" s="6"/>
-      <c r="F118" s="6"/>
-      <c r="G118" s="6"/>
-      <c r="H118" s="6"/>
-      <c r="I118" s="6"/>
-      <c r="J118" s="6"/>
-      <c r="K118" s="6"/>
-      <c r="L118" s="6"/>
-      <c r="M118" s="6"/>
-      <c r="N118" s="6"/>
-      <c r="O118" s="6"/>
-      <c r="P118" s="6"/>
-      <c r="Q118" s="6"/>
-      <c r="R118" s="6"/>
-      <c r="S118" s="6"/>
-      <c r="T118" s="6"/>
-    </row>
-    <row r="119" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="1" t="s">
+    </row>
+    <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="B119" s="7" t="s">
+      <c r="B119" s="4" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="120" customFormat="false" ht="54.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C119" s="6"/>
+      <c r="D119" s="6"/>
+      <c r="E119" s="6"/>
+      <c r="F119" s="6"/>
+      <c r="G119" s="6"/>
+      <c r="H119" s="6"/>
+      <c r="I119" s="6"/>
+      <c r="J119" s="6"/>
+      <c r="K119" s="6"/>
+      <c r="L119" s="6"/>
+      <c r="M119" s="6"/>
+      <c r="N119" s="6"/>
+      <c r="O119" s="6"/>
+      <c r="P119" s="6"/>
+      <c r="Q119" s="6"/>
+      <c r="R119" s="6"/>
+      <c r="S119" s="6"/>
+      <c r="T119" s="6"/>
+    </row>
+    <row r="120" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
         <v>286</v>
       </c>
@@ -6030,85 +6067,85 @@
         <v>287</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="54.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="B121" s="7" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B122" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="H122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="I122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="J122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="L122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="M122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="N122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="O122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="P122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="R122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="S122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="T122" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B123" s="4" t="s">
+      <c r="B123" s="1" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="124" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C123" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="L123" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="M123" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="N123" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="O123" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="P123" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q123" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="R123" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="S123" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="T123" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
         <v>294</v>
       </c>
@@ -6116,11 +6153,11 @@
         <v>295</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B125" s="4" t="s">
         <v>297</v>
       </c>
     </row>
@@ -6132,68 +6169,68 @@
         <v>299</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B127" s="4" t="s">
+      <c r="B127" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
         <v>302</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="AX128" s="3"/>
-      <c r="AY128" s="3"/>
-      <c r="AZ128" s="3"/>
-      <c r="BA128" s="3"/>
-      <c r="BB128" s="3"/>
-      <c r="BC128" s="3"/>
-      <c r="BD128" s="3"/>
-      <c r="BE128" s="3"/>
-      <c r="BF128" s="3"/>
-      <c r="BG128" s="3"/>
-      <c r="BH128" s="3"/>
-      <c r="BI128" s="3"/>
-      <c r="BJ128" s="3"/>
-      <c r="BK128" s="3"/>
-      <c r="BL128" s="3"/>
-      <c r="BM128" s="3"/>
-      <c r="BN128" s="3"/>
-      <c r="BO128" s="3"/>
-      <c r="BP128" s="3"/>
-      <c r="BQ128" s="3"/>
-      <c r="BR128" s="3"/>
-      <c r="BS128" s="3"/>
-      <c r="BT128" s="3"/>
-      <c r="BU128" s="3"/>
-      <c r="BV128" s="3"/>
-      <c r="BW128" s="3"/>
-      <c r="BX128" s="3"/>
-      <c r="BY128" s="3"/>
-      <c r="BZ128" s="3"/>
-      <c r="CA128" s="3"/>
-      <c r="CB128" s="3"/>
-      <c r="CC128" s="3"/>
-      <c r="CD128" s="3"/>
-      <c r="CE128" s="3"/>
-      <c r="CF128" s="3"/>
-      <c r="CG128" s="3"/>
-      <c r="CH128" s="3"/>
-      <c r="CI128" s="3"/>
-      <c r="CJ128" s="3"/>
-    </row>
-    <row r="129" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="129" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
         <v>304</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>305</v>
       </c>
+      <c r="AX129" s="3"/>
+      <c r="AY129" s="3"/>
+      <c r="AZ129" s="3"/>
+      <c r="BA129" s="3"/>
+      <c r="BB129" s="3"/>
+      <c r="BC129" s="3"/>
+      <c r="BD129" s="3"/>
+      <c r="BE129" s="3"/>
+      <c r="BF129" s="3"/>
+      <c r="BG129" s="3"/>
+      <c r="BH129" s="3"/>
+      <c r="BI129" s="3"/>
+      <c r="BJ129" s="3"/>
+      <c r="BK129" s="3"/>
+      <c r="BL129" s="3"/>
+      <c r="BM129" s="3"/>
+      <c r="BN129" s="3"/>
+      <c r="BO129" s="3"/>
+      <c r="BP129" s="3"/>
+      <c r="BQ129" s="3"/>
+      <c r="BR129" s="3"/>
+      <c r="BS129" s="3"/>
+      <c r="BT129" s="3"/>
+      <c r="BU129" s="3"/>
+      <c r="BV129" s="3"/>
+      <c r="BW129" s="3"/>
+      <c r="BX129" s="3"/>
+      <c r="BY129" s="3"/>
+      <c r="BZ129" s="3"/>
+      <c r="CA129" s="3"/>
+      <c r="CB129" s="3"/>
+      <c r="CC129" s="3"/>
+      <c r="CD129" s="3"/>
+      <c r="CE129" s="3"/>
+      <c r="CF129" s="3"/>
+      <c r="CG129" s="3"/>
+      <c r="CH129" s="3"/>
+      <c r="CI129" s="3"/>
+      <c r="CJ129" s="3"/>
     </row>
     <row r="130" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
@@ -6202,47 +6239,8 @@
       <c r="B130" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="AX130" s="3"/>
-      <c r="AY130" s="3"/>
-      <c r="AZ130" s="3"/>
-      <c r="BA130" s="3"/>
-      <c r="BB130" s="3"/>
-      <c r="BC130" s="3"/>
-      <c r="BD130" s="3"/>
-      <c r="BE130" s="3"/>
-      <c r="BF130" s="3"/>
-      <c r="BG130" s="3"/>
-      <c r="BH130" s="3"/>
-      <c r="BI130" s="3"/>
-      <c r="BJ130" s="3"/>
-      <c r="BK130" s="3"/>
-      <c r="BL130" s="3"/>
-      <c r="BM130" s="3"/>
-      <c r="BN130" s="3"/>
-      <c r="BO130" s="3"/>
-      <c r="BP130" s="3"/>
-      <c r="BQ130" s="3"/>
-      <c r="BR130" s="3"/>
-      <c r="BS130" s="3"/>
-      <c r="BT130" s="3"/>
-      <c r="BU130" s="3"/>
-      <c r="BV130" s="3"/>
-      <c r="BW130" s="3"/>
-      <c r="BX130" s="3"/>
-      <c r="BY130" s="3"/>
-      <c r="BZ130" s="3"/>
-      <c r="CA130" s="3"/>
-      <c r="CB130" s="3"/>
-      <c r="CC130" s="3"/>
-      <c r="CD130" s="3"/>
-      <c r="CE130" s="3"/>
-      <c r="CF130" s="3"/>
-      <c r="CG130" s="3"/>
-      <c r="CH130" s="3"/>
-      <c r="CI130" s="3"/>
-      <c r="CJ130" s="3"/>
-    </row>
-    <row r="131" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="131" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
         <v>308</v>
       </c>
@@ -6289,78 +6287,117 @@
       <c r="CI131" s="3"/>
       <c r="CJ131" s="3"/>
     </row>
-    <row r="132" s="3" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
         <v>310</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C132" s="1"/>
-      <c r="D132" s="1"/>
-      <c r="E132" s="1"/>
-      <c r="F132" s="1"/>
-      <c r="G132" s="1"/>
-      <c r="H132" s="1"/>
-      <c r="I132" s="1"/>
-      <c r="J132" s="1"/>
-      <c r="K132" s="1"/>
-      <c r="L132" s="1"/>
-      <c r="M132" s="1"/>
-      <c r="N132" s="1"/>
-      <c r="O132" s="1"/>
-      <c r="P132" s="1"/>
-      <c r="Q132" s="1"/>
-      <c r="R132" s="1"/>
-      <c r="S132" s="1"/>
-      <c r="T132" s="1"/>
-      <c r="U132" s="1"/>
-      <c r="V132" s="1"/>
-      <c r="W132" s="1"/>
-      <c r="X132" s="1"/>
-      <c r="Y132" s="1"/>
-      <c r="Z132" s="1"/>
-      <c r="AA132" s="1"/>
-      <c r="AB132" s="1"/>
-      <c r="AC132" s="1"/>
-      <c r="AD132" s="1"/>
-      <c r="AE132" s="1"/>
-      <c r="AF132" s="1"/>
-      <c r="AG132" s="1"/>
-      <c r="AH132" s="1"/>
-      <c r="AI132" s="1"/>
-      <c r="AJ132" s="1"/>
-      <c r="AK132" s="1"/>
-      <c r="AL132" s="1"/>
-      <c r="AM132" s="1"/>
-      <c r="AN132" s="1"/>
-      <c r="AO132" s="1"/>
-      <c r="AP132" s="1"/>
-      <c r="AQ132" s="1"/>
-      <c r="AR132" s="1"/>
-      <c r="AS132" s="1"/>
-      <c r="AT132" s="1"/>
-      <c r="AU132" s="1"/>
-      <c r="AV132" s="1"/>
-      <c r="AW132" s="1"/>
-    </row>
-    <row r="133" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>311</v>
+      </c>
+      <c r="AX132" s="3"/>
+      <c r="AY132" s="3"/>
+      <c r="AZ132" s="3"/>
+      <c r="BA132" s="3"/>
+      <c r="BB132" s="3"/>
+      <c r="BC132" s="3"/>
+      <c r="BD132" s="3"/>
+      <c r="BE132" s="3"/>
+      <c r="BF132" s="3"/>
+      <c r="BG132" s="3"/>
+      <c r="BH132" s="3"/>
+      <c r="BI132" s="3"/>
+      <c r="BJ132" s="3"/>
+      <c r="BK132" s="3"/>
+      <c r="BL132" s="3"/>
+      <c r="BM132" s="3"/>
+      <c r="BN132" s="3"/>
+      <c r="BO132" s="3"/>
+      <c r="BP132" s="3"/>
+      <c r="BQ132" s="3"/>
+      <c r="BR132" s="3"/>
+      <c r="BS132" s="3"/>
+      <c r="BT132" s="3"/>
+      <c r="BU132" s="3"/>
+      <c r="BV132" s="3"/>
+      <c r="BW132" s="3"/>
+      <c r="BX132" s="3"/>
+      <c r="BY132" s="3"/>
+      <c r="BZ132" s="3"/>
+      <c r="CA132" s="3"/>
+      <c r="CB132" s="3"/>
+      <c r="CC132" s="3"/>
+      <c r="CD132" s="3"/>
+      <c r="CE132" s="3"/>
+      <c r="CF132" s="3"/>
+      <c r="CG132" s="3"/>
+      <c r="CH132" s="3"/>
+      <c r="CI132" s="3"/>
+      <c r="CJ132" s="3"/>
+    </row>
+    <row r="133" s="3" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>164</v>
+      </c>
+      <c r="C133" s="1"/>
+      <c r="D133" s="1"/>
+      <c r="E133" s="1"/>
+      <c r="F133" s="1"/>
+      <c r="G133" s="1"/>
+      <c r="H133" s="1"/>
+      <c r="I133" s="1"/>
+      <c r="J133" s="1"/>
+      <c r="K133" s="1"/>
+      <c r="L133" s="1"/>
+      <c r="M133" s="1"/>
+      <c r="N133" s="1"/>
+      <c r="O133" s="1"/>
+      <c r="P133" s="1"/>
+      <c r="Q133" s="1"/>
+      <c r="R133" s="1"/>
+      <c r="S133" s="1"/>
+      <c r="T133" s="1"/>
+      <c r="U133" s="1"/>
+      <c r="V133" s="1"/>
+      <c r="W133" s="1"/>
+      <c r="X133" s="1"/>
+      <c r="Y133" s="1"/>
+      <c r="Z133" s="1"/>
+      <c r="AA133" s="1"/>
+      <c r="AB133" s="1"/>
+      <c r="AC133" s="1"/>
+      <c r="AD133" s="1"/>
+      <c r="AE133" s="1"/>
+      <c r="AF133" s="1"/>
+      <c r="AG133" s="1"/>
+      <c r="AH133" s="1"/>
+      <c r="AI133" s="1"/>
+      <c r="AJ133" s="1"/>
+      <c r="AK133" s="1"/>
+      <c r="AL133" s="1"/>
+      <c r="AM133" s="1"/>
+      <c r="AN133" s="1"/>
+      <c r="AO133" s="1"/>
+      <c r="AP133" s="1"/>
+      <c r="AQ133" s="1"/>
+      <c r="AR133" s="1"/>
+      <c r="AS133" s="1"/>
+      <c r="AT133" s="1"/>
+      <c r="AU133" s="1"/>
+      <c r="AV133" s="1"/>
+      <c r="AW133" s="1"/>
+    </row>
+    <row r="134" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B134" s="8" t="s">
+      <c r="B134" s="4" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
         <v>315</v>
       </c>
@@ -6368,16 +6405,24 @@
         <v>316</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B136" s="4" t="s">
+      <c r="B136" s="8" t="s">
         <v>318</v>
       </c>
     </row>
+    <row r="137" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>320</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:T135"/>
+  <autoFilter ref="A2:T136"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
